--- a/Sajjad data/by_country_and_state/USA/TX.xlsx
+++ b/Sajjad data/by_country_and_state/USA/TX.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="572" uniqueCount="273">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1534" uniqueCount="682">
   <si>
     <t>Business Name</t>
   </si>
@@ -830,6 +830,1233 @@
   </si>
   <si>
     <t>2026-10-24T01:22:16.024Z</t>
+  </si>
+  <si>
+    <t>Promenade Family Dental</t>
+  </si>
+  <si>
+    <t>(972) 470-1700</t>
+  </si>
+  <si>
+    <t>510 N Coit Rd #2048, Richardson, TX 75080</t>
+  </si>
+  <si>
+    <t>Richardson</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Promenade+Family+Dental/data=!4m7!3m6!1s0x864c210463ce46af:0xf844b9559f24e66a!8m2!3d32.9578285!4d-96.7682266!16s%2Fg%2F11x_2grfwz!19sChIJr0bOYwQhTIYRauYkn1W5RPg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T18:59:21.144Z</t>
+  </si>
+  <si>
+    <t>Carrell Darren A DDS</t>
+  </si>
+  <si>
+    <t>(972) 335-6400</t>
+  </si>
+  <si>
+    <t>9720 Coit Rd #130, Plano, TX 75025</t>
+  </si>
+  <si>
+    <t>Plano</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Carrell+Darren+A+DDS/data=!4m7!3m6!1s0x864c3d722448b6e9:0x2a498c4c7cb54d22!8m2!3d33.1110014!4d-96.7659061!16s%2Fg%2F1vnnjt8k!19sChIJ6bZIJHI9TIYRIk21fEyMSSo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T18:59:28.761Z</t>
+  </si>
+  <si>
+    <t>Emergency Dentist Hub</t>
+  </si>
+  <si>
+    <t>(214) 833-3964</t>
+  </si>
+  <si>
+    <t>4280 Lavon Dr #224, Garland, TX 75040</t>
+  </si>
+  <si>
+    <t>Garland</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Emergency+Dentist+Hub/data=!4m7!3m6!1s0x864c1d3e4fbca1f5:0x9d75c9a541e14585!8m2!3d32.9563291!4d-96.616379!16s%2Fg%2F11zx2y3t3h!19sChIJ9aG8Tz4dTIYRhUXhQaXJdZ0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:01:22.381Z</t>
+  </si>
+  <si>
+    <t>Collin Creek Dental</t>
+  </si>
+  <si>
+    <t>(972) 881-7550</t>
+  </si>
+  <si>
+    <t>660 N Central Expy Ste 644, Plano, TX 75074</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Collin+Creek+Dental/data=!4m7!3m6!1s0x864c18df7d91ff77:0x8749875e083ad593!8m2!3d33.0082702!4d-96.7069168!16s%2Fg%2F1tf292bn!19sChIJd_-Rfd8YTIYRk9U6CF6HSYc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:01:50.649Z</t>
+  </si>
+  <si>
+    <t>Sonrisa Dental Clinic</t>
+  </si>
+  <si>
+    <t>(972) 255-7107</t>
+  </si>
+  <si>
+    <t>4040 W Northgate Dr, Irving, TX 75062</t>
+  </si>
+  <si>
+    <t>Irving</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Sonrisa+Dental+Clinic/data=!4m7!3m6!1s0x864e823d945fe9e5:0x9742904145e545b1!8m2!3d32.8565693!4d-97.0058737!16s%2Fg%2F1wfcpk47!19sChIJ5elflD2CToYRsUXlRUGQQpc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:02:41.341Z</t>
+  </si>
+  <si>
+    <t>Irving Mall Family Dental Center</t>
+  </si>
+  <si>
+    <t>(888) 239-7502</t>
+  </si>
+  <si>
+    <t>Medical clinic</t>
+  </si>
+  <si>
+    <t>3879 Irving Mall, Irving, TX 75062</t>
+  </si>
+  <si>
+    <t>4.0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Irving+Mall+Family+Dental+Center/data=!4m7!3m6!1s0x864e8232f4146c1b:0xd12342a625e11d!8m2!3d32.8413167!4d-96.9946072!16s%2Fg%2F1vpfjyvv!19sChIJG2wU9DKCToYRHeElpkIj0QA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:02:43.910Z</t>
+  </si>
+  <si>
+    <t>Pioneer Smiles: Irving</t>
+  </si>
+  <si>
+    <t>(972) 254-6000</t>
+  </si>
+  <si>
+    <t>1711 W Irving Blvd #129, Irving, TX 75061</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Pioneer+Smiles:+Irving/data=!4m7!3m6!1s0x864e83a0ce019115:0xde05520af2f2cca1!8m2!3d32.8229537!4d-96.9658955!16s%2Fg%2F11clv8xp61!19sChIJFZEBzqCDToYRoczy8gpSBd4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:03:44.672Z</t>
+  </si>
+  <si>
+    <t>MacArthur Dental</t>
+  </si>
+  <si>
+    <t>(972) 871-7681</t>
+  </si>
+  <si>
+    <t>2747 N O'Connor Rd, Irving, TX 75062</t>
+  </si>
+  <si>
+    <t>Saturday9 AM–12:30 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/MacArthur+Dental/data=!4m7!3m6!1s0x864e82e31f082c4b:0xaf02b219044e106!8m2!3d32.8439949!4d-96.9516008!16s%2Fg%2F1tcxdm4b!19sChIJSywIH-OCToYRBuFEkCEr8Ao?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:03:47.127Z</t>
+  </si>
+  <si>
+    <t>Rebecca Kim, DDS</t>
+  </si>
+  <si>
+    <t>(972) 444-9337</t>
+  </si>
+  <si>
+    <t>7429 Las Colinas Blvd Suite D100, Irving, TX 75063</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Rebecca+Kim,+DDS/data=!4m7!3m6!1s0x864c29928a456aff:0x2a7af55dfbe7e1c1!8m2!3d32.9088691!4d-96.9544352!16s%2Fg%2F11h0hps0d6!19sChIJ_2pFipIpTIYRweHn-131eio?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:03:49.803Z</t>
+  </si>
+  <si>
+    <t>Optimal Dental Care</t>
+  </si>
+  <si>
+    <t>(972) 252-1600</t>
+  </si>
+  <si>
+    <t>3200 N MacArthur Blvd Ste 212, Irving, TX 75062</t>
+  </si>
+  <si>
+    <t>Saturday8–11:30 AM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Optimal+Dental+Care/data=!4m7!3m6!1s0x864e82f964b6a713:0xa3f253af9caa5bb1!8m2!3d32.8482322!4d-96.9586975!16s%2Fg%2F11rs0x74v!19sChIJE6e2ZPmCToYRsVuqnK9T8qM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:03:52.378Z</t>
+  </si>
+  <si>
+    <t>Dr. Carolyn F. Wilson, DDS</t>
+  </si>
+  <si>
+    <t>(972) 252-7569</t>
+  </si>
+  <si>
+    <t>Pediatric dentist</t>
+  </si>
+  <si>
+    <t>3219 N MacArthur Blvd Suite 100, Irving, TX 75062</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Carolyn+F.+Wilson,+DDS/data=!4m7!3m6!1s0x864e82f99c3e0603:0x2ff34bdae5f9c296!8m2!3d32.8491911!4d-96.9593948!16s%2Fg%2F1wzt2sn1!19sChIJAwY-nPmCToYRlsL55dpL8y8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:05:54.043Z</t>
+  </si>
+  <si>
+    <t>Pioneer Dental</t>
+  </si>
+  <si>
+    <t>(972) 870-5282</t>
+  </si>
+  <si>
+    <t>1100 W Pioneer Dr, Irving, TX 75061</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Pioneer+Dental/data=!4m7!3m6!1s0x864e830b9fb18d23:0x30d2e247c787149e!8m2!3d32.820995!4d-96.95969!16s%2Fg%2F1tfsndfm!19sChIJI42xnwuDToYRnhSHx0fi0jA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:05:56.289Z</t>
+  </si>
+  <si>
+    <t>Irving Emergency Dental Service</t>
+  </si>
+  <si>
+    <t>(469) 283-5218</t>
+  </si>
+  <si>
+    <t>9462 N MacArthur Blvd, Irving, TX 75063</t>
+  </si>
+  <si>
+    <t>3.0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Irving+Emergency+Dental+Service/data=!4m7!3m6!1s0x864c2910913534d9:0x2c7539df3b78d9e4!8m2!3d32.934559!4d-96.9514995!16s%2Fg%2F11mhlk8tsy!19sChIJ2TQ1kRApTIYR5Nl4O985dSw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:07:44.134Z</t>
+  </si>
+  <si>
+    <t>1800 Dentist Irving</t>
+  </si>
+  <si>
+    <t>(844) 213-6850</t>
+  </si>
+  <si>
+    <t>724 N Belt Line Rd, Irving, TX 75060</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/1800+Dentist+Irving/data=!4m7!3m6!1s0x864e830013f482d5:0xca276e57f40fb51c!8m2!3d32.82133!4d-96.9927635!16s%2Fg%2F11yl0q26tf!19sChIJ1YL0EwCDToYRHLUP9FduJ8o?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:07:46.289Z</t>
+  </si>
+  <si>
+    <t>Urgent Dental and Denture Care</t>
+  </si>
+  <si>
+    <t>(214) 935-5832</t>
+  </si>
+  <si>
+    <t>4952 N O'Connor Rd, Irving, TX 75062</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Urgent+Dental+and+Denture+Care/data=!4m7!3m6!1s0x864e83132e739d5f:0xf01bc408d8413736!8m2!3d32.8658994!4d-96.9460072!16s%2Fg%2F11sdxd01wc!19sChIJX51zLhODToYRNjdB2AjEG_A?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:07:49.203Z</t>
+  </si>
+  <si>
+    <t>Ever Dental Care</t>
+  </si>
+  <si>
+    <t>(972) 903-8573</t>
+  </si>
+  <si>
+    <t>136 E Irving Blvd, Irving, TX 75060</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Ever+Dental+Care/data=!4m7!3m6!1s0x864e830493ad91c7:0x52ddaa3a49cf9361!8m2!3d32.8136249!4d-96.9452352!16s%2Fg%2F11wng4rghy!19sChIJx5GtkwSDToYRYZPPSTqq3VI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:08:15.295Z</t>
+  </si>
+  <si>
+    <t>ThaiDentalClinic</t>
+  </si>
+  <si>
+    <t>(972) 276-5025</t>
+  </si>
+  <si>
+    <t>3465 W Walnut St #209, Garland, TX 75042</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/ThaiDentalClinic/data=!4m7!3m6!1s0x864c1e1681027f73:0x7cd506a13f47841d!8m2!3d32.9187086!4d-96.681722!16s%2Fg%2F1tjdglnf!19sChIJc38CgRYeTIYRHYRHP6EG1Xw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:09:20.641Z</t>
+  </si>
+  <si>
+    <t>Live Oak Dentistry &amp; Implant Center</t>
+  </si>
+  <si>
+    <t>(972) 240-0400</t>
+  </si>
+  <si>
+    <t>4449 Broadway Blvd, Garland, TX 75043</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Live+Oak+Dentistry+%26+Implant+Center/data=!4m7!3m6!1s0x864ea7b4c7a541d3:0x2bd777fc17507b74!8m2!3d32.860636!4d-96.603576!16s%2Fg%2F1tggp18q!19sChIJ00Glx7SnToYRdHtQF_x31ys?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:10:42.821Z</t>
+  </si>
+  <si>
+    <t>Smith Jr Robert H DDS</t>
+  </si>
+  <si>
+    <t>(972) 272-3496</t>
+  </si>
+  <si>
+    <t>1605 N Garland Ave # B, Garland, TX 75040</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Smith+Jr+Robert+H+DDS/data=!4m7!3m6!1s0x864c1dc3cb608fc5:0x236f6c692da28efb!8m2!3d32.927651!4d-96.6488904!16s%2Fg%2F1tdpglr9!19sChIJxY9gy8MdTIYR-46iLWlsbyM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:11:13.728Z</t>
+  </si>
+  <si>
+    <t>Best Smile Dental</t>
+  </si>
+  <si>
+    <t>(972) 271-5800</t>
+  </si>
+  <si>
+    <t>3421 W Kingsley Rd #103, Garland, TX 75041</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Best+Smile+Dental/data=!4m7!3m6!1s0x864ea0bf69a2d4f5:0xcea3f5bac393d95d!8m2!3d32.879094!4d-96.681314!16s%2Fg%2F11bz_2lckc!19sChIJ9dSiab-gToYRXdmTw7r1o84?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:11:26.144Z</t>
+  </si>
+  <si>
+    <t>The Periodontal Specialists</t>
+  </si>
+  <si>
+    <t>(844) 568-3384</t>
+  </si>
+  <si>
+    <t>4880 N President George Bush Hwy, Garland, TX 75040</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/The+Periodontal+Specialists/data=!4m7!3m6!1s0x864c1c4574958823:0x2cdf7d28dad0099f!8m2!3d32.9610025!4d-96.6337742!16s%2Fg%2F11g8v63x3c!19sChIJI4iVdEUcTIYRnwnQ2ih93yw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:13:47.463Z</t>
+  </si>
+  <si>
+    <t>GM Family Dental</t>
+  </si>
+  <si>
+    <t>(972) 988-3333</t>
+  </si>
+  <si>
+    <t>2507 Medical Row #104, Grand Prairie, TX 75051</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/GM+Family+Dental/data=!4m7!3m6!1s0x864e864dde9f35bd:0x3d2ff78ce2c77e8d!8m2!3d32.7335253!4d-97.0445865!16s%2Fg%2F1tdlhq6c!19sChIJvTWf3k2GToYRjX7H4oz3Lz0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:26:06.467Z</t>
+  </si>
+  <si>
+    <t>East Pioneer Dental</t>
+  </si>
+  <si>
+    <t>(972) 262-7200</t>
+  </si>
+  <si>
+    <t>2518 Hillcrest Ln #100, Grand Prairie, TX 75052</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/East+Pioneer+Dental/data=!4m7!3m6!1s0x864e86072ab92475:0x837db0a35df86918!8m2!3d32.7086423!4d-97.0094452!16s%2Fg%2F11f0l319_v!19sChIJdSS5KgeGToYRGGn4XaOwfYM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:26:09.076Z</t>
+  </si>
+  <si>
+    <t>Loyal Family Dentistry</t>
+  </si>
+  <si>
+    <t>(972) 264-4791</t>
+  </si>
+  <si>
+    <t>1021 SW 3rd St, Grand Prairie, TX 75051</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Loyal+Family+Dentistry/data=!4m7!3m6!1s0x864e85d8bf41233d:0xfb73b53cf27a3e47!8m2!3d32.7326013!4d-97.0057126!16s%2Fg%2F1tpbcd24!19sChIJPSNBv9iFToYRRz568jy1c_s?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:26:11.551Z</t>
+  </si>
+  <si>
+    <t>Serein Dental Implants &amp; Aesthetics</t>
+  </si>
+  <si>
+    <t>(972) 854-7339</t>
+  </si>
+  <si>
+    <t>5244 S State Hwy 360 Ste 398, Grand Prairie, TX 75052</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Serein+Dental+Implants+%26+Aesthetics/data=!4m7!3m6!1s0x864e8976e264f48f:0xf4c09aeaaf770ade!8m2!3d32.6453361!4d-97.0612801!16s%2Fg%2F11zz9z1mg3!19sChIJj_Rk4naJToYR3gp3r-qawPQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:29:11.260Z</t>
+  </si>
+  <si>
+    <t>The Pearl Bar</t>
+  </si>
+  <si>
+    <t>(972) 588-4494</t>
+  </si>
+  <si>
+    <t>2100 S Great SW Pkwy #306, Grand Prairie, TX 75051</t>
+  </si>
+  <si>
+    <t>1.0</t>
+  </si>
+  <si>
+    <t>Saturday1 PM–12 AM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/The+Pearl+Bar/data=!4m7!3m6!1s0x864e863203aa84a3:0x38ff0657115b215b!8m2!3d32.712894!4d-97.0444252!16s%2Fg%2F11c432k11p!19sChIJo4SqAzKGToYRWyFbEVcG_zg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:29:59.252Z</t>
+  </si>
+  <si>
+    <t>Denture Care Center Amarillo</t>
+  </si>
+  <si>
+    <t>(806) 207-3153</t>
+  </si>
+  <si>
+    <t>Denture care center</t>
+  </si>
+  <si>
+    <t>1105 S Taylor St, Amarillo, TX 79101</t>
+  </si>
+  <si>
+    <t>Amarillo</t>
+  </si>
+  <si>
+    <t>4</t>
+  </si>
+  <si>
+    <t>Saturday8 AM–8 PM; Sunday8 AM–5 PM; Monday8 AM–8 PM; Tuesday8 AM–8 PM; Wednesday8 AM–8 PM; Thursday8 AM–8 PM; Friday8 AM–8 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Denture+Care+Center+Amarillo/data=!4m7!3m6!1s0x87014fd2d7eb35ff:0xeb23013f54431ed6!8m2!3d35.2017953!4d-101.836394!16s%2Fg%2F11rcwcbq_r!19sChIJ_zXr19JPAYcR1h5DVD8BI-s?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:31:23.326Z</t>
+  </si>
+  <si>
+    <t>Urgent Dentist Help</t>
+  </si>
+  <si>
+    <t>(806) 207-9076</t>
+  </si>
+  <si>
+    <t>2467 W Interstate 40 Frontage Rd, Amarillo, TX 79109</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Urgent+Dentist+Help/data=!4m7!3m6!1s0x87014f5008ef748b:0x1a49a39101c8a789!8m2!3d35.193817!4d-101.8647597!16s%2Fg%2F11zx2x6ktc!19sChIJi3TvCFBPAYcRiafIAZGjSRo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:32:57.097Z</t>
+  </si>
+  <si>
+    <t>Short Todd DDS</t>
+  </si>
+  <si>
+    <t>(806) 374-8011</t>
+  </si>
+  <si>
+    <t>3503 S Soncy Rd, Amarillo, TX 79119</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Short+Todd+DDS/data=!4m7!3m6!1s0x870150f4fd844093:0x5b48cd98382312f0!8m2!3d35.1727837!4d-101.9376765!16s%2Fg%2F11c2qfvjk8!19sChIJk0CE_fRQAYcR8BIjOJjNSFs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:33:17.568Z</t>
+  </si>
+  <si>
+    <t>Ritchie Thomas M DDS</t>
+  </si>
+  <si>
+    <t>(806) 358-7311</t>
+  </si>
+  <si>
+    <t>1600 Coulter St S, Amarillo, TX 79106</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Ritchie+Thomas+M+DDS/data=!4m7!3m6!1s0x870151b263fc1851:0x9965134303ab8385!8m2!3d35.1967505!4d-101.9224265!16s%2Fg%2F1tfqrd76!19sChIJURj8Y7JRAYcRhYOrA0MTZZk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:33:23.590Z</t>
+  </si>
+  <si>
+    <t>Collins III B Houston DDS.</t>
+  </si>
+  <si>
+    <t>(806) 356-9448</t>
+  </si>
+  <si>
+    <t>10 Care Cir # B, Amarillo, TX 79124</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Collins+III+B+Houston+DDS./data=!4m7!3m6!1s0x870150530bd2a023:0x19697282040d4c85!8m2!3d35.1901819!4d-101.9268705!16s%2Fg%2F1tf_nrpl!19sChIJI6DSC1NQAYcRhUwNBIJyaRk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:33:46.701Z</t>
+  </si>
+  <si>
+    <t>Osborn William S, DDS</t>
+  </si>
+  <si>
+    <t>(806) 355-9226</t>
+  </si>
+  <si>
+    <t>4000 SW 34th Ave #B, Amarillo, TX 79109</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Osborn+William+S,+DDS/data=!4m7!3m6!1s0x87014fddb554b34b:0xeab8fb2304ff1285!8m2!3d35.1792487!4d-101.8822059!16s%2Fg%2F1tdfnqg8!19sChIJS7NUtd1PAYcRhRL_BCP7uOo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:34:12.103Z</t>
+  </si>
+  <si>
+    <t>whiten up by karrie teeth whitening</t>
+  </si>
+  <si>
+    <t>(806) 410-7366</t>
+  </si>
+  <si>
+    <t>3611 Soncy Rd Ste 1, Amarillo, TX 79119</t>
+  </si>
+  <si>
+    <t>Saturday10 AM–5 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/whiten+up+by+karrie+teeth+whitening/data=!4m7!3m6!1s0x8701512ff56b3cb9:0xfbef70f4593c7b12!8m2!3d35.169333!4d-101.937682!16s%2Fg%2F11v60yxpjl!19sChIJuTxr9S9RAYcREns8WfRw7_s?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:35:25.633Z</t>
+  </si>
+  <si>
+    <t>Brownsville Dental Clinic</t>
+  </si>
+  <si>
+    <t>(888) 217-4563</t>
+  </si>
+  <si>
+    <t>3193 W Alton Gloor Blvd Ste. P, Brownsville, TX 78520</t>
+  </si>
+  <si>
+    <t>Brownsville</t>
+  </si>
+  <si>
+    <t>Saturday11 AM–5 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Brownsville+Dental+Clinic/data=!4m7!3m6!1s0x866f91c32a92981f:0xba6131f690ab56dd!8m2!3d25.974465!4d-97.5314302!16s%2Fg%2F11r91t_3br!19sChIJH5iSKsORb4YR3VarkPYxYbo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:36:01.068Z</t>
+  </si>
+  <si>
+    <t>Valle Dental Center.</t>
+  </si>
+  <si>
+    <t>(844) 595-3679</t>
+  </si>
+  <si>
+    <t>925 W Jefferson St, Brownsville, TX 78520</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Valle+Dental+Center./data=!4m7!3m6!1s0x866f946cd7c199ad:0xa9b739845e807bd6!8m2!3d25.9186808!4d-97.5123063!16s%2Fg%2F1tzgpn8x!19sChIJrZnB12yUb4YR1nuAXoQ5t6k?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:36:03.853Z</t>
+  </si>
+  <si>
+    <t>STAR Dental</t>
+  </si>
+  <si>
+    <t>(956) 800-0123</t>
+  </si>
+  <si>
+    <t>2921 Boca Chica Blvd, Brownsville, TX 78521</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/STAR+Dental/data=!4m7!3m6!1s0x866f95fbe8d2fd8f:0x47cd816acab369e9!8m2!3d25.9218506!4d-97.47674!16s%2Fg%2F11jn4m300m!19sChIJj_3S6PuVb4YR6WmzymqBzUc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:36:05.647Z</t>
+  </si>
+  <si>
+    <t>A Tooth Fairy's Place</t>
+  </si>
+  <si>
+    <t>(956) 541-3624</t>
+  </si>
+  <si>
+    <t>1725 Central Blvd, Brownsville, TX 78520</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/A+Tooth+Fairy%27s+Place/data=!4m7!3m6!1s0x866f941081a9fc43:0x2b8dafd3e21dcd9e!8m2!3d25.928129!4d-97.5114595!16s%2Fg%2F1tgcs9s3!19sChIJQ_ypgRCUb4YRns0d4tOvjSs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:36:21.623Z</t>
+  </si>
+  <si>
+    <t>Professional Dental Group.</t>
+  </si>
+  <si>
+    <t>(956) 545-0668</t>
+  </si>
+  <si>
+    <t>1115 Professional Dr, Brownsville, TX 78520</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Professional+Dental+Group./data=!4m7!3m6!1s0x866f95b38140ff33:0x561881cb939dd80f!8m2!3d25.9179111!4d-97.5138375!16s%2Fg%2F11h64s7l_d!19sChIJM_9AgbOVb4YRD9idk8uBGFY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:36:24.641Z</t>
+  </si>
+  <si>
+    <t>Dr. Joe D. Zayas, DDS</t>
+  </si>
+  <si>
+    <t>(956) 546-7788</t>
+  </si>
+  <si>
+    <t>555 Boca Chica Blvd, Brownsville, TX 78520</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Joe+D.+Zayas,+DDS/data=!4m7!3m6!1s0x866f9411cc03ddd9:0xacac754f62134249!8m2!3d25.9262224!4d-97.5128784!16s%2Fg%2F1tmxrg28!19sChIJ2d0DzBGUb4YRSUITYk91rKw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:36:27.382Z</t>
+  </si>
+  <si>
+    <t>Brownsville Dental Center</t>
+  </si>
+  <si>
+    <t>(956) 621-0707</t>
+  </si>
+  <si>
+    <t>2744 Southmost Rd, Brownsville, TX 78521</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Brownsville+Dental+Center/data=!4m7!3m6!1s0x866f95a4bcef3fd7:0xbf5a8becb6eec86e!8m2!3d25.9070414!4d-97.4659552!16s%2Fg%2F1tfctngg!19sChIJ1z_vvKSVb4YRbsjutuyLWr8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:36:30.092Z</t>
+  </si>
+  <si>
+    <t>ABC Family Dental Care</t>
+  </si>
+  <si>
+    <t>(956) 548-0222</t>
+  </si>
+  <si>
+    <t>4430 E 14th St # C, Brownsville, TX 78521</t>
+  </si>
+  <si>
+    <t>3.4</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/ABC+Family+Dental+Care/data=!4m7!3m6!1s0x866f95c75ce10e2b:0x43324a166fc3ad54!8m2!3d25.9197268!4d-97.4674868!16s%2Fg%2F1tnctb5_!19sChIJKw7hXMeVb4YRVK3DbxZKMkM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:36:35.135Z</t>
+  </si>
+  <si>
+    <t>Dr. Gaylord R. Lewis, DDS</t>
+  </si>
+  <si>
+    <t>(956) 541-2181</t>
+  </si>
+  <si>
+    <t>35 W Elizabeth St, Brownsville, TX 78520</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Gaylord+R.+Lewis,+DDS/data=!4m7!3m6!1s0x866f9469240bee03:0xc1e0c0e846239368!8m2!3d25.9095826!4d-97.5074623!16s%2Fg%2F1vqth6jw!19sChIJA-4LJGmUb4YRaJMjRujA4ME?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:36:49.067Z</t>
+  </si>
+  <si>
+    <t>Dr. Kevin P. Osborne, DMD</t>
+  </si>
+  <si>
+    <t>(956) 546-2973</t>
+  </si>
+  <si>
+    <t>2334 Boca Chica Blvd #200, Brownsville, TX 78521</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Kevin+P.+Osborne,+DMD/data=!4m7!3m6!1s0x866f9436794bce99:0x312752492378c235!8m2!3d25.9206943!4d-97.4864061!16s%2Fg%2F1thw2l17!19sChIJmc5LeTaUb4YRNcJ4I0lSJzE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:36:50.783Z</t>
+  </si>
+  <si>
+    <t>Rio Grande Oral-Maxillofacial</t>
+  </si>
+  <si>
+    <t>(956) 542-2870</t>
+  </si>
+  <si>
+    <t>2330 Central Blvd, Brownsville, TX 78520</t>
+  </si>
+  <si>
+    <t>2.4</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Rio+Grande+Oral-Maxillofacial/data=!4m7!3m6!1s0x866f941c6a159879:0xe843d366f34559ed!8m2!3d25.936343!4d-97.5097306!16s%2Fg%2F1tfrh5yq!19sChIJeZgVahyUb4YR7VlF82bTQ-g?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:36:52.969Z</t>
+  </si>
+  <si>
+    <t>Dr. Alvaro Garza</t>
+  </si>
+  <si>
+    <t>(956) 372-1540</t>
+  </si>
+  <si>
+    <t>1113 Central Blvd a, Brownsville, TX 78520</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Alvaro+Garza/data=!4m7!3m6!1s0x866f941243caee85:0xa9f9a5ba0e666e01!8m2!3d25.921582!4d-97.5123648!16s%2Fg%2F11rwxfy6rj!19sChIJhe7KQxKUb4YRAW5mDrql-ak?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:36:55.321Z</t>
+  </si>
+  <si>
+    <t>Dr. Nelly Gonzalez, DDS</t>
+  </si>
+  <si>
+    <t>(956) 542-9200</t>
+  </si>
+  <si>
+    <t>2501 Paredes Line Rd Ste B3, Brownsville, TX 78526</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Nelly+Gonzalez,+DDS/data=!4m7!3m6!1s0x866f9700c608bac9:0x52de6a1a14aff9dc!8m2!3d25.9528337!4d-97.4875253!16s%2Fg%2F1tfl0mzr!19sChIJyboIxgCXb4YR3PmvFBpq3lI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:36:57.783Z</t>
+  </si>
+  <si>
+    <t>Melba Ortiz-Rivera</t>
+  </si>
+  <si>
+    <t>(956) 542-1956</t>
+  </si>
+  <si>
+    <t>1205 E Alton Gloor Blvd, Brownsville, TX 78526</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Melba+Ortiz-Rivera/data=!4m7!3m6!1s0x866f96e43045502b:0x63cf78d0d2cb940c!8m2!3d25.98074!4d-97.4968501!16s%2Fg%2F11tn6l49s3!19sChIJK1BFMOSWb4YRDJTL0tB4z2M?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:37:00.482Z</t>
+  </si>
+  <si>
+    <t>Dr. Manfred L. Delcastillo Jr, DDS</t>
+  </si>
+  <si>
+    <t>(956) 982-1533</t>
+  </si>
+  <si>
+    <t>1650 Paredes Line Rd Ste 103, Brownsville, TX 78521</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Manfred+L.+Delcastillo+Jr,+DDS/data=!4m7!3m6!1s0x866f9683db2bdf19:0x6317f75801d1f10e!8m2!3d25.9452478!4d-97.487265!16s%2Fg%2F1tgx2g3_!19sChIJGd8r24OWb4YRDvHRAVj3F2M?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:37:03.496Z</t>
+  </si>
+  <si>
+    <t>Ortiz-Rivera M DDS</t>
+  </si>
+  <si>
+    <t>(956) 465-4316</t>
+  </si>
+  <si>
+    <t>1004 Texas Ave, Brownsville, TX 78521</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Ortiz-Rivera+M+DDS/data=!4m7!3m6!1s0x866f95b59c466b41:0x3445ed76a02006ab!8m2!3d25.9183892!4d-97.4785934!16s%2Fg%2F12616n_59!19sChIJQWtGnLWVb4YRqwYgoHbtRTQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:37:05.361Z</t>
+  </si>
+  <si>
+    <t>Dr. George C. Collis, DDS</t>
+  </si>
+  <si>
+    <t>(956) 546-6260</t>
+  </si>
+  <si>
+    <t>6110 California Rd, Brownsville, TX 78521</t>
+  </si>
+  <si>
+    <t>3.3</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+George+C.+Collis,+DDS/data=!4m7!3m6!1s0x866fbfd275e51a59:0xfa466395b8126c36!8m2!3d25.894522!4d-97.427783!16s%2Fg%2F1tdfcjpn!19sChIJWRrlddK_b4YRNmwSuJVjRvo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:37:08.104Z</t>
+  </si>
+  <si>
+    <t>Los Fresnos Family Dentistry</t>
+  </si>
+  <si>
+    <t>(956) 233-5100</t>
+  </si>
+  <si>
+    <t>209 N Arroyo Blvd, Los Fresnos, TX 78566</t>
+  </si>
+  <si>
+    <t>Los Fresnos</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Los+Fresnos+Family+Dentistry/data=!4m7!3m6!1s0x866f99b2a03d9d0d:0x6f56de17b93ace8c!8m2!3d26.0729376!4d-97.4763304!16s%2Fg%2F1tjpqydq!19sChIJDZ09oLKZb4YRjM46uRfeVm8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:37:19.057Z</t>
+  </si>
+  <si>
+    <t>Leos Xavier DDS.</t>
+  </si>
+  <si>
+    <t>(956) 542-4466</t>
+  </si>
+  <si>
+    <t>1800 Central Blvd, Brownsville, TX 78520</t>
+  </si>
+  <si>
+    <t>2.2</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Leos+Xavier+DDS./data=!4m7!3m6!1s0x866f941082e875e1:0xd3d6d1d05ace8dbf!8m2!3d25.9293371!4d-97.5105532!16s%2Fg%2F1tf9nppf!19sChIJ4XXoghCUb4YRv43OWtDR1tM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:38:37.101Z</t>
+  </si>
+  <si>
+    <t>Attaphitaya Surat DDS</t>
+  </si>
+  <si>
+    <t>(956) 542-1177</t>
+  </si>
+  <si>
+    <t>4237 North Expy Ste 1, Brownsville, TX 78520</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Attaphitaya+Surat+DDS/data=!4m7!3m6!1s0x866f9419755ee083:0x272c008822b70d3f!8m2!3d25.964662!4d-97.5123202!16s%2Fg%2F1tf2snhk!19sChIJg-BedRmUb4YRPw23IogALCc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:39:09.866Z</t>
+  </si>
+  <si>
+    <t>Stetic Implant &amp; Dental Center</t>
+  </si>
+  <si>
+    <t>(956) 565-5100</t>
+  </si>
+  <si>
+    <t>201 S Texas Ave St, Mercedes, TX 78570</t>
+  </si>
+  <si>
+    <t>Mercedes</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Stetic+Implant+%26+Dental+Center/data=!4m7!3m6!1s0x86657900db44cf6d:0xcc0e58512cfb68e3!8m2!3d26.1497669!4d-97.9136108!16s%2Fg%2F1tdmkxt8!19sChIJbc9E2wB5ZYYR42j7LFFYDsw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:39:24.757Z</t>
+  </si>
+  <si>
+    <t>Certified Implant Center</t>
+  </si>
+  <si>
+    <t>+52 899 937 1225</t>
+  </si>
+  <si>
+    <t>Av. Benito Juárez 194-1-194-1, 88810 Nuevo Progreso, Tamps., Mexico</t>
+  </si>
+  <si>
+    <t>Tamps.</t>
+  </si>
+  <si>
+    <t>Saturday8 AM–6 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Certified+Implant+Center/data=!4m7!3m6!1s0x86657b04cb6da63f:0xdf5d5b24785750b!8m2!3d26.0605051!4d-97.9505349!16s%2Fg%2F11pf7rvv4c!19sChIJP6ZtywR7ZYYRC3WFR7LV9Q0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:39:27.551Z</t>
+  </si>
+  <si>
+    <t>Centro de especialidades odontologicas certificadas</t>
+  </si>
+  <si>
+    <t>+52 868 101 3233</t>
+  </si>
+  <si>
+    <t>Dental implants periodontist</t>
+  </si>
+  <si>
+    <t>Av. Álvaro Obregón 32, Jardín, 87330 Heroica Matamoros, Tamps., Mexico</t>
+  </si>
+  <si>
+    <t>2</t>
+  </si>
+  <si>
+    <t>Saturday9 AM–5 PM; SundayClosed; Monday9 AM–7 PM; Tuesday9 AM–7 PM; Wednesday9 AM–7 PM; Thursday9 AM–7 PM; Friday9 AM–7 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Centro+de+especialidades+odontologicas+certificadas/data=!4m7!3m6!1s0x866f952e7ff27545:0xdf83c9fa8d2dda19!8m2!3d25.8913!4d-97.502429!16s%2Fg%2F11jg1qd4z6!19sChIJRXXyfy6Vb4YRGdotjfrJg98?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:39:31.910Z</t>
+  </si>
+  <si>
+    <t>Urgencias Dentales Matamoros</t>
+  </si>
+  <si>
+    <t>+52 868 342 4320</t>
+  </si>
+  <si>
+    <t>Frente al IMSS, Av. Gral. Lauro Villar #606, Treviño Zapata, 87450 Heroica Matamoros, Tamps., Mexico</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Urgencias+Dentales+Matamoros/data=!4m7!3m6!1s0x866f95d77846ce5d:0x6347256f03384e!8m2!3d25.8600422!4d-97.4747164!16s%2Fg%2F11hw2pgnr8!19sChIJXc5GeNeVb4YRTjgDbyVHYwA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:39:42.926Z</t>
+  </si>
+  <si>
+    <t>Lindale Medical &amp; Dental Center</t>
+  </si>
+  <si>
+    <t>(956) 546-1868</t>
+  </si>
+  <si>
+    <t>Radiologist</t>
+  </si>
+  <si>
+    <t>500 Paredes Line Rd A, Brownsville, TX 78521</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Lindale+Medical+%26+Dental+Center/data=!4m7!3m6!1s0x866f9431c4ec62a9:0x916b1780795913cc!8m2!3d25.9297879!4d-97.4885807!16s%2Fg%2F1td4q3zr!19sChIJqWLsxDGUb4YRzBNZeYAXa5E?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:39:59.060Z</t>
+  </si>
+  <si>
+    <t>Hinojosa Dental Laboratory</t>
+  </si>
+  <si>
+    <t>(956) 542-5757</t>
+  </si>
+  <si>
+    <t>Dental laboratory</t>
+  </si>
+  <si>
+    <t>895 Ridgewood St, Brownsville, TX 78520</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Hinojosa+Dental+Laboratory/data=!4m7!3m6!1s0x866f942257ee7c8d:0x47dff4ffe9c06541!8m2!3d25.9330073!4d-97.5010845!16s%2Fg%2F1tg5vh1n!19sChIJjXzuVyKUb4YRQWXA6f_030c?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:40:01.661Z</t>
+  </si>
+  <si>
+    <t>Gutierrez Repairing Dental</t>
+  </si>
+  <si>
+    <t>(956) 544-5063</t>
+  </si>
+  <si>
+    <t>718 E 12th St, Brownsville, TX 78520</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Gutierrez+Repairing+Dental/data=!4m7!3m6!1s0x866f945b95b37537:0x5667fb7564be4f20!8m2!3d25.9025149!4d-97.4964113!16s%2Fg%2F1tk_pq47!19sChIJN3WzlVuUb4YRIE--ZHX7Z1Y?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:40:03.831Z</t>
+  </si>
+  <si>
+    <t>Killeen Free Clinic</t>
+  </si>
+  <si>
+    <t>(254) 618-4211</t>
+  </si>
+  <si>
+    <t>Community health center</t>
+  </si>
+  <si>
+    <t>718 N 2nd St Ste A, Killeen, TX 76541</t>
+  </si>
+  <si>
+    <t>Killeen</t>
+  </si>
+  <si>
+    <t>13</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Killeen+Free+Clinic/data=!4m7!3m6!1s0x86454b8809a46845:0x1f3673766e52b906!8m2!3d31.124761!4d-97.7286518!16s%2Fg%2F1tffvb43!19sChIJRWikCYhLRYYRBrlSbnZzNh8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:40:50.560Z</t>
+  </si>
+  <si>
+    <t>Thomas E Young DDS</t>
+  </si>
+  <si>
+    <t>(254) 690-8200</t>
+  </si>
+  <si>
+    <t>807 S W S Young Dr, Killeen, TX 76543</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Thomas+E+Young+DDS/data=!4m7!3m6!1s0x86454bec2a79d3df:0xee79d185b5df181f!8m2!3d31.1070175!4d-97.716896!16s%2Fg%2F1tj1sh1c!19sChIJ39N5KuxLRYYRHxjftYXRee4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:41:33.260Z</t>
+  </si>
+  <si>
+    <t>Fanning Donald DDS</t>
+  </si>
+  <si>
+    <t>(254) 690-3600</t>
+  </si>
+  <si>
+    <t>4104 E Stan Schlueter Loop Ste 4, Killeen, TX 76542</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Fanning+Donald+DDS/data=!4m7!3m6!1s0x86454a2b3cc14fa7:0xd02d2b5bb333bcdd!8m2!3d31.0774473!4d-97.7017457!16s%2Fg%2F1td33fnq!19sChIJp0_BPCtKRYYR3bwzs1srLdA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:42:23.068Z</t>
+  </si>
+  <si>
+    <t>Dr. Michael B. Berman, DDS</t>
+  </si>
+  <si>
+    <t>(254) 628-0221</t>
+  </si>
+  <si>
+    <t>1711 E Central Texas Expy, Killeen, TX 76541</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Michael+B.+Berman,+DDS/data=!4m7!3m6!1s0x86454bb91fc7325f:0xedf8e72fa3b37b5a!8m2!3d31.0932644!4d-97.722872!16s%2Fg%2F1tfk9dlt!19sChIJXzLHH7lLRYYRWnuzoy_n-O0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:42:25.397Z</t>
+  </si>
+  <si>
+    <t>Dr. Ethan Higson</t>
+  </si>
+  <si>
+    <t>(254) 634-3811</t>
+  </si>
+  <si>
+    <t>3106 S W S Young Dr Ste A-101, Killeen, TX 76542</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Ethan+Higson/data=!4m7!3m6!1s0x86454bb60bffffff:0xb0ecdd7d1b2b7cd6!8m2!3d31.083279!4d-97.7209636!16s%2Fg%2F11qgb7cjnc!19sChIJ____C7ZLRYYR1nwrG33d7LA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:42:33.295Z</t>
+  </si>
+  <si>
+    <t>Dr. Mary Rose C. Black, DMD</t>
+  </si>
+  <si>
+    <t>(512) 537-3301</t>
+  </si>
+  <si>
+    <t>2300 E Rancier Ave Ste 110, Killeen, TX 76543</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Mary+Rose+C.+Black,+DMD/data=!4m7!3m6!1s0x86454bf9d61706bf:0x47e90296329f03a0!8m2!3d31.1201501!4d-97.7088971!16s%2Fg%2F1hc1pscwr!19sChIJvwYX1vlLRYYRoAOfMpYC6Uc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:42:37.605Z</t>
+  </si>
+  <si>
+    <t>Dr. Suzanne Baldwin</t>
+  </si>
+  <si>
+    <t>(254) 213-6300</t>
+  </si>
+  <si>
+    <t>1711 E Central Texas Expy Ste 102, Killeen, TX 76541</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Suzanne+Baldwin/data=!4m7!3m6!1s0x86454bb926f3a021:0x788ccbd3ba23d76c!8m2!3d31.0932791!4d-97.7229035!16s%2Fg%2F11rwxf6r16!19sChIJIaDzJrlLRYYRbNcjutPLjHg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:42:42.204Z</t>
+  </si>
+  <si>
+    <t>Pundt Gary w DDS</t>
+  </si>
+  <si>
+    <t>(254) 634-0234</t>
+  </si>
+  <si>
+    <t>421 N 38th St, Killeen, TX 76543</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Pundt+Gary+w+DDS/data=!4m7!3m6!1s0x86454be2d4f77399:0x2c0fcc8e23cd210c!8m2!3d31.11247!4d-97.7003815!16s%2Fg%2F1tdzlz1k!19sChIJmXP31OJLRYYRDCHNI47MDyw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:43:27.806Z</t>
+  </si>
+  <si>
+    <t>Dr. Edward E. Yang, DDS</t>
+  </si>
+  <si>
+    <t>(254) 690-7997</t>
+  </si>
+  <si>
+    <t>1203 E Central Texas Expy, Killeen, TX 76541</t>
+  </si>
+  <si>
+    <t>2.5</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Edward+E.+Yang,+DDS/data=!4m7!3m6!1s0x86454bbca2b51eaf:0xe41c1d2b41e74576!8m2!3d31.0949579!4d-97.7298947!16s%2Fg%2F1xg5t1sm!19sChIJrx61orxLRYYRdkXnQSsdHOQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:43:46.319Z</t>
+  </si>
+  <si>
+    <t>Dr. Aditi Saxena</t>
+  </si>
+  <si>
+    <t>(254) 680-4450</t>
+  </si>
+  <si>
+    <t>5610 E Central Texas Expy Ste 3, Killeen, TX 76543</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Aditi+Saxena/data=!4m7!3m6!1s0x8645498349d116f3:0x463ac3a3c0435d41!8m2!3d31.0749062!4d-97.6878513!16s%2Fg%2F11p07bdp8g!19sChIJ8xbRSYNJRYYRQV1DwKPDOkY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:44:19.051Z</t>
+  </si>
+  <si>
+    <t>Resolution Dental</t>
+  </si>
+  <si>
+    <t>(254) 781-0537</t>
+  </si>
+  <si>
+    <t>2200 S W S Young Dr, Killeen, TX 76543</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Resolution+Dental/data=!4m7!3m6!1s0x86454ba48b8972fb:0x2e23d80089a86dde!8m2!3d31.094488!4d-97.720634!16s%2Fg%2F1tfbck41!19sChIJ-3KJi6RLRYYR3m2oiQDYIy4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:44:43.730Z</t>
+  </si>
+  <si>
+    <t>Harker Heights Smiles</t>
+  </si>
+  <si>
+    <t>(254) 699-7002</t>
+  </si>
+  <si>
+    <t>100 W Central Texas Expy #110, Harker Heights, TX 76548</t>
+  </si>
+  <si>
+    <t>Harker Heights</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Harker+Heights+Smiles/data=!4m7!3m6!1s0x864549a4dad77275:0x34e21bd2954d67bc!8m2!3d31.0692731!4d-97.6693005!16s%2Fg%2F1thhkxk8!19sChIJdXLX2qRJRYYRvGdNldIb4jQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:45:11.744Z</t>
+  </si>
+  <si>
+    <t>Perkins Dental.</t>
+  </si>
+  <si>
+    <t>(254) 288-7695</t>
+  </si>
+  <si>
+    <t>33001 Battalion Ave, Fort Hood, TX 76544</t>
+  </si>
+  <si>
+    <t>Fort Hood</t>
+  </si>
+  <si>
+    <t>1.9</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Perkins+Dental./data=!4m7!3m6!1s0x865ab33640f9d5c9:0xc8e5fcc6604da0be!8m2!3d31.1430171!4d-97.793166!16s%2Fg%2F11cmc4f6sr!19sChIJydX5QDazWoYRvqBNYMb85cg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:45:27.784Z</t>
+  </si>
+  <si>
+    <t>Johnathan Callia</t>
+  </si>
+  <si>
+    <t>(254) 295-1980</t>
+  </si>
+  <si>
+    <t>410 E Central Texas Expy Bell, Harker Heights, TX 76548</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Johnathan+Callia/data=!4m7!3m6!1s0x864549add5dab8e9:0xc36b1ef746535610!8m2!3d31.071999!4d-97.6601142!16s%2Fg%2F11t6xq701h!19sChIJ6bja1a1JRYYREFZTRvcea8M?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T19:45:47.933Z</t>
   </si>
 </sst>
 </file>
@@ -1210,7 +2437,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M44"/>
+  <dimension ref="A1:M118"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -3031,6 +4258,3040 @@
         <v>272</v>
       </c>
     </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A45" t="s">
+        <v>273</v>
+      </c>
+      <c r="B45" t="s">
+        <v>274</v>
+      </c>
+      <c r="C45" t="s">
+        <v>15</v>
+      </c>
+      <c r="D45" t="s">
+        <v>275</v>
+      </c>
+      <c r="E45" t="s">
+        <v>276</v>
+      </c>
+      <c r="F45" t="s">
+        <v>18</v>
+      </c>
+      <c r="G45" t="s">
+        <v>19</v>
+      </c>
+      <c r="H45" t="s">
+        <v>20</v>
+      </c>
+      <c r="I45" t="s">
+        <v>21</v>
+      </c>
+      <c r="J45" t="s">
+        <v>30</v>
+      </c>
+      <c r="K45" t="s">
+        <v>23</v>
+      </c>
+      <c r="L45" t="s">
+        <v>277</v>
+      </c>
+      <c r="M45" t="s">
+        <v>278</v>
+      </c>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A46" t="s">
+        <v>279</v>
+      </c>
+      <c r="B46" t="s">
+        <v>280</v>
+      </c>
+      <c r="C46" t="s">
+        <v>15</v>
+      </c>
+      <c r="D46" t="s">
+        <v>281</v>
+      </c>
+      <c r="E46" t="s">
+        <v>282</v>
+      </c>
+      <c r="F46" t="s">
+        <v>18</v>
+      </c>
+      <c r="G46" t="s">
+        <v>19</v>
+      </c>
+      <c r="H46" t="s">
+        <v>78</v>
+      </c>
+      <c r="I46" t="s">
+        <v>21</v>
+      </c>
+      <c r="J46" t="s">
+        <v>30</v>
+      </c>
+      <c r="K46" t="s">
+        <v>23</v>
+      </c>
+      <c r="L46" t="s">
+        <v>283</v>
+      </c>
+      <c r="M46" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A47" t="s">
+        <v>285</v>
+      </c>
+      <c r="B47" t="s">
+        <v>286</v>
+      </c>
+      <c r="C47" t="s">
+        <v>88</v>
+      </c>
+      <c r="D47" t="s">
+        <v>287</v>
+      </c>
+      <c r="E47" t="s">
+        <v>288</v>
+      </c>
+      <c r="F47" t="s">
+        <v>18</v>
+      </c>
+      <c r="G47" t="s">
+        <v>19</v>
+      </c>
+      <c r="H47" t="s">
+        <v>65</v>
+      </c>
+      <c r="I47" t="s">
+        <v>66</v>
+      </c>
+      <c r="J47" t="s">
+        <v>65</v>
+      </c>
+      <c r="K47" t="s">
+        <v>23</v>
+      </c>
+      <c r="L47" t="s">
+        <v>289</v>
+      </c>
+      <c r="M47" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A48" t="s">
+        <v>291</v>
+      </c>
+      <c r="B48" t="s">
+        <v>292</v>
+      </c>
+      <c r="C48" t="s">
+        <v>15</v>
+      </c>
+      <c r="D48" t="s">
+        <v>293</v>
+      </c>
+      <c r="E48" t="s">
+        <v>282</v>
+      </c>
+      <c r="F48" t="s">
+        <v>18</v>
+      </c>
+      <c r="G48" t="s">
+        <v>19</v>
+      </c>
+      <c r="H48" t="s">
+        <v>36</v>
+      </c>
+      <c r="I48" t="s">
+        <v>21</v>
+      </c>
+      <c r="J48" t="s">
+        <v>30</v>
+      </c>
+      <c r="K48" t="s">
+        <v>23</v>
+      </c>
+      <c r="L48" t="s">
+        <v>294</v>
+      </c>
+      <c r="M48" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="49" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A49" t="s">
+        <v>296</v>
+      </c>
+      <c r="B49" t="s">
+        <v>297</v>
+      </c>
+      <c r="C49" t="s">
+        <v>62</v>
+      </c>
+      <c r="D49" t="s">
+        <v>298</v>
+      </c>
+      <c r="E49" t="s">
+        <v>299</v>
+      </c>
+      <c r="F49" t="s">
+        <v>18</v>
+      </c>
+      <c r="G49" t="s">
+        <v>19</v>
+      </c>
+      <c r="H49" t="s">
+        <v>43</v>
+      </c>
+      <c r="I49" t="s">
+        <v>21</v>
+      </c>
+      <c r="J49" t="s">
+        <v>30</v>
+      </c>
+      <c r="K49" t="s">
+        <v>23</v>
+      </c>
+      <c r="L49" t="s">
+        <v>300</v>
+      </c>
+      <c r="M49" t="s">
+        <v>301</v>
+      </c>
+    </row>
+    <row r="50" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A50" t="s">
+        <v>302</v>
+      </c>
+      <c r="B50" t="s">
+        <v>303</v>
+      </c>
+      <c r="C50" t="s">
+        <v>304</v>
+      </c>
+      <c r="D50" t="s">
+        <v>305</v>
+      </c>
+      <c r="E50" t="s">
+        <v>299</v>
+      </c>
+      <c r="F50" t="s">
+        <v>18</v>
+      </c>
+      <c r="G50" t="s">
+        <v>19</v>
+      </c>
+      <c r="H50" t="s">
+        <v>306</v>
+      </c>
+      <c r="I50" t="s">
+        <v>21</v>
+      </c>
+      <c r="J50" t="s">
+        <v>173</v>
+      </c>
+      <c r="K50" t="s">
+        <v>23</v>
+      </c>
+      <c r="L50" t="s">
+        <v>307</v>
+      </c>
+      <c r="M50" t="s">
+        <v>308</v>
+      </c>
+    </row>
+    <row r="51" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A51" t="s">
+        <v>309</v>
+      </c>
+      <c r="B51" t="s">
+        <v>310</v>
+      </c>
+      <c r="C51" t="s">
+        <v>15</v>
+      </c>
+      <c r="D51" t="s">
+        <v>311</v>
+      </c>
+      <c r="E51" t="s">
+        <v>299</v>
+      </c>
+      <c r="F51" t="s">
+        <v>18</v>
+      </c>
+      <c r="G51" t="s">
+        <v>19</v>
+      </c>
+      <c r="H51" t="s">
+        <v>20</v>
+      </c>
+      <c r="I51" t="s">
+        <v>21</v>
+      </c>
+      <c r="J51" t="s">
+        <v>30</v>
+      </c>
+      <c r="K51" t="s">
+        <v>23</v>
+      </c>
+      <c r="L51" t="s">
+        <v>312</v>
+      </c>
+      <c r="M51" t="s">
+        <v>313</v>
+      </c>
+    </row>
+    <row r="52" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A52" t="s">
+        <v>314</v>
+      </c>
+      <c r="B52" t="s">
+        <v>315</v>
+      </c>
+      <c r="C52" t="s">
+        <v>15</v>
+      </c>
+      <c r="D52" t="s">
+        <v>316</v>
+      </c>
+      <c r="E52" t="s">
+        <v>299</v>
+      </c>
+      <c r="F52" t="s">
+        <v>18</v>
+      </c>
+      <c r="G52" t="s">
+        <v>19</v>
+      </c>
+      <c r="H52" t="s">
+        <v>72</v>
+      </c>
+      <c r="I52" t="s">
+        <v>21</v>
+      </c>
+      <c r="J52" t="s">
+        <v>317</v>
+      </c>
+      <c r="K52" t="s">
+        <v>23</v>
+      </c>
+      <c r="L52" t="s">
+        <v>318</v>
+      </c>
+      <c r="M52" t="s">
+        <v>319</v>
+      </c>
+    </row>
+    <row r="53" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A53" t="s">
+        <v>320</v>
+      </c>
+      <c r="B53" t="s">
+        <v>321</v>
+      </c>
+      <c r="C53" t="s">
+        <v>15</v>
+      </c>
+      <c r="D53" t="s">
+        <v>322</v>
+      </c>
+      <c r="E53" t="s">
+        <v>299</v>
+      </c>
+      <c r="F53" t="s">
+        <v>18</v>
+      </c>
+      <c r="G53" t="s">
+        <v>19</v>
+      </c>
+      <c r="H53" t="s">
+        <v>72</v>
+      </c>
+      <c r="I53" t="s">
+        <v>21</v>
+      </c>
+      <c r="J53" t="s">
+        <v>258</v>
+      </c>
+      <c r="K53" t="s">
+        <v>23</v>
+      </c>
+      <c r="L53" t="s">
+        <v>323</v>
+      </c>
+      <c r="M53" t="s">
+        <v>324</v>
+      </c>
+    </row>
+    <row r="54" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A54" t="s">
+        <v>325</v>
+      </c>
+      <c r="B54" t="s">
+        <v>326</v>
+      </c>
+      <c r="C54" t="s">
+        <v>15</v>
+      </c>
+      <c r="D54" t="s">
+        <v>327</v>
+      </c>
+      <c r="E54" t="s">
+        <v>299</v>
+      </c>
+      <c r="F54" t="s">
+        <v>18</v>
+      </c>
+      <c r="G54" t="s">
+        <v>19</v>
+      </c>
+      <c r="H54" t="s">
+        <v>43</v>
+      </c>
+      <c r="I54" t="s">
+        <v>21</v>
+      </c>
+      <c r="J54" t="s">
+        <v>328</v>
+      </c>
+      <c r="K54" t="s">
+        <v>23</v>
+      </c>
+      <c r="L54" t="s">
+        <v>329</v>
+      </c>
+      <c r="M54" t="s">
+        <v>330</v>
+      </c>
+    </row>
+    <row r="55" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A55" t="s">
+        <v>331</v>
+      </c>
+      <c r="B55" t="s">
+        <v>332</v>
+      </c>
+      <c r="C55" t="s">
+        <v>333</v>
+      </c>
+      <c r="D55" t="s">
+        <v>334</v>
+      </c>
+      <c r="E55" t="s">
+        <v>299</v>
+      </c>
+      <c r="F55" t="s">
+        <v>18</v>
+      </c>
+      <c r="G55" t="s">
+        <v>19</v>
+      </c>
+      <c r="H55" t="s">
+        <v>72</v>
+      </c>
+      <c r="I55" t="s">
+        <v>21</v>
+      </c>
+      <c r="J55" t="s">
+        <v>65</v>
+      </c>
+      <c r="K55" t="s">
+        <v>23</v>
+      </c>
+      <c r="L55" t="s">
+        <v>335</v>
+      </c>
+      <c r="M55" t="s">
+        <v>336</v>
+      </c>
+    </row>
+    <row r="56" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A56" t="s">
+        <v>337</v>
+      </c>
+      <c r="B56" t="s">
+        <v>338</v>
+      </c>
+      <c r="C56" t="s">
+        <v>138</v>
+      </c>
+      <c r="D56" t="s">
+        <v>339</v>
+      </c>
+      <c r="E56" t="s">
+        <v>299</v>
+      </c>
+      <c r="F56" t="s">
+        <v>18</v>
+      </c>
+      <c r="G56" t="s">
+        <v>19</v>
+      </c>
+      <c r="H56" t="s">
+        <v>78</v>
+      </c>
+      <c r="I56" t="s">
+        <v>21</v>
+      </c>
+      <c r="J56" t="s">
+        <v>251</v>
+      </c>
+      <c r="K56" t="s">
+        <v>23</v>
+      </c>
+      <c r="L56" t="s">
+        <v>340</v>
+      </c>
+      <c r="M56" t="s">
+        <v>341</v>
+      </c>
+    </row>
+    <row r="57" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A57" t="s">
+        <v>342</v>
+      </c>
+      <c r="B57" t="s">
+        <v>343</v>
+      </c>
+      <c r="C57" t="s">
+        <v>88</v>
+      </c>
+      <c r="D57" t="s">
+        <v>344</v>
+      </c>
+      <c r="E57" t="s">
+        <v>299</v>
+      </c>
+      <c r="F57" t="s">
+        <v>18</v>
+      </c>
+      <c r="G57" t="s">
+        <v>19</v>
+      </c>
+      <c r="H57" t="s">
+        <v>345</v>
+      </c>
+      <c r="I57" t="s">
+        <v>21</v>
+      </c>
+      <c r="J57" t="s">
+        <v>65</v>
+      </c>
+      <c r="K57" t="s">
+        <v>23</v>
+      </c>
+      <c r="L57" t="s">
+        <v>346</v>
+      </c>
+      <c r="M57" t="s">
+        <v>347</v>
+      </c>
+    </row>
+    <row r="58" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A58" t="s">
+        <v>348</v>
+      </c>
+      <c r="B58" t="s">
+        <v>349</v>
+      </c>
+      <c r="C58" t="s">
+        <v>88</v>
+      </c>
+      <c r="D58" t="s">
+        <v>350</v>
+      </c>
+      <c r="E58" t="s">
+        <v>299</v>
+      </c>
+      <c r="F58" t="s">
+        <v>18</v>
+      </c>
+      <c r="G58" t="s">
+        <v>19</v>
+      </c>
+      <c r="H58" t="s">
+        <v>72</v>
+      </c>
+      <c r="I58" t="s">
+        <v>21</v>
+      </c>
+      <c r="J58" t="s">
+        <v>65</v>
+      </c>
+      <c r="K58" t="s">
+        <v>23</v>
+      </c>
+      <c r="L58" t="s">
+        <v>351</v>
+      </c>
+      <c r="M58" t="s">
+        <v>352</v>
+      </c>
+    </row>
+    <row r="59" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A59" t="s">
+        <v>353</v>
+      </c>
+      <c r="B59" t="s">
+        <v>354</v>
+      </c>
+      <c r="C59" t="s">
+        <v>88</v>
+      </c>
+      <c r="D59" t="s">
+        <v>355</v>
+      </c>
+      <c r="E59" t="s">
+        <v>299</v>
+      </c>
+      <c r="F59" t="s">
+        <v>18</v>
+      </c>
+      <c r="G59" t="s">
+        <v>19</v>
+      </c>
+      <c r="H59" t="s">
+        <v>72</v>
+      </c>
+      <c r="I59" t="s">
+        <v>21</v>
+      </c>
+      <c r="J59" t="s">
+        <v>65</v>
+      </c>
+      <c r="K59" t="s">
+        <v>23</v>
+      </c>
+      <c r="L59" t="s">
+        <v>356</v>
+      </c>
+      <c r="M59" t="s">
+        <v>357</v>
+      </c>
+    </row>
+    <row r="60" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A60" t="s">
+        <v>358</v>
+      </c>
+      <c r="B60" t="s">
+        <v>359</v>
+      </c>
+      <c r="C60" t="s">
+        <v>88</v>
+      </c>
+      <c r="D60" t="s">
+        <v>360</v>
+      </c>
+      <c r="E60" t="s">
+        <v>299</v>
+      </c>
+      <c r="F60" t="s">
+        <v>18</v>
+      </c>
+      <c r="G60" t="s">
+        <v>19</v>
+      </c>
+      <c r="H60" t="s">
+        <v>72</v>
+      </c>
+      <c r="I60" t="s">
+        <v>21</v>
+      </c>
+      <c r="J60" t="s">
+        <v>65</v>
+      </c>
+      <c r="K60" t="s">
+        <v>23</v>
+      </c>
+      <c r="L60" t="s">
+        <v>361</v>
+      </c>
+      <c r="M60" t="s">
+        <v>362</v>
+      </c>
+    </row>
+    <row r="61" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A61" t="s">
+        <v>363</v>
+      </c>
+      <c r="B61" t="s">
+        <v>364</v>
+      </c>
+      <c r="C61" t="s">
+        <v>15</v>
+      </c>
+      <c r="D61" t="s">
+        <v>365</v>
+      </c>
+      <c r="E61" t="s">
+        <v>288</v>
+      </c>
+      <c r="F61" t="s">
+        <v>18</v>
+      </c>
+      <c r="G61" t="s">
+        <v>19</v>
+      </c>
+      <c r="H61" t="s">
+        <v>122</v>
+      </c>
+      <c r="I61" t="s">
+        <v>21</v>
+      </c>
+      <c r="J61" t="s">
+        <v>51</v>
+      </c>
+      <c r="K61" t="s">
+        <v>23</v>
+      </c>
+      <c r="L61" t="s">
+        <v>366</v>
+      </c>
+      <c r="M61" t="s">
+        <v>367</v>
+      </c>
+    </row>
+    <row r="62" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A62" t="s">
+        <v>368</v>
+      </c>
+      <c r="B62" t="s">
+        <v>369</v>
+      </c>
+      <c r="C62" t="s">
+        <v>15</v>
+      </c>
+      <c r="D62" t="s">
+        <v>370</v>
+      </c>
+      <c r="E62" t="s">
+        <v>288</v>
+      </c>
+      <c r="F62" t="s">
+        <v>18</v>
+      </c>
+      <c r="G62" t="s">
+        <v>19</v>
+      </c>
+      <c r="H62" t="s">
+        <v>122</v>
+      </c>
+      <c r="I62" t="s">
+        <v>21</v>
+      </c>
+      <c r="J62" t="s">
+        <v>65</v>
+      </c>
+      <c r="K62" t="s">
+        <v>23</v>
+      </c>
+      <c r="L62" t="s">
+        <v>371</v>
+      </c>
+      <c r="M62" t="s">
+        <v>372</v>
+      </c>
+    </row>
+    <row r="63" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A63" t="s">
+        <v>373</v>
+      </c>
+      <c r="B63" t="s">
+        <v>374</v>
+      </c>
+      <c r="C63" t="s">
+        <v>15</v>
+      </c>
+      <c r="D63" t="s">
+        <v>375</v>
+      </c>
+      <c r="E63" t="s">
+        <v>288</v>
+      </c>
+      <c r="F63" t="s">
+        <v>18</v>
+      </c>
+      <c r="G63" t="s">
+        <v>19</v>
+      </c>
+      <c r="H63" t="s">
+        <v>72</v>
+      </c>
+      <c r="I63" t="s">
+        <v>21</v>
+      </c>
+      <c r="J63" t="s">
+        <v>30</v>
+      </c>
+      <c r="K63" t="s">
+        <v>23</v>
+      </c>
+      <c r="L63" t="s">
+        <v>376</v>
+      </c>
+      <c r="M63" t="s">
+        <v>377</v>
+      </c>
+    </row>
+    <row r="64" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A64" t="s">
+        <v>378</v>
+      </c>
+      <c r="B64" t="s">
+        <v>379</v>
+      </c>
+      <c r="C64" t="s">
+        <v>15</v>
+      </c>
+      <c r="D64" t="s">
+        <v>380</v>
+      </c>
+      <c r="E64" t="s">
+        <v>288</v>
+      </c>
+      <c r="F64" t="s">
+        <v>18</v>
+      </c>
+      <c r="G64" t="s">
+        <v>19</v>
+      </c>
+      <c r="H64" t="s">
+        <v>72</v>
+      </c>
+      <c r="I64" t="s">
+        <v>21</v>
+      </c>
+      <c r="J64" t="s">
+        <v>44</v>
+      </c>
+      <c r="K64" t="s">
+        <v>23</v>
+      </c>
+      <c r="L64" t="s">
+        <v>381</v>
+      </c>
+      <c r="M64" t="s">
+        <v>382</v>
+      </c>
+    </row>
+    <row r="65" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A65" t="s">
+        <v>383</v>
+      </c>
+      <c r="B65" t="s">
+        <v>384</v>
+      </c>
+      <c r="C65" t="s">
+        <v>15</v>
+      </c>
+      <c r="D65" t="s">
+        <v>385</v>
+      </c>
+      <c r="E65" t="s">
+        <v>288</v>
+      </c>
+      <c r="F65" t="s">
+        <v>18</v>
+      </c>
+      <c r="G65" t="s">
+        <v>19</v>
+      </c>
+      <c r="H65" t="s">
+        <v>65</v>
+      </c>
+      <c r="I65" t="s">
+        <v>66</v>
+      </c>
+      <c r="J65" t="s">
+        <v>65</v>
+      </c>
+      <c r="K65" t="s">
+        <v>23</v>
+      </c>
+      <c r="L65" t="s">
+        <v>386</v>
+      </c>
+      <c r="M65" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="66" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A66" t="s">
+        <v>388</v>
+      </c>
+      <c r="B66" t="s">
+        <v>389</v>
+      </c>
+      <c r="C66" t="s">
+        <v>62</v>
+      </c>
+      <c r="D66" t="s">
+        <v>390</v>
+      </c>
+      <c r="E66" t="s">
+        <v>156</v>
+      </c>
+      <c r="F66" t="s">
+        <v>18</v>
+      </c>
+      <c r="G66" t="s">
+        <v>19</v>
+      </c>
+      <c r="H66" t="s">
+        <v>29</v>
+      </c>
+      <c r="I66" t="s">
+        <v>21</v>
+      </c>
+      <c r="J66" t="s">
+        <v>30</v>
+      </c>
+      <c r="K66" t="s">
+        <v>23</v>
+      </c>
+      <c r="L66" t="s">
+        <v>391</v>
+      </c>
+      <c r="M66" t="s">
+        <v>392</v>
+      </c>
+    </row>
+    <row r="67" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A67" t="s">
+        <v>393</v>
+      </c>
+      <c r="B67" t="s">
+        <v>394</v>
+      </c>
+      <c r="C67" t="s">
+        <v>15</v>
+      </c>
+      <c r="D67" t="s">
+        <v>395</v>
+      </c>
+      <c r="E67" t="s">
+        <v>156</v>
+      </c>
+      <c r="F67" t="s">
+        <v>18</v>
+      </c>
+      <c r="G67" t="s">
+        <v>19</v>
+      </c>
+      <c r="H67" t="s">
+        <v>128</v>
+      </c>
+      <c r="I67" t="s">
+        <v>21</v>
+      </c>
+      <c r="J67" t="s">
+        <v>251</v>
+      </c>
+      <c r="K67" t="s">
+        <v>23</v>
+      </c>
+      <c r="L67" t="s">
+        <v>396</v>
+      </c>
+      <c r="M67" t="s">
+        <v>397</v>
+      </c>
+    </row>
+    <row r="68" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A68" t="s">
+        <v>398</v>
+      </c>
+      <c r="B68" t="s">
+        <v>399</v>
+      </c>
+      <c r="C68" t="s">
+        <v>15</v>
+      </c>
+      <c r="D68" t="s">
+        <v>400</v>
+      </c>
+      <c r="E68" t="s">
+        <v>156</v>
+      </c>
+      <c r="F68" t="s">
+        <v>18</v>
+      </c>
+      <c r="G68" t="s">
+        <v>19</v>
+      </c>
+      <c r="H68" t="s">
+        <v>72</v>
+      </c>
+      <c r="I68" t="s">
+        <v>21</v>
+      </c>
+      <c r="J68" t="s">
+        <v>30</v>
+      </c>
+      <c r="K68" t="s">
+        <v>23</v>
+      </c>
+      <c r="L68" t="s">
+        <v>401</v>
+      </c>
+      <c r="M68" t="s">
+        <v>402</v>
+      </c>
+    </row>
+    <row r="69" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A69" t="s">
+        <v>403</v>
+      </c>
+      <c r="B69" t="s">
+        <v>404</v>
+      </c>
+      <c r="C69" t="s">
+        <v>15</v>
+      </c>
+      <c r="D69" t="s">
+        <v>405</v>
+      </c>
+      <c r="E69" t="s">
+        <v>156</v>
+      </c>
+      <c r="F69" t="s">
+        <v>18</v>
+      </c>
+      <c r="G69" t="s">
+        <v>19</v>
+      </c>
+      <c r="H69" t="s">
+        <v>65</v>
+      </c>
+      <c r="I69" t="s">
+        <v>66</v>
+      </c>
+      <c r="J69" t="s">
+        <v>65</v>
+      </c>
+      <c r="K69" t="s">
+        <v>23</v>
+      </c>
+      <c r="L69" t="s">
+        <v>406</v>
+      </c>
+      <c r="M69" t="s">
+        <v>407</v>
+      </c>
+    </row>
+    <row r="70" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A70" t="s">
+        <v>408</v>
+      </c>
+      <c r="B70" t="s">
+        <v>409</v>
+      </c>
+      <c r="C70" t="s">
+        <v>171</v>
+      </c>
+      <c r="D70" t="s">
+        <v>410</v>
+      </c>
+      <c r="E70" t="s">
+        <v>156</v>
+      </c>
+      <c r="F70" t="s">
+        <v>18</v>
+      </c>
+      <c r="G70" t="s">
+        <v>19</v>
+      </c>
+      <c r="H70" t="s">
+        <v>411</v>
+      </c>
+      <c r="I70" t="s">
+        <v>21</v>
+      </c>
+      <c r="J70" t="s">
+        <v>412</v>
+      </c>
+      <c r="K70" t="s">
+        <v>23</v>
+      </c>
+      <c r="L70" t="s">
+        <v>413</v>
+      </c>
+      <c r="M70" t="s">
+        <v>414</v>
+      </c>
+    </row>
+    <row r="71" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A71" t="s">
+        <v>415</v>
+      </c>
+      <c r="B71" t="s">
+        <v>416</v>
+      </c>
+      <c r="C71" t="s">
+        <v>417</v>
+      </c>
+      <c r="D71" t="s">
+        <v>418</v>
+      </c>
+      <c r="E71" t="s">
+        <v>419</v>
+      </c>
+      <c r="F71" t="s">
+        <v>18</v>
+      </c>
+      <c r="G71" t="s">
+        <v>19</v>
+      </c>
+      <c r="H71" t="s">
+        <v>306</v>
+      </c>
+      <c r="I71" t="s">
+        <v>420</v>
+      </c>
+      <c r="J71" t="s">
+        <v>421</v>
+      </c>
+      <c r="K71" t="s">
+        <v>23</v>
+      </c>
+      <c r="L71" t="s">
+        <v>422</v>
+      </c>
+      <c r="M71" t="s">
+        <v>423</v>
+      </c>
+    </row>
+    <row r="72" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A72" t="s">
+        <v>424</v>
+      </c>
+      <c r="B72" t="s">
+        <v>425</v>
+      </c>
+      <c r="C72" t="s">
+        <v>88</v>
+      </c>
+      <c r="D72" t="s">
+        <v>426</v>
+      </c>
+      <c r="E72" t="s">
+        <v>419</v>
+      </c>
+      <c r="F72" t="s">
+        <v>18</v>
+      </c>
+      <c r="G72" t="s">
+        <v>19</v>
+      </c>
+      <c r="H72" t="s">
+        <v>411</v>
+      </c>
+      <c r="I72" t="s">
+        <v>21</v>
+      </c>
+      <c r="J72" t="s">
+        <v>65</v>
+      </c>
+      <c r="K72" t="s">
+        <v>23</v>
+      </c>
+      <c r="L72" t="s">
+        <v>427</v>
+      </c>
+      <c r="M72" t="s">
+        <v>428</v>
+      </c>
+    </row>
+    <row r="73" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A73" t="s">
+        <v>429</v>
+      </c>
+      <c r="B73" t="s">
+        <v>430</v>
+      </c>
+      <c r="C73" t="s">
+        <v>15</v>
+      </c>
+      <c r="D73" t="s">
+        <v>431</v>
+      </c>
+      <c r="E73" t="s">
+        <v>419</v>
+      </c>
+      <c r="F73" t="s">
+        <v>18</v>
+      </c>
+      <c r="G73" t="s">
+        <v>19</v>
+      </c>
+      <c r="H73" t="s">
+        <v>72</v>
+      </c>
+      <c r="I73" t="s">
+        <v>21</v>
+      </c>
+      <c r="J73" t="s">
+        <v>30</v>
+      </c>
+      <c r="K73" t="s">
+        <v>23</v>
+      </c>
+      <c r="L73" t="s">
+        <v>432</v>
+      </c>
+      <c r="M73" t="s">
+        <v>433</v>
+      </c>
+    </row>
+    <row r="74" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A74" t="s">
+        <v>434</v>
+      </c>
+      <c r="B74" t="s">
+        <v>435</v>
+      </c>
+      <c r="C74" t="s">
+        <v>15</v>
+      </c>
+      <c r="D74" t="s">
+        <v>436</v>
+      </c>
+      <c r="E74" t="s">
+        <v>419</v>
+      </c>
+      <c r="F74" t="s">
+        <v>18</v>
+      </c>
+      <c r="G74" t="s">
+        <v>19</v>
+      </c>
+      <c r="H74" t="s">
+        <v>72</v>
+      </c>
+      <c r="I74" t="s">
+        <v>21</v>
+      </c>
+      <c r="J74" t="s">
+        <v>65</v>
+      </c>
+      <c r="K74" t="s">
+        <v>23</v>
+      </c>
+      <c r="L74" t="s">
+        <v>437</v>
+      </c>
+      <c r="M74" t="s">
+        <v>438</v>
+      </c>
+    </row>
+    <row r="75" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A75" t="s">
+        <v>439</v>
+      </c>
+      <c r="B75" t="s">
+        <v>440</v>
+      </c>
+      <c r="C75" t="s">
+        <v>15</v>
+      </c>
+      <c r="D75" t="s">
+        <v>441</v>
+      </c>
+      <c r="E75" t="s">
+        <v>419</v>
+      </c>
+      <c r="F75" t="s">
+        <v>18</v>
+      </c>
+      <c r="G75" t="s">
+        <v>19</v>
+      </c>
+      <c r="H75" t="s">
+        <v>72</v>
+      </c>
+      <c r="I75" t="s">
+        <v>21</v>
+      </c>
+      <c r="J75" t="s">
+        <v>30</v>
+      </c>
+      <c r="K75" t="s">
+        <v>23</v>
+      </c>
+      <c r="L75" t="s">
+        <v>442</v>
+      </c>
+      <c r="M75" t="s">
+        <v>443</v>
+      </c>
+    </row>
+    <row r="76" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A76" t="s">
+        <v>444</v>
+      </c>
+      <c r="B76" t="s">
+        <v>445</v>
+      </c>
+      <c r="C76" t="s">
+        <v>15</v>
+      </c>
+      <c r="D76" t="s">
+        <v>446</v>
+      </c>
+      <c r="E76" t="s">
+        <v>419</v>
+      </c>
+      <c r="F76" t="s">
+        <v>18</v>
+      </c>
+      <c r="G76" t="s">
+        <v>19</v>
+      </c>
+      <c r="H76" t="s">
+        <v>72</v>
+      </c>
+      <c r="I76" t="s">
+        <v>21</v>
+      </c>
+      <c r="J76" t="s">
+        <v>30</v>
+      </c>
+      <c r="K76" t="s">
+        <v>23</v>
+      </c>
+      <c r="L76" t="s">
+        <v>447</v>
+      </c>
+      <c r="M76" t="s">
+        <v>448</v>
+      </c>
+    </row>
+    <row r="77" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A77" t="s">
+        <v>449</v>
+      </c>
+      <c r="B77" t="s">
+        <v>450</v>
+      </c>
+      <c r="C77" t="s">
+        <v>171</v>
+      </c>
+      <c r="D77" t="s">
+        <v>451</v>
+      </c>
+      <c r="E77" t="s">
+        <v>419</v>
+      </c>
+      <c r="F77" t="s">
+        <v>18</v>
+      </c>
+      <c r="G77" t="s">
+        <v>19</v>
+      </c>
+      <c r="H77" t="s">
+        <v>72</v>
+      </c>
+      <c r="I77" t="s">
+        <v>21</v>
+      </c>
+      <c r="J77" t="s">
+        <v>452</v>
+      </c>
+      <c r="K77" t="s">
+        <v>23</v>
+      </c>
+      <c r="L77" t="s">
+        <v>453</v>
+      </c>
+      <c r="M77" t="s">
+        <v>454</v>
+      </c>
+    </row>
+    <row r="78" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A78" t="s">
+        <v>455</v>
+      </c>
+      <c r="B78" t="s">
+        <v>456</v>
+      </c>
+      <c r="C78" t="s">
+        <v>304</v>
+      </c>
+      <c r="D78" t="s">
+        <v>457</v>
+      </c>
+      <c r="E78" t="s">
+        <v>458</v>
+      </c>
+      <c r="F78" t="s">
+        <v>18</v>
+      </c>
+      <c r="G78" t="s">
+        <v>19</v>
+      </c>
+      <c r="H78" t="s">
+        <v>250</v>
+      </c>
+      <c r="I78" t="s">
+        <v>21</v>
+      </c>
+      <c r="J78" t="s">
+        <v>459</v>
+      </c>
+      <c r="K78" t="s">
+        <v>23</v>
+      </c>
+      <c r="L78" t="s">
+        <v>460</v>
+      </c>
+      <c r="M78" t="s">
+        <v>461</v>
+      </c>
+    </row>
+    <row r="79" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A79" t="s">
+        <v>462</v>
+      </c>
+      <c r="B79" t="s">
+        <v>463</v>
+      </c>
+      <c r="C79" t="s">
+        <v>62</v>
+      </c>
+      <c r="D79" t="s">
+        <v>464</v>
+      </c>
+      <c r="E79" t="s">
+        <v>458</v>
+      </c>
+      <c r="F79" t="s">
+        <v>18</v>
+      </c>
+      <c r="G79" t="s">
+        <v>19</v>
+      </c>
+      <c r="H79" t="s">
+        <v>72</v>
+      </c>
+      <c r="I79" t="s">
+        <v>21</v>
+      </c>
+      <c r="J79" t="s">
+        <v>30</v>
+      </c>
+      <c r="K79" t="s">
+        <v>23</v>
+      </c>
+      <c r="L79" t="s">
+        <v>465</v>
+      </c>
+      <c r="M79" t="s">
+        <v>466</v>
+      </c>
+    </row>
+    <row r="80" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A80" t="s">
+        <v>467</v>
+      </c>
+      <c r="B80" t="s">
+        <v>468</v>
+      </c>
+      <c r="C80" t="s">
+        <v>15</v>
+      </c>
+      <c r="D80" t="s">
+        <v>469</v>
+      </c>
+      <c r="E80" t="s">
+        <v>458</v>
+      </c>
+      <c r="F80" t="s">
+        <v>18</v>
+      </c>
+      <c r="G80" t="s">
+        <v>19</v>
+      </c>
+      <c r="H80" t="s">
+        <v>20</v>
+      </c>
+      <c r="I80" t="s">
+        <v>21</v>
+      </c>
+      <c r="J80" t="s">
+        <v>37</v>
+      </c>
+      <c r="K80" t="s">
+        <v>23</v>
+      </c>
+      <c r="L80" t="s">
+        <v>470</v>
+      </c>
+      <c r="M80" t="s">
+        <v>471</v>
+      </c>
+    </row>
+    <row r="81" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A81" t="s">
+        <v>472</v>
+      </c>
+      <c r="B81" t="s">
+        <v>473</v>
+      </c>
+      <c r="C81" t="s">
+        <v>15</v>
+      </c>
+      <c r="D81" t="s">
+        <v>474</v>
+      </c>
+      <c r="E81" t="s">
+        <v>458</v>
+      </c>
+      <c r="F81" t="s">
+        <v>18</v>
+      </c>
+      <c r="G81" t="s">
+        <v>19</v>
+      </c>
+      <c r="H81" t="s">
+        <v>43</v>
+      </c>
+      <c r="I81" t="s">
+        <v>21</v>
+      </c>
+      <c r="J81" t="s">
+        <v>30</v>
+      </c>
+      <c r="K81" t="s">
+        <v>23</v>
+      </c>
+      <c r="L81" t="s">
+        <v>475</v>
+      </c>
+      <c r="M81" t="s">
+        <v>476</v>
+      </c>
+    </row>
+    <row r="82" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A82" t="s">
+        <v>477</v>
+      </c>
+      <c r="B82" t="s">
+        <v>478</v>
+      </c>
+      <c r="C82" t="s">
+        <v>304</v>
+      </c>
+      <c r="D82" t="s">
+        <v>479</v>
+      </c>
+      <c r="E82" t="s">
+        <v>458</v>
+      </c>
+      <c r="F82" t="s">
+        <v>18</v>
+      </c>
+      <c r="G82" t="s">
+        <v>19</v>
+      </c>
+      <c r="H82" t="s">
+        <v>72</v>
+      </c>
+      <c r="I82" t="s">
+        <v>21</v>
+      </c>
+      <c r="J82" t="s">
+        <v>30</v>
+      </c>
+      <c r="K82" t="s">
+        <v>23</v>
+      </c>
+      <c r="L82" t="s">
+        <v>480</v>
+      </c>
+      <c r="M82" t="s">
+        <v>481</v>
+      </c>
+    </row>
+    <row r="83" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A83" t="s">
+        <v>482</v>
+      </c>
+      <c r="B83" t="s">
+        <v>483</v>
+      </c>
+      <c r="C83" t="s">
+        <v>304</v>
+      </c>
+      <c r="D83" t="s">
+        <v>484</v>
+      </c>
+      <c r="E83" t="s">
+        <v>458</v>
+      </c>
+      <c r="F83" t="s">
+        <v>18</v>
+      </c>
+      <c r="G83" t="s">
+        <v>19</v>
+      </c>
+      <c r="H83" t="s">
+        <v>43</v>
+      </c>
+      <c r="I83" t="s">
+        <v>21</v>
+      </c>
+      <c r="J83" t="s">
+        <v>30</v>
+      </c>
+      <c r="K83" t="s">
+        <v>23</v>
+      </c>
+      <c r="L83" t="s">
+        <v>485</v>
+      </c>
+      <c r="M83" t="s">
+        <v>486</v>
+      </c>
+    </row>
+    <row r="84" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A84" t="s">
+        <v>487</v>
+      </c>
+      <c r="B84" t="s">
+        <v>488</v>
+      </c>
+      <c r="C84" t="s">
+        <v>15</v>
+      </c>
+      <c r="D84" t="s">
+        <v>489</v>
+      </c>
+      <c r="E84" t="s">
+        <v>458</v>
+      </c>
+      <c r="F84" t="s">
+        <v>18</v>
+      </c>
+      <c r="G84" t="s">
+        <v>19</v>
+      </c>
+      <c r="H84" t="s">
+        <v>65</v>
+      </c>
+      <c r="I84" t="s">
+        <v>66</v>
+      </c>
+      <c r="J84" t="s">
+        <v>65</v>
+      </c>
+      <c r="K84" t="s">
+        <v>23</v>
+      </c>
+      <c r="L84" t="s">
+        <v>490</v>
+      </c>
+      <c r="M84" t="s">
+        <v>491</v>
+      </c>
+    </row>
+    <row r="85" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A85" t="s">
+        <v>492</v>
+      </c>
+      <c r="B85" t="s">
+        <v>493</v>
+      </c>
+      <c r="C85" t="s">
+        <v>62</v>
+      </c>
+      <c r="D85" t="s">
+        <v>494</v>
+      </c>
+      <c r="E85" t="s">
+        <v>458</v>
+      </c>
+      <c r="F85" t="s">
+        <v>18</v>
+      </c>
+      <c r="G85" t="s">
+        <v>19</v>
+      </c>
+      <c r="H85" t="s">
+        <v>495</v>
+      </c>
+      <c r="I85" t="s">
+        <v>21</v>
+      </c>
+      <c r="J85" t="s">
+        <v>30</v>
+      </c>
+      <c r="K85" t="s">
+        <v>23</v>
+      </c>
+      <c r="L85" t="s">
+        <v>496</v>
+      </c>
+      <c r="M85" t="s">
+        <v>497</v>
+      </c>
+    </row>
+    <row r="86" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A86" t="s">
+        <v>498</v>
+      </c>
+      <c r="B86" t="s">
+        <v>499</v>
+      </c>
+      <c r="C86" t="s">
+        <v>15</v>
+      </c>
+      <c r="D86" t="s">
+        <v>500</v>
+      </c>
+      <c r="E86" t="s">
+        <v>458</v>
+      </c>
+      <c r="F86" t="s">
+        <v>18</v>
+      </c>
+      <c r="G86" t="s">
+        <v>19</v>
+      </c>
+      <c r="H86" t="s">
+        <v>244</v>
+      </c>
+      <c r="I86" t="s">
+        <v>21</v>
+      </c>
+      <c r="J86" t="s">
+        <v>65</v>
+      </c>
+      <c r="K86" t="s">
+        <v>23</v>
+      </c>
+      <c r="L86" t="s">
+        <v>501</v>
+      </c>
+      <c r="M86" t="s">
+        <v>502</v>
+      </c>
+    </row>
+    <row r="87" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A87" t="s">
+        <v>503</v>
+      </c>
+      <c r="B87" t="s">
+        <v>504</v>
+      </c>
+      <c r="C87" t="s">
+        <v>15</v>
+      </c>
+      <c r="D87" t="s">
+        <v>505</v>
+      </c>
+      <c r="E87" t="s">
+        <v>458</v>
+      </c>
+      <c r="F87" t="s">
+        <v>18</v>
+      </c>
+      <c r="G87" t="s">
+        <v>19</v>
+      </c>
+      <c r="H87" t="s">
+        <v>72</v>
+      </c>
+      <c r="I87" t="s">
+        <v>21</v>
+      </c>
+      <c r="J87" t="s">
+        <v>30</v>
+      </c>
+      <c r="K87" t="s">
+        <v>23</v>
+      </c>
+      <c r="L87" t="s">
+        <v>506</v>
+      </c>
+      <c r="M87" t="s">
+        <v>507</v>
+      </c>
+    </row>
+    <row r="88" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A88" t="s">
+        <v>508</v>
+      </c>
+      <c r="B88" t="s">
+        <v>509</v>
+      </c>
+      <c r="C88" t="s">
+        <v>15</v>
+      </c>
+      <c r="D88" t="s">
+        <v>510</v>
+      </c>
+      <c r="E88" t="s">
+        <v>458</v>
+      </c>
+      <c r="F88" t="s">
+        <v>18</v>
+      </c>
+      <c r="G88" t="s">
+        <v>19</v>
+      </c>
+      <c r="H88" t="s">
+        <v>511</v>
+      </c>
+      <c r="I88" t="s">
+        <v>21</v>
+      </c>
+      <c r="J88" t="s">
+        <v>65</v>
+      </c>
+      <c r="K88" t="s">
+        <v>23</v>
+      </c>
+      <c r="L88" t="s">
+        <v>512</v>
+      </c>
+      <c r="M88" t="s">
+        <v>513</v>
+      </c>
+    </row>
+    <row r="89" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A89" t="s">
+        <v>514</v>
+      </c>
+      <c r="B89" t="s">
+        <v>515</v>
+      </c>
+      <c r="C89" t="s">
+        <v>15</v>
+      </c>
+      <c r="D89" t="s">
+        <v>516</v>
+      </c>
+      <c r="E89" t="s">
+        <v>458</v>
+      </c>
+      <c r="F89" t="s">
+        <v>18</v>
+      </c>
+      <c r="G89" t="s">
+        <v>19</v>
+      </c>
+      <c r="H89" t="s">
+        <v>345</v>
+      </c>
+      <c r="I89" t="s">
+        <v>21</v>
+      </c>
+      <c r="J89" t="s">
+        <v>65</v>
+      </c>
+      <c r="K89" t="s">
+        <v>23</v>
+      </c>
+      <c r="L89" t="s">
+        <v>517</v>
+      </c>
+      <c r="M89" t="s">
+        <v>518</v>
+      </c>
+    </row>
+    <row r="90" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A90" t="s">
+        <v>519</v>
+      </c>
+      <c r="B90" t="s">
+        <v>520</v>
+      </c>
+      <c r="C90" t="s">
+        <v>15</v>
+      </c>
+      <c r="D90" t="s">
+        <v>521</v>
+      </c>
+      <c r="E90" t="s">
+        <v>458</v>
+      </c>
+      <c r="F90" t="s">
+        <v>18</v>
+      </c>
+      <c r="G90" t="s">
+        <v>19</v>
+      </c>
+      <c r="H90" t="s">
+        <v>65</v>
+      </c>
+      <c r="I90" t="s">
+        <v>66</v>
+      </c>
+      <c r="J90" t="s">
+        <v>65</v>
+      </c>
+      <c r="K90" t="s">
+        <v>23</v>
+      </c>
+      <c r="L90" t="s">
+        <v>522</v>
+      </c>
+      <c r="M90" t="s">
+        <v>523</v>
+      </c>
+    </row>
+    <row r="91" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A91" t="s">
+        <v>524</v>
+      </c>
+      <c r="B91" t="s">
+        <v>525</v>
+      </c>
+      <c r="C91" t="s">
+        <v>15</v>
+      </c>
+      <c r="D91" t="s">
+        <v>526</v>
+      </c>
+      <c r="E91" t="s">
+        <v>458</v>
+      </c>
+      <c r="F91" t="s">
+        <v>18</v>
+      </c>
+      <c r="G91" t="s">
+        <v>19</v>
+      </c>
+      <c r="H91" t="s">
+        <v>72</v>
+      </c>
+      <c r="I91" t="s">
+        <v>21</v>
+      </c>
+      <c r="J91" t="s">
+        <v>65</v>
+      </c>
+      <c r="K91" t="s">
+        <v>23</v>
+      </c>
+      <c r="L91" t="s">
+        <v>527</v>
+      </c>
+      <c r="M91" t="s">
+        <v>528</v>
+      </c>
+    </row>
+    <row r="92" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A92" t="s">
+        <v>529</v>
+      </c>
+      <c r="B92" t="s">
+        <v>530</v>
+      </c>
+      <c r="C92" t="s">
+        <v>15</v>
+      </c>
+      <c r="D92" t="s">
+        <v>531</v>
+      </c>
+      <c r="E92" t="s">
+        <v>458</v>
+      </c>
+      <c r="F92" t="s">
+        <v>18</v>
+      </c>
+      <c r="G92" t="s">
+        <v>19</v>
+      </c>
+      <c r="H92" t="s">
+        <v>72</v>
+      </c>
+      <c r="I92" t="s">
+        <v>21</v>
+      </c>
+      <c r="J92" t="s">
+        <v>65</v>
+      </c>
+      <c r="K92" t="s">
+        <v>23</v>
+      </c>
+      <c r="L92" t="s">
+        <v>532</v>
+      </c>
+      <c r="M92" t="s">
+        <v>533</v>
+      </c>
+    </row>
+    <row r="93" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A93" t="s">
+        <v>534</v>
+      </c>
+      <c r="B93" t="s">
+        <v>535</v>
+      </c>
+      <c r="C93" t="s">
+        <v>15</v>
+      </c>
+      <c r="D93" t="s">
+        <v>536</v>
+      </c>
+      <c r="E93" t="s">
+        <v>458</v>
+      </c>
+      <c r="F93" t="s">
+        <v>18</v>
+      </c>
+      <c r="G93" t="s">
+        <v>19</v>
+      </c>
+      <c r="H93" t="s">
+        <v>72</v>
+      </c>
+      <c r="I93" t="s">
+        <v>21</v>
+      </c>
+      <c r="J93" t="s">
+        <v>65</v>
+      </c>
+      <c r="K93" t="s">
+        <v>23</v>
+      </c>
+      <c r="L93" t="s">
+        <v>537</v>
+      </c>
+      <c r="M93" t="s">
+        <v>538</v>
+      </c>
+    </row>
+    <row r="94" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A94" t="s">
+        <v>539</v>
+      </c>
+      <c r="B94" t="s">
+        <v>540</v>
+      </c>
+      <c r="C94" t="s">
+        <v>15</v>
+      </c>
+      <c r="D94" t="s">
+        <v>541</v>
+      </c>
+      <c r="E94" t="s">
+        <v>458</v>
+      </c>
+      <c r="F94" t="s">
+        <v>18</v>
+      </c>
+      <c r="G94" t="s">
+        <v>19</v>
+      </c>
+      <c r="H94" t="s">
+        <v>542</v>
+      </c>
+      <c r="I94" t="s">
+        <v>21</v>
+      </c>
+      <c r="J94" t="s">
+        <v>65</v>
+      </c>
+      <c r="K94" t="s">
+        <v>23</v>
+      </c>
+      <c r="L94" t="s">
+        <v>543</v>
+      </c>
+      <c r="M94" t="s">
+        <v>544</v>
+      </c>
+    </row>
+    <row r="95" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A95" t="s">
+        <v>545</v>
+      </c>
+      <c r="B95" t="s">
+        <v>546</v>
+      </c>
+      <c r="C95" t="s">
+        <v>15</v>
+      </c>
+      <c r="D95" t="s">
+        <v>547</v>
+      </c>
+      <c r="E95" t="s">
+        <v>548</v>
+      </c>
+      <c r="F95" t="s">
+        <v>18</v>
+      </c>
+      <c r="G95" t="s">
+        <v>19</v>
+      </c>
+      <c r="H95" t="s">
+        <v>244</v>
+      </c>
+      <c r="I95" t="s">
+        <v>21</v>
+      </c>
+      <c r="J95" t="s">
+        <v>30</v>
+      </c>
+      <c r="K95" t="s">
+        <v>23</v>
+      </c>
+      <c r="L95" t="s">
+        <v>549</v>
+      </c>
+      <c r="M95" t="s">
+        <v>550</v>
+      </c>
+    </row>
+    <row r="96" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A96" t="s">
+        <v>551</v>
+      </c>
+      <c r="B96" t="s">
+        <v>552</v>
+      </c>
+      <c r="C96" t="s">
+        <v>15</v>
+      </c>
+      <c r="D96" t="s">
+        <v>553</v>
+      </c>
+      <c r="E96" t="s">
+        <v>458</v>
+      </c>
+      <c r="F96" t="s">
+        <v>18</v>
+      </c>
+      <c r="G96" t="s">
+        <v>19</v>
+      </c>
+      <c r="H96" t="s">
+        <v>554</v>
+      </c>
+      <c r="I96" t="s">
+        <v>21</v>
+      </c>
+      <c r="J96" t="s">
+        <v>65</v>
+      </c>
+      <c r="K96" t="s">
+        <v>23</v>
+      </c>
+      <c r="L96" t="s">
+        <v>555</v>
+      </c>
+      <c r="M96" t="s">
+        <v>556</v>
+      </c>
+    </row>
+    <row r="97" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A97" t="s">
+        <v>557</v>
+      </c>
+      <c r="B97" t="s">
+        <v>558</v>
+      </c>
+      <c r="C97" t="s">
+        <v>138</v>
+      </c>
+      <c r="D97" t="s">
+        <v>559</v>
+      </c>
+      <c r="E97" t="s">
+        <v>458</v>
+      </c>
+      <c r="F97" t="s">
+        <v>18</v>
+      </c>
+      <c r="G97" t="s">
+        <v>19</v>
+      </c>
+      <c r="H97" t="s">
+        <v>65</v>
+      </c>
+      <c r="I97" t="s">
+        <v>66</v>
+      </c>
+      <c r="J97" t="s">
+        <v>30</v>
+      </c>
+      <c r="K97" t="s">
+        <v>23</v>
+      </c>
+      <c r="L97" t="s">
+        <v>560</v>
+      </c>
+      <c r="M97" t="s">
+        <v>561</v>
+      </c>
+    </row>
+    <row r="98" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A98" t="s">
+        <v>562</v>
+      </c>
+      <c r="B98" t="s">
+        <v>563</v>
+      </c>
+      <c r="C98" t="s">
+        <v>15</v>
+      </c>
+      <c r="D98" t="s">
+        <v>564</v>
+      </c>
+      <c r="E98" t="s">
+        <v>565</v>
+      </c>
+      <c r="F98" t="s">
+        <v>18</v>
+      </c>
+      <c r="G98" t="s">
+        <v>19</v>
+      </c>
+      <c r="H98" t="s">
+        <v>72</v>
+      </c>
+      <c r="I98" t="s">
+        <v>21</v>
+      </c>
+      <c r="J98" t="s">
+        <v>145</v>
+      </c>
+      <c r="K98" t="s">
+        <v>23</v>
+      </c>
+      <c r="L98" t="s">
+        <v>566</v>
+      </c>
+      <c r="M98" t="s">
+        <v>567</v>
+      </c>
+    </row>
+    <row r="99" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A99" t="s">
+        <v>568</v>
+      </c>
+      <c r="B99" t="s">
+        <v>569</v>
+      </c>
+      <c r="C99" t="s">
+        <v>62</v>
+      </c>
+      <c r="D99" t="s">
+        <v>570</v>
+      </c>
+      <c r="E99" t="s">
+        <v>571</v>
+      </c>
+      <c r="F99" t="s">
+        <v>18</v>
+      </c>
+      <c r="G99" t="s">
+        <v>19</v>
+      </c>
+      <c r="H99" t="s">
+        <v>72</v>
+      </c>
+      <c r="I99" t="s">
+        <v>21</v>
+      </c>
+      <c r="J99" t="s">
+        <v>572</v>
+      </c>
+      <c r="K99" t="s">
+        <v>23</v>
+      </c>
+      <c r="L99" t="s">
+        <v>573</v>
+      </c>
+      <c r="M99" t="s">
+        <v>574</v>
+      </c>
+    </row>
+    <row r="100" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A100" t="s">
+        <v>575</v>
+      </c>
+      <c r="B100" t="s">
+        <v>576</v>
+      </c>
+      <c r="C100" t="s">
+        <v>577</v>
+      </c>
+      <c r="D100" t="s">
+        <v>578</v>
+      </c>
+      <c r="E100" t="s">
+        <v>571</v>
+      </c>
+      <c r="F100" t="s">
+        <v>18</v>
+      </c>
+      <c r="G100" t="s">
+        <v>19</v>
+      </c>
+      <c r="H100" t="s">
+        <v>72</v>
+      </c>
+      <c r="I100" t="s">
+        <v>579</v>
+      </c>
+      <c r="J100" t="s">
+        <v>580</v>
+      </c>
+      <c r="K100" t="s">
+        <v>23</v>
+      </c>
+      <c r="L100" t="s">
+        <v>581</v>
+      </c>
+      <c r="M100" t="s">
+        <v>582</v>
+      </c>
+    </row>
+    <row r="101" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A101" t="s">
+        <v>583</v>
+      </c>
+      <c r="B101" t="s">
+        <v>584</v>
+      </c>
+      <c r="C101" t="s">
+        <v>88</v>
+      </c>
+      <c r="D101" t="s">
+        <v>585</v>
+      </c>
+      <c r="E101" t="s">
+        <v>571</v>
+      </c>
+      <c r="F101" t="s">
+        <v>18</v>
+      </c>
+      <c r="G101" t="s">
+        <v>19</v>
+      </c>
+      <c r="H101" t="s">
+        <v>72</v>
+      </c>
+      <c r="I101" t="s">
+        <v>21</v>
+      </c>
+      <c r="J101" t="s">
+        <v>65</v>
+      </c>
+      <c r="K101" t="s">
+        <v>23</v>
+      </c>
+      <c r="L101" t="s">
+        <v>586</v>
+      </c>
+      <c r="M101" t="s">
+        <v>587</v>
+      </c>
+    </row>
+    <row r="102" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A102" t="s">
+        <v>588</v>
+      </c>
+      <c r="B102" t="s">
+        <v>589</v>
+      </c>
+      <c r="C102" t="s">
+        <v>590</v>
+      </c>
+      <c r="D102" t="s">
+        <v>591</v>
+      </c>
+      <c r="E102" t="s">
+        <v>458</v>
+      </c>
+      <c r="F102" t="s">
+        <v>18</v>
+      </c>
+      <c r="G102" t="s">
+        <v>19</v>
+      </c>
+      <c r="H102" t="s">
+        <v>65</v>
+      </c>
+      <c r="I102" t="s">
+        <v>66</v>
+      </c>
+      <c r="J102" t="s">
+        <v>65</v>
+      </c>
+      <c r="K102" t="s">
+        <v>23</v>
+      </c>
+      <c r="L102" t="s">
+        <v>592</v>
+      </c>
+      <c r="M102" t="s">
+        <v>593</v>
+      </c>
+    </row>
+    <row r="103" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A103" t="s">
+        <v>594</v>
+      </c>
+      <c r="B103" t="s">
+        <v>595</v>
+      </c>
+      <c r="C103" t="s">
+        <v>596</v>
+      </c>
+      <c r="D103" t="s">
+        <v>597</v>
+      </c>
+      <c r="E103" t="s">
+        <v>458</v>
+      </c>
+      <c r="F103" t="s">
+        <v>18</v>
+      </c>
+      <c r="G103" t="s">
+        <v>19</v>
+      </c>
+      <c r="H103" t="s">
+        <v>65</v>
+      </c>
+      <c r="I103" t="s">
+        <v>66</v>
+      </c>
+      <c r="J103" t="s">
+        <v>65</v>
+      </c>
+      <c r="K103" t="s">
+        <v>23</v>
+      </c>
+      <c r="L103" t="s">
+        <v>598</v>
+      </c>
+      <c r="M103" t="s">
+        <v>599</v>
+      </c>
+    </row>
+    <row r="104" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A104" t="s">
+        <v>600</v>
+      </c>
+      <c r="B104" t="s">
+        <v>601</v>
+      </c>
+      <c r="C104" t="s">
+        <v>15</v>
+      </c>
+      <c r="D104" t="s">
+        <v>602</v>
+      </c>
+      <c r="E104" t="s">
+        <v>458</v>
+      </c>
+      <c r="F104" t="s">
+        <v>18</v>
+      </c>
+      <c r="G104" t="s">
+        <v>19</v>
+      </c>
+      <c r="H104" t="s">
+        <v>65</v>
+      </c>
+      <c r="I104" t="s">
+        <v>66</v>
+      </c>
+      <c r="J104" t="s">
+        <v>65</v>
+      </c>
+      <c r="K104" t="s">
+        <v>23</v>
+      </c>
+      <c r="L104" t="s">
+        <v>603</v>
+      </c>
+      <c r="M104" t="s">
+        <v>604</v>
+      </c>
+    </row>
+    <row r="105" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A105" t="s">
+        <v>605</v>
+      </c>
+      <c r="B105" t="s">
+        <v>606</v>
+      </c>
+      <c r="C105" t="s">
+        <v>607</v>
+      </c>
+      <c r="D105" t="s">
+        <v>608</v>
+      </c>
+      <c r="E105" t="s">
+        <v>609</v>
+      </c>
+      <c r="F105" t="s">
+        <v>18</v>
+      </c>
+      <c r="G105" t="s">
+        <v>19</v>
+      </c>
+      <c r="H105" t="s">
+        <v>50</v>
+      </c>
+      <c r="I105" t="s">
+        <v>610</v>
+      </c>
+      <c r="J105" t="s">
+        <v>30</v>
+      </c>
+      <c r="K105" t="s">
+        <v>23</v>
+      </c>
+      <c r="L105" t="s">
+        <v>611</v>
+      </c>
+      <c r="M105" t="s">
+        <v>612</v>
+      </c>
+    </row>
+    <row r="106" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A106" t="s">
+        <v>613</v>
+      </c>
+      <c r="B106" t="s">
+        <v>614</v>
+      </c>
+      <c r="C106" t="s">
+        <v>15</v>
+      </c>
+      <c r="D106" t="s">
+        <v>615</v>
+      </c>
+      <c r="E106" t="s">
+        <v>609</v>
+      </c>
+      <c r="F106" t="s">
+        <v>18</v>
+      </c>
+      <c r="G106" t="s">
+        <v>19</v>
+      </c>
+      <c r="H106" t="s">
+        <v>36</v>
+      </c>
+      <c r="I106" t="s">
+        <v>21</v>
+      </c>
+      <c r="J106" t="s">
+        <v>258</v>
+      </c>
+      <c r="K106" t="s">
+        <v>23</v>
+      </c>
+      <c r="L106" t="s">
+        <v>616</v>
+      </c>
+      <c r="M106" t="s">
+        <v>617</v>
+      </c>
+    </row>
+    <row r="107" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A107" t="s">
+        <v>618</v>
+      </c>
+      <c r="B107" t="s">
+        <v>619</v>
+      </c>
+      <c r="C107" t="s">
+        <v>15</v>
+      </c>
+      <c r="D107" t="s">
+        <v>620</v>
+      </c>
+      <c r="E107" t="s">
+        <v>609</v>
+      </c>
+      <c r="F107" t="s">
+        <v>18</v>
+      </c>
+      <c r="G107" t="s">
+        <v>19</v>
+      </c>
+      <c r="H107" t="s">
+        <v>306</v>
+      </c>
+      <c r="I107" t="s">
+        <v>21</v>
+      </c>
+      <c r="J107" t="s">
+        <v>65</v>
+      </c>
+      <c r="K107" t="s">
+        <v>23</v>
+      </c>
+      <c r="L107" t="s">
+        <v>621</v>
+      </c>
+      <c r="M107" t="s">
+        <v>622</v>
+      </c>
+    </row>
+    <row r="108" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A108" t="s">
+        <v>623</v>
+      </c>
+      <c r="B108" t="s">
+        <v>624</v>
+      </c>
+      <c r="C108" t="s">
+        <v>15</v>
+      </c>
+      <c r="D108" t="s">
+        <v>625</v>
+      </c>
+      <c r="E108" t="s">
+        <v>609</v>
+      </c>
+      <c r="F108" t="s">
+        <v>18</v>
+      </c>
+      <c r="G108" t="s">
+        <v>19</v>
+      </c>
+      <c r="H108" t="s">
+        <v>65</v>
+      </c>
+      <c r="I108" t="s">
+        <v>66</v>
+      </c>
+      <c r="J108" t="s">
+        <v>65</v>
+      </c>
+      <c r="K108" t="s">
+        <v>23</v>
+      </c>
+      <c r="L108" t="s">
+        <v>626</v>
+      </c>
+      <c r="M108" t="s">
+        <v>627</v>
+      </c>
+    </row>
+    <row r="109" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A109" t="s">
+        <v>628</v>
+      </c>
+      <c r="B109" t="s">
+        <v>629</v>
+      </c>
+      <c r="C109" t="s">
+        <v>15</v>
+      </c>
+      <c r="D109" t="s">
+        <v>630</v>
+      </c>
+      <c r="E109" t="s">
+        <v>609</v>
+      </c>
+      <c r="F109" t="s">
+        <v>18</v>
+      </c>
+      <c r="G109" t="s">
+        <v>19</v>
+      </c>
+      <c r="H109" t="s">
+        <v>72</v>
+      </c>
+      <c r="I109" t="s">
+        <v>21</v>
+      </c>
+      <c r="J109" t="s">
+        <v>65</v>
+      </c>
+      <c r="K109" t="s">
+        <v>23</v>
+      </c>
+      <c r="L109" t="s">
+        <v>631</v>
+      </c>
+      <c r="M109" t="s">
+        <v>632</v>
+      </c>
+    </row>
+    <row r="110" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A110" t="s">
+        <v>633</v>
+      </c>
+      <c r="B110" t="s">
+        <v>634</v>
+      </c>
+      <c r="C110" t="s">
+        <v>15</v>
+      </c>
+      <c r="D110" t="s">
+        <v>635</v>
+      </c>
+      <c r="E110" t="s">
+        <v>609</v>
+      </c>
+      <c r="F110" t="s">
+        <v>18</v>
+      </c>
+      <c r="G110" t="s">
+        <v>19</v>
+      </c>
+      <c r="H110" t="s">
+        <v>65</v>
+      </c>
+      <c r="I110" t="s">
+        <v>66</v>
+      </c>
+      <c r="J110" t="s">
+        <v>65</v>
+      </c>
+      <c r="K110" t="s">
+        <v>23</v>
+      </c>
+      <c r="L110" t="s">
+        <v>636</v>
+      </c>
+      <c r="M110" t="s">
+        <v>637</v>
+      </c>
+    </row>
+    <row r="111" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A111" t="s">
+        <v>638</v>
+      </c>
+      <c r="B111" t="s">
+        <v>639</v>
+      </c>
+      <c r="C111" t="s">
+        <v>15</v>
+      </c>
+      <c r="D111" t="s">
+        <v>640</v>
+      </c>
+      <c r="E111" t="s">
+        <v>609</v>
+      </c>
+      <c r="F111" t="s">
+        <v>18</v>
+      </c>
+      <c r="G111" t="s">
+        <v>19</v>
+      </c>
+      <c r="H111" t="s">
+        <v>65</v>
+      </c>
+      <c r="I111" t="s">
+        <v>66</v>
+      </c>
+      <c r="J111" t="s">
+        <v>65</v>
+      </c>
+      <c r="K111" t="s">
+        <v>23</v>
+      </c>
+      <c r="L111" t="s">
+        <v>641</v>
+      </c>
+      <c r="M111" t="s">
+        <v>642</v>
+      </c>
+    </row>
+    <row r="112" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A112" t="s">
+        <v>643</v>
+      </c>
+      <c r="B112" t="s">
+        <v>644</v>
+      </c>
+      <c r="C112" t="s">
+        <v>15</v>
+      </c>
+      <c r="D112" t="s">
+        <v>645</v>
+      </c>
+      <c r="E112" t="s">
+        <v>609</v>
+      </c>
+      <c r="F112" t="s">
+        <v>18</v>
+      </c>
+      <c r="G112" t="s">
+        <v>19</v>
+      </c>
+      <c r="H112" t="s">
+        <v>72</v>
+      </c>
+      <c r="I112" t="s">
+        <v>21</v>
+      </c>
+      <c r="J112" t="s">
+        <v>65</v>
+      </c>
+      <c r="K112" t="s">
+        <v>23</v>
+      </c>
+      <c r="L112" t="s">
+        <v>646</v>
+      </c>
+      <c r="M112" t="s">
+        <v>647</v>
+      </c>
+    </row>
+    <row r="113" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A113" t="s">
+        <v>648</v>
+      </c>
+      <c r="B113" t="s">
+        <v>649</v>
+      </c>
+      <c r="C113" t="s">
+        <v>15</v>
+      </c>
+      <c r="D113" t="s">
+        <v>650</v>
+      </c>
+      <c r="E113" t="s">
+        <v>609</v>
+      </c>
+      <c r="F113" t="s">
+        <v>18</v>
+      </c>
+      <c r="G113" t="s">
+        <v>19</v>
+      </c>
+      <c r="H113" t="s">
+        <v>651</v>
+      </c>
+      <c r="I113" t="s">
+        <v>21</v>
+      </c>
+      <c r="J113" t="s">
+        <v>65</v>
+      </c>
+      <c r="K113" t="s">
+        <v>23</v>
+      </c>
+      <c r="L113" t="s">
+        <v>652</v>
+      </c>
+      <c r="M113" t="s">
+        <v>653</v>
+      </c>
+    </row>
+    <row r="114" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A114" t="s">
+        <v>654</v>
+      </c>
+      <c r="B114" t="s">
+        <v>655</v>
+      </c>
+      <c r="C114" t="s">
+        <v>15</v>
+      </c>
+      <c r="D114" t="s">
+        <v>656</v>
+      </c>
+      <c r="E114" t="s">
+        <v>609</v>
+      </c>
+      <c r="F114" t="s">
+        <v>18</v>
+      </c>
+      <c r="G114" t="s">
+        <v>19</v>
+      </c>
+      <c r="H114" t="s">
+        <v>65</v>
+      </c>
+      <c r="I114" t="s">
+        <v>66</v>
+      </c>
+      <c r="J114" t="s">
+        <v>65</v>
+      </c>
+      <c r="K114" t="s">
+        <v>23</v>
+      </c>
+      <c r="L114" t="s">
+        <v>657</v>
+      </c>
+      <c r="M114" t="s">
+        <v>658</v>
+      </c>
+    </row>
+    <row r="115" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A115" t="s">
+        <v>659</v>
+      </c>
+      <c r="B115" t="s">
+        <v>660</v>
+      </c>
+      <c r="C115" t="s">
+        <v>15</v>
+      </c>
+      <c r="D115" t="s">
+        <v>661</v>
+      </c>
+      <c r="E115" t="s">
+        <v>609</v>
+      </c>
+      <c r="F115" t="s">
+        <v>18</v>
+      </c>
+      <c r="G115" t="s">
+        <v>19</v>
+      </c>
+      <c r="H115" t="s">
+        <v>43</v>
+      </c>
+      <c r="I115" t="s">
+        <v>21</v>
+      </c>
+      <c r="J115" t="s">
+        <v>44</v>
+      </c>
+      <c r="K115" t="s">
+        <v>23</v>
+      </c>
+      <c r="L115" t="s">
+        <v>662</v>
+      </c>
+      <c r="M115" t="s">
+        <v>663</v>
+      </c>
+    </row>
+    <row r="116" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A116" t="s">
+        <v>664</v>
+      </c>
+      <c r="B116" t="s">
+        <v>665</v>
+      </c>
+      <c r="C116" t="s">
+        <v>62</v>
+      </c>
+      <c r="D116" t="s">
+        <v>666</v>
+      </c>
+      <c r="E116" t="s">
+        <v>667</v>
+      </c>
+      <c r="F116" t="s">
+        <v>18</v>
+      </c>
+      <c r="G116" t="s">
+        <v>19</v>
+      </c>
+      <c r="H116" t="s">
+        <v>542</v>
+      </c>
+      <c r="I116" t="s">
+        <v>21</v>
+      </c>
+      <c r="J116" t="s">
+        <v>30</v>
+      </c>
+      <c r="K116" t="s">
+        <v>23</v>
+      </c>
+      <c r="L116" t="s">
+        <v>668</v>
+      </c>
+      <c r="M116" t="s">
+        <v>669</v>
+      </c>
+    </row>
+    <row r="117" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A117" t="s">
+        <v>670</v>
+      </c>
+      <c r="B117" t="s">
+        <v>671</v>
+      </c>
+      <c r="C117" t="s">
+        <v>15</v>
+      </c>
+      <c r="D117" t="s">
+        <v>672</v>
+      </c>
+      <c r="E117" t="s">
+        <v>673</v>
+      </c>
+      <c r="F117" t="s">
+        <v>18</v>
+      </c>
+      <c r="G117" t="s">
+        <v>19</v>
+      </c>
+      <c r="H117" t="s">
+        <v>674</v>
+      </c>
+      <c r="I117" t="s">
+        <v>21</v>
+      </c>
+      <c r="J117" t="s">
+        <v>51</v>
+      </c>
+      <c r="K117" t="s">
+        <v>23</v>
+      </c>
+      <c r="L117" t="s">
+        <v>675</v>
+      </c>
+      <c r="M117" t="s">
+        <v>676</v>
+      </c>
+    </row>
+    <row r="118" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A118" t="s">
+        <v>677</v>
+      </c>
+      <c r="B118" t="s">
+        <v>678</v>
+      </c>
+      <c r="C118" t="s">
+        <v>56</v>
+      </c>
+      <c r="D118" t="s">
+        <v>679</v>
+      </c>
+      <c r="E118" t="s">
+        <v>667</v>
+      </c>
+      <c r="F118" t="s">
+        <v>18</v>
+      </c>
+      <c r="G118" t="s">
+        <v>19</v>
+      </c>
+      <c r="H118" t="s">
+        <v>72</v>
+      </c>
+      <c r="I118" t="s">
+        <v>21</v>
+      </c>
+      <c r="J118" t="s">
+        <v>65</v>
+      </c>
+      <c r="K118" t="s">
+        <v>23</v>
+      </c>
+      <c r="L118" t="s">
+        <v>680</v>
+      </c>
+      <c r="M118" t="s">
+        <v>681</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/Sajjad data/by_country_and_state/USA/TX.xlsx
+++ b/Sajjad data/by_country_and_state/USA/TX.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1534" uniqueCount="682">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2080" uniqueCount="906">
   <si>
     <t>Business Name</t>
   </si>
@@ -2057,6 +2057,678 @@
   </si>
   <si>
     <t>2026-10-24T19:45:47.933Z</t>
+  </si>
+  <si>
+    <t>Dentist Help Now</t>
+  </si>
+  <si>
+    <t>(254) 831-0246</t>
+  </si>
+  <si>
+    <t>1701 Austin Ave ste.a, Waco, TX 76701</t>
+  </si>
+  <si>
+    <t>Waco</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dentist+Help+Now/data=!4m7!3m6!1s0x864f831e0f5cfb11:0x39e66356f36b62d8!8m2!3d31.5471224!4d-97.1431601!16s%2Fg%2F11zwvqj174!19sChIJEftcDx6DT4YR2GJr81Zj5jk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:19:17.359Z</t>
+  </si>
+  <si>
+    <t>Vance Jack F DDS</t>
+  </si>
+  <si>
+    <t>(254) 754-1972</t>
+  </si>
+  <si>
+    <t>1111 N 18th St, Waco, TX 76707</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Vance+Jack+F+DDS/data=!4m7!3m6!1s0x864f83a35d338355:0x5863ce5d968d382b!8m2!3d31.5550378!4d-97.1526788!16s%2Fg%2F1tgns206!19sChIJVYMzXaODT4YRKziNll3OY1g?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:19:26.087Z</t>
+  </si>
+  <si>
+    <t>Mark W. Wingate, D.D.S.</t>
+  </si>
+  <si>
+    <t>(254) 772-0180</t>
+  </si>
+  <si>
+    <t>5001 Lakewood Dr, Waco, TX 76710</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Mark+W.+Wingate,+D.D.S./data=!4m7!3m6!1s0x864f84126566d983:0x84aff3ebfe19997a!8m2!3d31.5367089!4d-97.1904506!16s%2Fg%2F1vj5_mg_!19sChIJg9lmZRKET4YRepkZ_uvzr4Q?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:19:28.453Z</t>
+  </si>
+  <si>
+    <t>Dr. Zachary Schwab</t>
+  </si>
+  <si>
+    <t>(254) 776-5727</t>
+  </si>
+  <si>
+    <t>6400 Cobbs Dr Ste 800, Waco, TX 76710</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Zachary+Schwab/data=!4m7!3m6!1s0x864f843cfd4de7ff:0x2cbf4d21458688e4!8m2!3d31.5303366!4d-97.2033022!16s%2Fg%2F11rwxg575_!19sChIJ_-dN_TyET4YR5IiGRSFNvyw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:19:41.848Z</t>
+  </si>
+  <si>
+    <t>Central Texas ImplantCenter</t>
+  </si>
+  <si>
+    <t>(254) 751-1171</t>
+  </si>
+  <si>
+    <t>7030 New Sanger Ave Suite 100, Waco, TX 76712</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Central+Texas+ImplantCenter/data=!4m7!3m6!1s0x864f869fa7eaef8d:0xea9602039a40928c!8m2!3d31.5135033!4d-97.2026038!16s%2Fg%2F1tkp061q!19sChIJje_qp5-GT4YRjJJAmgMCluo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:20:13.732Z</t>
+  </si>
+  <si>
+    <t>Dr. Travis Hildebrand</t>
+  </si>
+  <si>
+    <t>(254) 523-4550</t>
+  </si>
+  <si>
+    <t>1601 Walton Dr, Waco, TX 76705</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Travis+Hildebrand/data=!4m7!3m6!1s0x864f82b00c56c9af:0x1b32430ee0fdcc4b!8m2!3d31.6023607!4d-97.1048169!16s%2Fg%2F11k3_k3q5t!19sChIJr8lWDLCCT4YRS8z94A5DMhs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:20:29.851Z</t>
+  </si>
+  <si>
+    <t>Charles Weathers, D.D.S, M.S.D Orthodontics</t>
+  </si>
+  <si>
+    <t>(254) 776-0318</t>
+  </si>
+  <si>
+    <t>5016 Lakeland Cir Ste A, Waco, TX 76710</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Charles+Weathers,+D.D.S,+M.S.D+Orthodontics/data=!4m7!3m6!1s0x864f84126009cc73:0x9444cccfc409d711!8m2!3d31.5370648!4d-97.1911836!16s%2Fg%2F1v4ptdt2!19sChIJc8wJYBKET4YREdcJxM_MRJQ?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:20:45.850Z</t>
+  </si>
+  <si>
+    <t>Michael Collins</t>
+  </si>
+  <si>
+    <t>(254) 772-5933</t>
+  </si>
+  <si>
+    <t>8400 Old McGregor Rd, Waco, TX 76712</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Michael+Collins/data=!4m7!3m6!1s0x864f868e757c8c81:0xaa34c3472169b246!8m2!3d31.4993154!4d-97.2128597!16s%2Fg%2F11sh29zg80!19sChIJgYx8dY6GT4YRRrJpIUfDNKo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:20:48.217Z</t>
+  </si>
+  <si>
+    <t>Dr. Lisa Kerns</t>
+  </si>
+  <si>
+    <t>(254) 399-9800</t>
+  </si>
+  <si>
+    <t>5156 W Waco Dr, Waco, TX 76710</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Lisa+Kerns/data=!4m7!3m6!1s0x864f84003b2c9cf5:0xc16359a2e9f66d81!8m2!3d31.5188807!4d-97.1808312!16s%2Fg%2F11tn6l2t_z!19sChIJ9ZwsOwCET4YRgW326aJZY8E?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:20:51.259Z</t>
+  </si>
+  <si>
+    <t>Jill F. Michaels, D.D.S.</t>
+  </si>
+  <si>
+    <t>(254) 772-0373</t>
+  </si>
+  <si>
+    <t>331 W Hwy 6 Ste G, Waco, TX 76710</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Jill+F.+Michaels,+D.D.S./data=!4m7!3m6!1s0x864f86a0b0fa6533:0x7787c278c4937d40!8m2!3d31.5163585!4d-97.1958239!16s%2Fg%2F1tdky2dj!19sChIJM2X6sKCGT4YRQH2TxHjCh3c?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:20:54.830Z</t>
+  </si>
+  <si>
+    <t>Best Choice Denture Implants and Repair</t>
+  </si>
+  <si>
+    <t>(254) 475-1005</t>
+  </si>
+  <si>
+    <t>3312 Hillcrest Dr, Waco, TX 76708</t>
+  </si>
+  <si>
+    <t>43</t>
+  </si>
+  <si>
+    <t>SaturdayClosed; SundayClosed; Monday9 AM–5 PM; Tuesday9 AM–5 PM; Wednesday9 AM–5 PM; Thursday9 AM–5 PM; Friday9 AM–5 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Best+Choice+Denture+Implants+and+Repair/data=!4m7!3m6!1s0x864f83d261f0cb5b:0xb3e7ac57f4853202!8m2!3d31.5569308!4d-97.1778354!16s%2Fg%2F11j_747w00!19sChIJW8vwYdKDT4YRAjKF9Fes57M?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:21:23.026Z</t>
+  </si>
+  <si>
+    <t>Dream Gleam by Roxxi</t>
+  </si>
+  <si>
+    <t>(254) 436-3831</t>
+  </si>
+  <si>
+    <t>3708 W Waco Dr #3, Waco, TX 76710</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dream+Gleam+by+Roxxi/data=!4m7!3m6!1s0x864f83b70c767565:0x283f394450444a56!8m2!3d31.5330958!4d-97.1648756!16s%2Fg%2F11q823n8vv!19sChIJZXV2DLeDT4YRVkpEUEQ5Pyg?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:22:11.478Z</t>
+  </si>
+  <si>
+    <t>Community Clinic</t>
+  </si>
+  <si>
+    <t>(940) 387-5788</t>
+  </si>
+  <si>
+    <t>Non-profit organization</t>
+  </si>
+  <si>
+    <t>4310 Mesa Dr, Denton, TX 76207</t>
+  </si>
+  <si>
+    <t>Denton</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Community+Clinic/data=!4m7!3m6!1s0x864db5fe45334f75:0xe5f53417be721a7b!8m2!3d33.2350314!4d-97.1770452!16s%2Fg%2F1thw2k3d!19sChIJdU8zRf61TYYRexpyvhc09eU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:22:33.112Z</t>
+  </si>
+  <si>
+    <t>1st Smile Dental</t>
+  </si>
+  <si>
+    <t>(940) 483-1599</t>
+  </si>
+  <si>
+    <t>1800 Brinker Rd, Denton, TX 76208</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/1st+Smile+Dental/data=!4m7!3m6!1s0x864dcb2a7aae46f9:0x419cfc6093b3d206!8m2!3d33.1906817!4d-97.0962041!16s%2Fg%2F11ddwt_xh4!19sChIJ-UaueirLTYYRBtKzk2D8nEE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:22:35.604Z</t>
+  </si>
+  <si>
+    <t>Peter Huynh, DDS PC</t>
+  </si>
+  <si>
+    <t>(940) 591-1195</t>
+  </si>
+  <si>
+    <t>1912 N Carroll Blvd, Denton, TX 76201</t>
+  </si>
+  <si>
+    <t>3.6</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Peter+Huynh,+DDS+PC/data=!4m7!3m6!1s0x864c2cec08094fd1:0xbebd7774915c9865!8m2!3d33.2316667!4d-97.1366118!16s%2Fg%2F1tltmsdd!19sChIJ0U8JCOwsTIYRZZhckXR3vb4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:22:39.038Z</t>
+  </si>
+  <si>
+    <t>Mc Cracken Todd DDS</t>
+  </si>
+  <si>
+    <t>(940) 891-0663</t>
+  </si>
+  <si>
+    <t>2215 S Loop 288, Denton, TX 76205</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Mc+Cracken+Todd+DDS/data=!4m7!3m6!1s0x864dcb27b574485f:0x2143050564b91717!8m2!3d33.1870819!4d-97.1059521!16s%2Fg%2F1tglzc_q!19sChIJX0h0tSfLTYYRFxe5ZAUFQyE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:25:35.817Z</t>
+  </si>
+  <si>
+    <t>Lake Cities Pediatric Dentistry and Orthodontics</t>
+  </si>
+  <si>
+    <t>(940) 353-5437</t>
+  </si>
+  <si>
+    <t>3502 Corinth Pkwy Ste 400, Corinth, TX 76208</t>
+  </si>
+  <si>
+    <t>Corinth</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Lake+Cities+Pediatric+Dentistry+and+Orthodontics/data=!4m7!3m6!1s0x864c357ffc4b8dc3:0x5d04d30858bef2b7!8m2!3d33.1529397!4d-97.0547549!16s%2Fg%2F11fs16z0_s!19sChIJw41L_H81TIYRt_K-WAjTBF0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:25:42.448Z</t>
+  </si>
+  <si>
+    <t>Jones Hamilton L DDS</t>
+  </si>
+  <si>
+    <t>(940) 387-0823</t>
+  </si>
+  <si>
+    <t>1212 Bent Oaks Ct Ste 100, Denton, TX 76210</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Jones+Hamilton+L+DDS/data=!4m7!3m6!1s0x864dcb3e5065e1a3:0x208a30d75338bf55!8m2!3d33.1714515!4d-97.1123274!16s%2Fg%2F1tdmkwzp!19sChIJo-FlUD7LTYYRVb84U9cwiiA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:25:45.030Z</t>
+  </si>
+  <si>
+    <t>Yvette Dye</t>
+  </si>
+  <si>
+    <t>(940) 380-9050</t>
+  </si>
+  <si>
+    <t>2548 Lillian Miller Pkwy #120, Denton, TX 76210</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Yvette+Dye/data=!4m7!3m6!1s0x864dcb239e39d6ed:0x40fad4378028c4d4!8m2!3d33.182235!4d-97.1100254!16s%2Fg%2F1tdrfs49!19sChIJ7dY5niPLTYYR1MQogDfU-kA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:25:49.938Z</t>
+  </si>
+  <si>
+    <t>Kool Smiles</t>
+  </si>
+  <si>
+    <t>(866) 227-0727</t>
+  </si>
+  <si>
+    <t>2903 50th St, Lubbock, TX 79413</t>
+  </si>
+  <si>
+    <t>Lubbock</t>
+  </si>
+  <si>
+    <t>Saturday6 AM–11 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Kool+Smiles/data=!4m7!3m6!1s0x86fe6d656877c1d7:0xab5ac3c4e080ad29!8m2!3d33.5477391!4d-101.878463!16s%2Fg%2F1tdbfwjy!19sChIJ18F3aGVt_oYRKa2A4MTDWqs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:28:56.060Z</t>
+  </si>
+  <si>
+    <t>Dr. Dietmar A. Kennel, DDS</t>
+  </si>
+  <si>
+    <t>(806) 749-5437</t>
+  </si>
+  <si>
+    <t>1504 Buddy Holly Ave, Lubbock, TX 79401</t>
+  </si>
+  <si>
+    <t>3.2</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Dietmar+A.+Kennel,+DDS/data=!4m7!3m6!1s0x86fe6d2abedd70cd:0x2ac48a505d9f71d5!8m2!3d33.5814144!4d-101.8446642!16s%2Fg%2F1v6p992x!19sChIJzXDdvipt_oYR1XGfXVCKxCo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:30:50.587Z</t>
+  </si>
+  <si>
+    <t>South Plains Pediatric Dental</t>
+  </si>
+  <si>
+    <t>(806) 783-9309</t>
+  </si>
+  <si>
+    <t>4601 50th St, Lubbock, TX 79414</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/South+Plains+Pediatric+Dental/data=!4m7!3m6!1s0x86fe72936f9013d1:0xa276eafe58b653a4!8m2!3d33.5480228!4d-101.9099634!16s%2Fg%2F1tf1c5zl!19sChIJ0ROQb5Ny_oYRpFO2WP7qdqI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:30:53.514Z</t>
+  </si>
+  <si>
+    <t>Dental Emergency Access</t>
+  </si>
+  <si>
+    <t>(806) 666-3127</t>
+  </si>
+  <si>
+    <t>1107 Main St, Lubbock, TX 79401</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+Emergency+Access/data=!4m7!3m6!1s0x86fe138d011d2e19:0x6d0db07f68ebbdd7!8m2!3d33.5853768!4d-101.8472214!16s%2Fg%2F11zz9_0fzt!19sChIJGS4dAY0T_oYR173raH-wDW0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:31:56.752Z</t>
+  </si>
+  <si>
+    <t>Urgent Dental Guide</t>
+  </si>
+  <si>
+    <t>(806) 240-9730</t>
+  </si>
+  <si>
+    <t>3209 34th St, Lubbock, TX 79410</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Urgent+Dental+Guide/data=!4m7!3m6!1s0x86fe6dd12665f245:0x400cc60a00a68c!8m2!3d33.5630257!4d-101.8843634!16s%2Fg%2F11zzfy8r0y!19sChIJRfJlJtFt_oYRjKYACsYMQAA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:32:01.618Z</t>
+  </si>
+  <si>
+    <t>Dental Emergency Exchange /Michael S. Luce DDS</t>
+  </si>
+  <si>
+    <t>(361) 993-3211</t>
+  </si>
+  <si>
+    <t>2033 Airline Rd Ste h-5, Corpus Christi, TX 78412</t>
+  </si>
+  <si>
+    <t>Corpus Christi</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+Emergency+Exchange+%2FMichael+S.+Luce+DDS/data=!4m7!3m6!1s0x8668f5cf8d24d911:0x4ec8052e43e088a7!8m2!3d27.6934593!4d-97.3638821!16s%2Fg%2F11c5bjzv5w!19sChIJEdkkjc_1aIYRp4jgQy4FyE4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:33:23.067Z</t>
+  </si>
+  <si>
+    <t>Western Affordable Dental.</t>
+  </si>
+  <si>
+    <t>(361) 271-0297</t>
+  </si>
+  <si>
+    <t>210 N Carancahua St, Corpus Christi, TX 78401</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Western+Affordable+Dental./data=!4m7!3m6!1s0x86685e58d47f894d:0x596a7247c75828c!8m2!3d27.7911599!4d-97.397295!16s%2Fg%2F11dx8njqtf!19sChIJTYl_1FheaIYRjIJ1fCSnlgU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:33:25.767Z</t>
+  </si>
+  <si>
+    <t>Sabal Dentistry Clinic</t>
+  </si>
+  <si>
+    <t>(361) 991-8743</t>
+  </si>
+  <si>
+    <t>5426 Holly Rd, Corpus Christi, TX 78411</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Sabal+Dentistry+Clinic/data=!4m7!3m6!1s0x8668f5c206118607:0x7a55ca8eea2b8965!8m2!3d27.7001708!4d-97.3779538!16s%2Fg%2F11kqcnmbpv!19sChIJB4YRBsL1aIYRZYkr6o7KVXo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:33:30.918Z</t>
+  </si>
+  <si>
+    <t>O2 Dental</t>
+  </si>
+  <si>
+    <t>(361) 937-8333</t>
+  </si>
+  <si>
+    <t>9929 S Padre Island Dr #119, Corpus Christi, TX 78418</t>
+  </si>
+  <si>
+    <t>Saturday8:30 AM–2 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/O2+Dental/data=!4m7!3m6!1s0x8668f740d3392f19:0x125f9e300894d37f!8m2!3d27.6716174!4d-97.290579!16s%2Fg%2F11ry1yhmtf!19sChIJGS8500D3aIYRf9OUCDCeXxI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:33:33.993Z</t>
+  </si>
+  <si>
+    <t>Dr. Russell D. Borth, DDS</t>
+  </si>
+  <si>
+    <t>(361) 994-5414</t>
+  </si>
+  <si>
+    <t>5756 S Staples St Ste B, Corpus Christi, TX 78413</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Russell+D.+Borth,+DDS/data=!4m7!3m6!1s0x8668f5b90ffb3171:0xc7980e9234c3f732!8m2!3d27.6966831!4d-97.3763489!16s%2Fg%2F1trqhndq!19sChIJcTH7D7n1aIYRMvfDNJIOmMc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:35:10.073Z</t>
+  </si>
+  <si>
+    <t>TMJ &amp; Facial Pain Center: Curtis, David W. DDS</t>
+  </si>
+  <si>
+    <t>(361) 992-1441</t>
+  </si>
+  <si>
+    <t>5525 S Staples St a4, Corpus Christi, TX 78411</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/TMJ+%26+Facial+Pain+Center:+Curtis,+David+W.+DDS/data=!4m7!3m6!1s0x8668f5b9ca099ba5:0x79f81c458895623e!8m2!3d27.7007057!4d-97.3751766!16s%2Fg%2F1tgm38_7!19sChIJpZsJyrn1aIYRPmKViEUc-Hk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:35:17.444Z</t>
+  </si>
+  <si>
+    <t>Felipe Juarez, DMD- Family Dentistry</t>
+  </si>
+  <si>
+    <t>(361) 241-6622</t>
+  </si>
+  <si>
+    <t>9922 Leopard St Ste 210, Corpus Christi, TX 78410</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Felipe+Juarez,+DMD-+Family+Dentistry/data=!4m7!3m6!1s0x8668638020097083:0x3bb21f995376fdae!8m2!3d27.8331763!4d-97.5621668!16s%2Fg%2F1tj858cf!19sChIJg3AJIIBjaIYRrv12U5kfsjs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:35:47.112Z</t>
+  </si>
+  <si>
+    <t>An Elegante Dental Care</t>
+  </si>
+  <si>
+    <t>(361) 850-8000</t>
+  </si>
+  <si>
+    <t>4117 S Staples St #300, Corpus Christi, TX 78411</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/An+Elegante+Dental+Care/data=!4m7!3m6!1s0x8668f589b46e9059:0x25425e7fdde0514c!8m2!3d27.7264105!4d-97.381665!16s%2Fg%2F11f15p04r0!19sChIJWZButIn1aIYRTFHg3X9eQiU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:36:34.314Z</t>
+  </si>
+  <si>
+    <t>Paul A Kennedy Jr Inc</t>
+  </si>
+  <si>
+    <t>(361) 992-9500</t>
+  </si>
+  <si>
+    <t>6200 Saratoga Blvd Bldg 1, Corpus Christi, TX 78414</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Paul+A+Kennedy+Jr+Inc/data=!4m7!3m6!1s0x8668f4356f76cca7:0x67b4140277fdcb7e!8m2!3d27.6797773!4d-97.371486!16s%2Fg%2F1hc908nny!19sChIJp8x2bzX0aIYRfsv9dwIUtGc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:36:36.933Z</t>
+  </si>
+  <si>
+    <t>Lee Overstreet DDS</t>
+  </si>
+  <si>
+    <t>(361) 991-5911</t>
+  </si>
+  <si>
+    <t>5525 S Staples St A-1, Corpus Christi, TX 25411</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Lee+Overstreet+DDS/data=!4m7!3m6!1s0x8668f5bf3e9ade23:0x42a6bf67bfdd1064!8m2!3d27.7008244!4d-97.3753456!16s%2Fg%2F1td8zk9b!19sChIJI96aPr_1aIYRZBDdv2e_pkI?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:36:39.597Z</t>
+  </si>
+  <si>
+    <t>Saratoga Dental Center</t>
+  </si>
+  <si>
+    <t>(361) 200-2458</t>
+  </si>
+  <si>
+    <t>6410 Weber Rd #6, Corpus Christi, TX 78413</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Saratoga+Dental+Center/data=!4m7!3m6!1s0x8668f5147894081b:0xb998bb0396c900e8!8m2!3d27.7001809!4d-97.4111305!16s%2Fg%2F1tdnlkbd!19sChIJGwiUeBT1aIYR6ADJlgO7mLk?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:36:42.280Z</t>
+  </si>
+  <si>
+    <t>Cynthia Casillas DDS</t>
+  </si>
+  <si>
+    <t>(361) 855-1521</t>
+  </si>
+  <si>
+    <t>5756 S Staples St, Corpus Christi, TX 78413</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Cynthia+Casillas+DDS/data=!4m7!3m6!1s0x86688bde30e65ff5:0x735a228ba0657fb9!8m2!3d27.6961597!4d-97.3755008!16s%2Fg%2F11c0vlhm31!19sChIJ9V_mMN6LaIYRuX9loIsiWnM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:36:44.855Z</t>
+  </si>
+  <si>
+    <t>Dr. Roxanne G. Robertson, DDS</t>
+  </si>
+  <si>
+    <t>(361) 992-2483</t>
+  </si>
+  <si>
+    <t>4750 S Padre Island Dr #101, Corpus Christi, TX 78411</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Roxanne+G.+Robertson,+DDS/data=!4m7!3m6!1s0x8668f59ab375bad7:0xe17ad9ace4598c00!8m2!3d27.716179!4d-97.384944!16s%2Fg%2F1tr9nvs2!19sChIJ17p1s5r1aIYRAIxZ5KzZeuE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:36:59.747Z</t>
+  </si>
+  <si>
+    <t>Ronald D. Ferrell, DDS</t>
+  </si>
+  <si>
+    <t>(361) 853-0439</t>
+  </si>
+  <si>
+    <t>4949 Everhart Rd #105, Corpus Christi, TX 78411</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Ronald+D.+Ferrell,+DDS/data=!4m7!3m6!1s0x8668f58555821d63:0x413eb4c4affa76a3!8m2!3d27.7174544!4d-97.3827302!16s%2Fg%2F1tmxx0bc!19sChIJYx2CVYX1aIYRo3b6r8S0PkE?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:37:04.380Z</t>
+  </si>
+  <si>
+    <t>Dr. Haysam Dawod, DDS</t>
+  </si>
+  <si>
+    <t>(361) 200-2457</t>
+  </si>
+  <si>
+    <t>4514 S Staples St, Corpus Christi, TX 78412</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Haysam+Dawod,+DDS/data=!4m7!3m6!1s0x8668f58d4cc480e1:0xcb88859dd4873b15!8m2!3d27.717526!4d-97.3727033!16s%2Fg%2F113f43pyv!19sChIJ4YDETI31aIYRFTuH1J2FiMs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:37:06.564Z</t>
+  </si>
+  <si>
+    <t>DentNow</t>
+  </si>
+  <si>
+    <t>(361) 223-0210</t>
+  </si>
+  <si>
+    <t>13725 Northwest Blvd Ste 225, Corpus Christi, TX 78410</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/DentNow/data=!4m7!3m6!1s0x86687bced7ccdaa9:0x90040e7a4b9e3260!8m2!3d27.8551928!4d-97.6358551!16s%2Fg%2F11zxcjzk95!19sChIJqdrM1857aIYRYDKeS3oOBJA?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:37:24.582Z</t>
+  </si>
+  <si>
+    <t>UrgentDent</t>
+  </si>
+  <si>
+    <t>(361) 246-1195</t>
+  </si>
+  <si>
+    <t>5155 Flynn Pkwy ste 541, Corpus Christi, TX 78411</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/UrgentDent/data=!4m7!3m6!1s0x8668f53528ed1093:0x7b47567bd06c6835!8m2!3d27.7157199!4d-97.3934863!16s%2Fg%2F11zxcjs6r3!19sChIJkxDtKDX1aIYRNWhs0HtWR3s?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:37:27.612Z</t>
+  </si>
+  <si>
+    <t>Dr. Robert K. Hood, DDS</t>
+  </si>
+  <si>
+    <t>(361) 853-6161</t>
+  </si>
+  <si>
+    <t>5756 S Staples St a3, Corpus Christi, TX 78413</t>
+  </si>
+  <si>
+    <t>19</t>
+  </si>
+  <si>
+    <t>SaturdayClosed; SundayClosed; Monday8 AM–5 PM; Tuesday8 AM–5 PM; Wednesday8 AM–5 PM; Thursday8 AM–5 PM; Friday9 AM–3 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Robert+K.+Hood,+DDS/data=!4m7!3m6!1s0x8668f513447959af:0x7b65f0fb090487a!8m2!3d27.6965001!4d-97.3764854!16s%2Fg%2F1tdkh25f!19sChIJr1l5RBP1aIYRekiQsA9ftgc?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-24T22:38:26.693Z</t>
   </si>
 </sst>
 </file>
@@ -2437,7 +3109,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M118"/>
+  <dimension ref="A1:M160"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -7292,6 +7964,1728 @@
         <v>681</v>
       </c>
     </row>
+    <row r="119" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A119" t="s">
+        <v>682</v>
+      </c>
+      <c r="B119" t="s">
+        <v>683</v>
+      </c>
+      <c r="C119" t="s">
+        <v>88</v>
+      </c>
+      <c r="D119" t="s">
+        <v>684</v>
+      </c>
+      <c r="E119" t="s">
+        <v>685</v>
+      </c>
+      <c r="F119" t="s">
+        <v>18</v>
+      </c>
+      <c r="G119" t="s">
+        <v>19</v>
+      </c>
+      <c r="H119" t="s">
+        <v>72</v>
+      </c>
+      <c r="I119" t="s">
+        <v>21</v>
+      </c>
+      <c r="J119" t="s">
+        <v>65</v>
+      </c>
+      <c r="K119" t="s">
+        <v>23</v>
+      </c>
+      <c r="L119" t="s">
+        <v>686</v>
+      </c>
+      <c r="M119" t="s">
+        <v>687</v>
+      </c>
+    </row>
+    <row r="120" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A120" t="s">
+        <v>688</v>
+      </c>
+      <c r="B120" t="s">
+        <v>689</v>
+      </c>
+      <c r="C120" t="s">
+        <v>15</v>
+      </c>
+      <c r="D120" t="s">
+        <v>690</v>
+      </c>
+      <c r="E120" t="s">
+        <v>685</v>
+      </c>
+      <c r="F120" t="s">
+        <v>18</v>
+      </c>
+      <c r="G120" t="s">
+        <v>19</v>
+      </c>
+      <c r="H120" t="s">
+        <v>72</v>
+      </c>
+      <c r="I120" t="s">
+        <v>21</v>
+      </c>
+      <c r="J120" t="s">
+        <v>65</v>
+      </c>
+      <c r="K120" t="s">
+        <v>23</v>
+      </c>
+      <c r="L120" t="s">
+        <v>691</v>
+      </c>
+      <c r="M120" t="s">
+        <v>692</v>
+      </c>
+    </row>
+    <row r="121" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A121" t="s">
+        <v>693</v>
+      </c>
+      <c r="B121" t="s">
+        <v>694</v>
+      </c>
+      <c r="C121" t="s">
+        <v>15</v>
+      </c>
+      <c r="D121" t="s">
+        <v>695</v>
+      </c>
+      <c r="E121" t="s">
+        <v>685</v>
+      </c>
+      <c r="F121" t="s">
+        <v>18</v>
+      </c>
+      <c r="G121" t="s">
+        <v>19</v>
+      </c>
+      <c r="H121" t="s">
+        <v>72</v>
+      </c>
+      <c r="I121" t="s">
+        <v>21</v>
+      </c>
+      <c r="J121" t="s">
+        <v>30</v>
+      </c>
+      <c r="K121" t="s">
+        <v>23</v>
+      </c>
+      <c r="L121" t="s">
+        <v>696</v>
+      </c>
+      <c r="M121" t="s">
+        <v>697</v>
+      </c>
+    </row>
+    <row r="122" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A122" t="s">
+        <v>698</v>
+      </c>
+      <c r="B122" t="s">
+        <v>699</v>
+      </c>
+      <c r="C122" t="s">
+        <v>15</v>
+      </c>
+      <c r="D122" t="s">
+        <v>700</v>
+      </c>
+      <c r="E122" t="s">
+        <v>685</v>
+      </c>
+      <c r="F122" t="s">
+        <v>18</v>
+      </c>
+      <c r="G122" t="s">
+        <v>19</v>
+      </c>
+      <c r="H122" t="s">
+        <v>65</v>
+      </c>
+      <c r="I122" t="s">
+        <v>66</v>
+      </c>
+      <c r="J122" t="s">
+        <v>65</v>
+      </c>
+      <c r="K122" t="s">
+        <v>23</v>
+      </c>
+      <c r="L122" t="s">
+        <v>701</v>
+      </c>
+      <c r="M122" t="s">
+        <v>702</v>
+      </c>
+    </row>
+    <row r="123" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A123" t="s">
+        <v>703</v>
+      </c>
+      <c r="B123" t="s">
+        <v>704</v>
+      </c>
+      <c r="C123" t="s">
+        <v>15</v>
+      </c>
+      <c r="D123" t="s">
+        <v>705</v>
+      </c>
+      <c r="E123" t="s">
+        <v>685</v>
+      </c>
+      <c r="F123" t="s">
+        <v>18</v>
+      </c>
+      <c r="G123" t="s">
+        <v>19</v>
+      </c>
+      <c r="H123" t="s">
+        <v>72</v>
+      </c>
+      <c r="I123" t="s">
+        <v>21</v>
+      </c>
+      <c r="J123" t="s">
+        <v>30</v>
+      </c>
+      <c r="K123" t="s">
+        <v>23</v>
+      </c>
+      <c r="L123" t="s">
+        <v>706</v>
+      </c>
+      <c r="M123" t="s">
+        <v>707</v>
+      </c>
+    </row>
+    <row r="124" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A124" t="s">
+        <v>708</v>
+      </c>
+      <c r="B124" t="s">
+        <v>709</v>
+      </c>
+      <c r="C124" t="s">
+        <v>333</v>
+      </c>
+      <c r="D124" t="s">
+        <v>710</v>
+      </c>
+      <c r="E124" t="s">
+        <v>685</v>
+      </c>
+      <c r="F124" t="s">
+        <v>18</v>
+      </c>
+      <c r="G124" t="s">
+        <v>19</v>
+      </c>
+      <c r="H124" t="s">
+        <v>65</v>
+      </c>
+      <c r="I124" t="s">
+        <v>66</v>
+      </c>
+      <c r="J124" t="s">
+        <v>65</v>
+      </c>
+      <c r="K124" t="s">
+        <v>23</v>
+      </c>
+      <c r="L124" t="s">
+        <v>711</v>
+      </c>
+      <c r="M124" t="s">
+        <v>712</v>
+      </c>
+    </row>
+    <row r="125" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A125" t="s">
+        <v>713</v>
+      </c>
+      <c r="B125" t="s">
+        <v>714</v>
+      </c>
+      <c r="C125" t="s">
+        <v>138</v>
+      </c>
+      <c r="D125" t="s">
+        <v>715</v>
+      </c>
+      <c r="E125" t="s">
+        <v>685</v>
+      </c>
+      <c r="F125" t="s">
+        <v>18</v>
+      </c>
+      <c r="G125" t="s">
+        <v>19</v>
+      </c>
+      <c r="H125" t="s">
+        <v>72</v>
+      </c>
+      <c r="I125" t="s">
+        <v>21</v>
+      </c>
+      <c r="J125" t="s">
+        <v>65</v>
+      </c>
+      <c r="K125" t="s">
+        <v>23</v>
+      </c>
+      <c r="L125" t="s">
+        <v>716</v>
+      </c>
+      <c r="M125" t="s">
+        <v>717</v>
+      </c>
+    </row>
+    <row r="126" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A126" t="s">
+        <v>718</v>
+      </c>
+      <c r="B126" t="s">
+        <v>719</v>
+      </c>
+      <c r="C126" t="s">
+        <v>138</v>
+      </c>
+      <c r="D126" t="s">
+        <v>720</v>
+      </c>
+      <c r="E126" t="s">
+        <v>685</v>
+      </c>
+      <c r="F126" t="s">
+        <v>18</v>
+      </c>
+      <c r="G126" t="s">
+        <v>19</v>
+      </c>
+      <c r="H126" t="s">
+        <v>72</v>
+      </c>
+      <c r="I126" t="s">
+        <v>21</v>
+      </c>
+      <c r="J126" t="s">
+        <v>65</v>
+      </c>
+      <c r="K126" t="s">
+        <v>23</v>
+      </c>
+      <c r="L126" t="s">
+        <v>721</v>
+      </c>
+      <c r="M126" t="s">
+        <v>722</v>
+      </c>
+    </row>
+    <row r="127" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A127" t="s">
+        <v>723</v>
+      </c>
+      <c r="B127" t="s">
+        <v>724</v>
+      </c>
+      <c r="C127" t="s">
+        <v>138</v>
+      </c>
+      <c r="D127" t="s">
+        <v>725</v>
+      </c>
+      <c r="E127" t="s">
+        <v>685</v>
+      </c>
+      <c r="F127" t="s">
+        <v>18</v>
+      </c>
+      <c r="G127" t="s">
+        <v>19</v>
+      </c>
+      <c r="H127" t="s">
+        <v>72</v>
+      </c>
+      <c r="I127" t="s">
+        <v>21</v>
+      </c>
+      <c r="J127" t="s">
+        <v>65</v>
+      </c>
+      <c r="K127" t="s">
+        <v>23</v>
+      </c>
+      <c r="L127" t="s">
+        <v>726</v>
+      </c>
+      <c r="M127" t="s">
+        <v>727</v>
+      </c>
+    </row>
+    <row r="128" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A128" t="s">
+        <v>728</v>
+      </c>
+      <c r="B128" t="s">
+        <v>729</v>
+      </c>
+      <c r="C128" t="s">
+        <v>15</v>
+      </c>
+      <c r="D128" t="s">
+        <v>730</v>
+      </c>
+      <c r="E128" t="s">
+        <v>685</v>
+      </c>
+      <c r="F128" t="s">
+        <v>18</v>
+      </c>
+      <c r="G128" t="s">
+        <v>19</v>
+      </c>
+      <c r="H128" t="s">
+        <v>72</v>
+      </c>
+      <c r="I128" t="s">
+        <v>21</v>
+      </c>
+      <c r="J128" t="s">
+        <v>30</v>
+      </c>
+      <c r="K128" t="s">
+        <v>23</v>
+      </c>
+      <c r="L128" t="s">
+        <v>731</v>
+      </c>
+      <c r="M128" t="s">
+        <v>732</v>
+      </c>
+    </row>
+    <row r="129" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A129" t="s">
+        <v>733</v>
+      </c>
+      <c r="B129" t="s">
+        <v>734</v>
+      </c>
+      <c r="C129" t="s">
+        <v>417</v>
+      </c>
+      <c r="D129" t="s">
+        <v>735</v>
+      </c>
+      <c r="E129" t="s">
+        <v>685</v>
+      </c>
+      <c r="F129" t="s">
+        <v>18</v>
+      </c>
+      <c r="G129" t="s">
+        <v>19</v>
+      </c>
+      <c r="H129" t="s">
+        <v>65</v>
+      </c>
+      <c r="I129" t="s">
+        <v>736</v>
+      </c>
+      <c r="J129" t="s">
+        <v>737</v>
+      </c>
+      <c r="K129" t="s">
+        <v>23</v>
+      </c>
+      <c r="L129" t="s">
+        <v>738</v>
+      </c>
+      <c r="M129" t="s">
+        <v>739</v>
+      </c>
+    </row>
+    <row r="130" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A130" t="s">
+        <v>740</v>
+      </c>
+      <c r="B130" t="s">
+        <v>741</v>
+      </c>
+      <c r="C130" t="s">
+        <v>171</v>
+      </c>
+      <c r="D130" t="s">
+        <v>742</v>
+      </c>
+      <c r="E130" t="s">
+        <v>685</v>
+      </c>
+      <c r="F130" t="s">
+        <v>18</v>
+      </c>
+      <c r="G130" t="s">
+        <v>19</v>
+      </c>
+      <c r="H130" t="s">
+        <v>72</v>
+      </c>
+      <c r="I130" t="s">
+        <v>21</v>
+      </c>
+      <c r="J130" t="s">
+        <v>65</v>
+      </c>
+      <c r="K130" t="s">
+        <v>23</v>
+      </c>
+      <c r="L130" t="s">
+        <v>743</v>
+      </c>
+      <c r="M130" t="s">
+        <v>744</v>
+      </c>
+    </row>
+    <row r="131" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A131" t="s">
+        <v>745</v>
+      </c>
+      <c r="B131" t="s">
+        <v>746</v>
+      </c>
+      <c r="C131" t="s">
+        <v>747</v>
+      </c>
+      <c r="D131" t="s">
+        <v>748</v>
+      </c>
+      <c r="E131" t="s">
+        <v>749</v>
+      </c>
+      <c r="F131" t="s">
+        <v>18</v>
+      </c>
+      <c r="G131" t="s">
+        <v>19</v>
+      </c>
+      <c r="H131" t="s">
+        <v>72</v>
+      </c>
+      <c r="I131" t="s">
+        <v>21</v>
+      </c>
+      <c r="J131" t="s">
+        <v>65</v>
+      </c>
+      <c r="K131" t="s">
+        <v>23</v>
+      </c>
+      <c r="L131" t="s">
+        <v>750</v>
+      </c>
+      <c r="M131" t="s">
+        <v>751</v>
+      </c>
+    </row>
+    <row r="132" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A132" t="s">
+        <v>752</v>
+      </c>
+      <c r="B132" t="s">
+        <v>753</v>
+      </c>
+      <c r="C132" t="s">
+        <v>62</v>
+      </c>
+      <c r="D132" t="s">
+        <v>754</v>
+      </c>
+      <c r="E132" t="s">
+        <v>749</v>
+      </c>
+      <c r="F132" t="s">
+        <v>18</v>
+      </c>
+      <c r="G132" t="s">
+        <v>19</v>
+      </c>
+      <c r="H132" t="s">
+        <v>65</v>
+      </c>
+      <c r="I132" t="s">
+        <v>66</v>
+      </c>
+      <c r="J132" t="s">
+        <v>65</v>
+      </c>
+      <c r="K132" t="s">
+        <v>23</v>
+      </c>
+      <c r="L132" t="s">
+        <v>755</v>
+      </c>
+      <c r="M132" t="s">
+        <v>756</v>
+      </c>
+    </row>
+    <row r="133" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A133" t="s">
+        <v>757</v>
+      </c>
+      <c r="B133" t="s">
+        <v>758</v>
+      </c>
+      <c r="C133" t="s">
+        <v>15</v>
+      </c>
+      <c r="D133" t="s">
+        <v>759</v>
+      </c>
+      <c r="E133" t="s">
+        <v>749</v>
+      </c>
+      <c r="F133" t="s">
+        <v>18</v>
+      </c>
+      <c r="G133" t="s">
+        <v>19</v>
+      </c>
+      <c r="H133" t="s">
+        <v>760</v>
+      </c>
+      <c r="I133" t="s">
+        <v>21</v>
+      </c>
+      <c r="J133" t="s">
+        <v>30</v>
+      </c>
+      <c r="K133" t="s">
+        <v>23</v>
+      </c>
+      <c r="L133" t="s">
+        <v>761</v>
+      </c>
+      <c r="M133" t="s">
+        <v>762</v>
+      </c>
+    </row>
+    <row r="134" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A134" t="s">
+        <v>763</v>
+      </c>
+      <c r="B134" t="s">
+        <v>764</v>
+      </c>
+      <c r="C134" t="s">
+        <v>15</v>
+      </c>
+      <c r="D134" t="s">
+        <v>765</v>
+      </c>
+      <c r="E134" t="s">
+        <v>749</v>
+      </c>
+      <c r="F134" t="s">
+        <v>18</v>
+      </c>
+      <c r="G134" t="s">
+        <v>19</v>
+      </c>
+      <c r="H134" t="s">
+        <v>128</v>
+      </c>
+      <c r="I134" t="s">
+        <v>21</v>
+      </c>
+      <c r="J134" t="s">
+        <v>65</v>
+      </c>
+      <c r="K134" t="s">
+        <v>23</v>
+      </c>
+      <c r="L134" t="s">
+        <v>766</v>
+      </c>
+      <c r="M134" t="s">
+        <v>767</v>
+      </c>
+    </row>
+    <row r="135" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A135" t="s">
+        <v>768</v>
+      </c>
+      <c r="B135" t="s">
+        <v>769</v>
+      </c>
+      <c r="C135" t="s">
+        <v>333</v>
+      </c>
+      <c r="D135" t="s">
+        <v>770</v>
+      </c>
+      <c r="E135" t="s">
+        <v>771</v>
+      </c>
+      <c r="F135" t="s">
+        <v>18</v>
+      </c>
+      <c r="G135" t="s">
+        <v>19</v>
+      </c>
+      <c r="H135" t="s">
+        <v>72</v>
+      </c>
+      <c r="I135" t="s">
+        <v>21</v>
+      </c>
+      <c r="J135" t="s">
+        <v>30</v>
+      </c>
+      <c r="K135" t="s">
+        <v>23</v>
+      </c>
+      <c r="L135" t="s">
+        <v>772</v>
+      </c>
+      <c r="M135" t="s">
+        <v>773</v>
+      </c>
+    </row>
+    <row r="136" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A136" t="s">
+        <v>774</v>
+      </c>
+      <c r="B136" t="s">
+        <v>775</v>
+      </c>
+      <c r="C136" t="s">
+        <v>333</v>
+      </c>
+      <c r="D136" t="s">
+        <v>776</v>
+      </c>
+      <c r="E136" t="s">
+        <v>749</v>
+      </c>
+      <c r="F136" t="s">
+        <v>18</v>
+      </c>
+      <c r="G136" t="s">
+        <v>19</v>
+      </c>
+      <c r="H136" t="s">
+        <v>495</v>
+      </c>
+      <c r="I136" t="s">
+        <v>21</v>
+      </c>
+      <c r="J136" t="s">
+        <v>65</v>
+      </c>
+      <c r="K136" t="s">
+        <v>23</v>
+      </c>
+      <c r="L136" t="s">
+        <v>777</v>
+      </c>
+      <c r="M136" t="s">
+        <v>778</v>
+      </c>
+    </row>
+    <row r="137" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A137" t="s">
+        <v>779</v>
+      </c>
+      <c r="B137" t="s">
+        <v>780</v>
+      </c>
+      <c r="C137" t="s">
+        <v>333</v>
+      </c>
+      <c r="D137" t="s">
+        <v>781</v>
+      </c>
+      <c r="E137" t="s">
+        <v>749</v>
+      </c>
+      <c r="F137" t="s">
+        <v>18</v>
+      </c>
+      <c r="G137" t="s">
+        <v>19</v>
+      </c>
+      <c r="H137" t="s">
+        <v>72</v>
+      </c>
+      <c r="I137" t="s">
+        <v>21</v>
+      </c>
+      <c r="J137" t="s">
+        <v>65</v>
+      </c>
+      <c r="K137" t="s">
+        <v>23</v>
+      </c>
+      <c r="L137" t="s">
+        <v>782</v>
+      </c>
+      <c r="M137" t="s">
+        <v>783</v>
+      </c>
+    </row>
+    <row r="138" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A138" t="s">
+        <v>784</v>
+      </c>
+      <c r="B138" t="s">
+        <v>785</v>
+      </c>
+      <c r="C138" t="s">
+        <v>15</v>
+      </c>
+      <c r="D138" t="s">
+        <v>786</v>
+      </c>
+      <c r="E138" t="s">
+        <v>787</v>
+      </c>
+      <c r="F138" t="s">
+        <v>18</v>
+      </c>
+      <c r="G138" t="s">
+        <v>19</v>
+      </c>
+      <c r="H138" t="s">
+        <v>250</v>
+      </c>
+      <c r="I138" t="s">
+        <v>21</v>
+      </c>
+      <c r="J138" t="s">
+        <v>788</v>
+      </c>
+      <c r="K138" t="s">
+        <v>23</v>
+      </c>
+      <c r="L138" t="s">
+        <v>789</v>
+      </c>
+      <c r="M138" t="s">
+        <v>790</v>
+      </c>
+    </row>
+    <row r="139" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A139" t="s">
+        <v>791</v>
+      </c>
+      <c r="B139" t="s">
+        <v>792</v>
+      </c>
+      <c r="C139" t="s">
+        <v>333</v>
+      </c>
+      <c r="D139" t="s">
+        <v>793</v>
+      </c>
+      <c r="E139" t="s">
+        <v>787</v>
+      </c>
+      <c r="F139" t="s">
+        <v>18</v>
+      </c>
+      <c r="G139" t="s">
+        <v>19</v>
+      </c>
+      <c r="H139" t="s">
+        <v>794</v>
+      </c>
+      <c r="I139" t="s">
+        <v>21</v>
+      </c>
+      <c r="J139" t="s">
+        <v>30</v>
+      </c>
+      <c r="K139" t="s">
+        <v>23</v>
+      </c>
+      <c r="L139" t="s">
+        <v>795</v>
+      </c>
+      <c r="M139" t="s">
+        <v>796</v>
+      </c>
+    </row>
+    <row r="140" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A140" t="s">
+        <v>797</v>
+      </c>
+      <c r="B140" t="s">
+        <v>798</v>
+      </c>
+      <c r="C140" t="s">
+        <v>333</v>
+      </c>
+      <c r="D140" t="s">
+        <v>799</v>
+      </c>
+      <c r="E140" t="s">
+        <v>787</v>
+      </c>
+      <c r="F140" t="s">
+        <v>18</v>
+      </c>
+      <c r="G140" t="s">
+        <v>19</v>
+      </c>
+      <c r="H140" t="s">
+        <v>65</v>
+      </c>
+      <c r="I140" t="s">
+        <v>66</v>
+      </c>
+      <c r="J140" t="s">
+        <v>65</v>
+      </c>
+      <c r="K140" t="s">
+        <v>23</v>
+      </c>
+      <c r="L140" t="s">
+        <v>800</v>
+      </c>
+      <c r="M140" t="s">
+        <v>801</v>
+      </c>
+    </row>
+    <row r="141" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A141" t="s">
+        <v>802</v>
+      </c>
+      <c r="B141" t="s">
+        <v>803</v>
+      </c>
+      <c r="C141" t="s">
+        <v>88</v>
+      </c>
+      <c r="D141" t="s">
+        <v>804</v>
+      </c>
+      <c r="E141" t="s">
+        <v>787</v>
+      </c>
+      <c r="F141" t="s">
+        <v>18</v>
+      </c>
+      <c r="G141" t="s">
+        <v>19</v>
+      </c>
+      <c r="H141" t="s">
+        <v>65</v>
+      </c>
+      <c r="I141" t="s">
+        <v>66</v>
+      </c>
+      <c r="J141" t="s">
+        <v>65</v>
+      </c>
+      <c r="K141" t="s">
+        <v>23</v>
+      </c>
+      <c r="L141" t="s">
+        <v>805</v>
+      </c>
+      <c r="M141" t="s">
+        <v>806</v>
+      </c>
+    </row>
+    <row r="142" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A142" t="s">
+        <v>807</v>
+      </c>
+      <c r="B142" t="s">
+        <v>808</v>
+      </c>
+      <c r="C142" t="s">
+        <v>88</v>
+      </c>
+      <c r="D142" t="s">
+        <v>809</v>
+      </c>
+      <c r="E142" t="s">
+        <v>787</v>
+      </c>
+      <c r="F142" t="s">
+        <v>18</v>
+      </c>
+      <c r="G142" t="s">
+        <v>19</v>
+      </c>
+      <c r="H142" t="s">
+        <v>65</v>
+      </c>
+      <c r="I142" t="s">
+        <v>66</v>
+      </c>
+      <c r="J142" t="s">
+        <v>65</v>
+      </c>
+      <c r="K142" t="s">
+        <v>23</v>
+      </c>
+      <c r="L142" t="s">
+        <v>810</v>
+      </c>
+      <c r="M142" t="s">
+        <v>811</v>
+      </c>
+    </row>
+    <row r="143" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A143" t="s">
+        <v>812</v>
+      </c>
+      <c r="B143" t="s">
+        <v>813</v>
+      </c>
+      <c r="C143" t="s">
+        <v>15</v>
+      </c>
+      <c r="D143" t="s">
+        <v>814</v>
+      </c>
+      <c r="E143" t="s">
+        <v>815</v>
+      </c>
+      <c r="F143" t="s">
+        <v>18</v>
+      </c>
+      <c r="G143" t="s">
+        <v>19</v>
+      </c>
+      <c r="H143" t="s">
+        <v>36</v>
+      </c>
+      <c r="I143" t="s">
+        <v>21</v>
+      </c>
+      <c r="J143" t="s">
+        <v>51</v>
+      </c>
+      <c r="K143" t="s">
+        <v>23</v>
+      </c>
+      <c r="L143" t="s">
+        <v>816</v>
+      </c>
+      <c r="M143" t="s">
+        <v>817</v>
+      </c>
+    </row>
+    <row r="144" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A144" t="s">
+        <v>818</v>
+      </c>
+      <c r="B144" t="s">
+        <v>819</v>
+      </c>
+      <c r="C144" t="s">
+        <v>62</v>
+      </c>
+      <c r="D144" t="s">
+        <v>820</v>
+      </c>
+      <c r="E144" t="s">
+        <v>815</v>
+      </c>
+      <c r="F144" t="s">
+        <v>18</v>
+      </c>
+      <c r="G144" t="s">
+        <v>19</v>
+      </c>
+      <c r="H144" t="s">
+        <v>345</v>
+      </c>
+      <c r="I144" t="s">
+        <v>21</v>
+      </c>
+      <c r="J144" t="s">
+        <v>51</v>
+      </c>
+      <c r="K144" t="s">
+        <v>23</v>
+      </c>
+      <c r="L144" t="s">
+        <v>821</v>
+      </c>
+      <c r="M144" t="s">
+        <v>822</v>
+      </c>
+    </row>
+    <row r="145" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A145" t="s">
+        <v>823</v>
+      </c>
+      <c r="B145" t="s">
+        <v>824</v>
+      </c>
+      <c r="C145" t="s">
+        <v>15</v>
+      </c>
+      <c r="D145" t="s">
+        <v>825</v>
+      </c>
+      <c r="E145" t="s">
+        <v>815</v>
+      </c>
+      <c r="F145" t="s">
+        <v>18</v>
+      </c>
+      <c r="G145" t="s">
+        <v>19</v>
+      </c>
+      <c r="H145" t="s">
+        <v>29</v>
+      </c>
+      <c r="I145" t="s">
+        <v>21</v>
+      </c>
+      <c r="J145" t="s">
+        <v>51</v>
+      </c>
+      <c r="K145" t="s">
+        <v>23</v>
+      </c>
+      <c r="L145" t="s">
+        <v>826</v>
+      </c>
+      <c r="M145" t="s">
+        <v>827</v>
+      </c>
+    </row>
+    <row r="146" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A146" t="s">
+        <v>828</v>
+      </c>
+      <c r="B146" t="s">
+        <v>829</v>
+      </c>
+      <c r="C146" t="s">
+        <v>15</v>
+      </c>
+      <c r="D146" t="s">
+        <v>830</v>
+      </c>
+      <c r="E146" t="s">
+        <v>815</v>
+      </c>
+      <c r="F146" t="s">
+        <v>18</v>
+      </c>
+      <c r="G146" t="s">
+        <v>19</v>
+      </c>
+      <c r="H146" t="s">
+        <v>29</v>
+      </c>
+      <c r="I146" t="s">
+        <v>21</v>
+      </c>
+      <c r="J146" t="s">
+        <v>831</v>
+      </c>
+      <c r="K146" t="s">
+        <v>23</v>
+      </c>
+      <c r="L146" t="s">
+        <v>832</v>
+      </c>
+      <c r="M146" t="s">
+        <v>833</v>
+      </c>
+    </row>
+    <row r="147" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A147" t="s">
+        <v>834</v>
+      </c>
+      <c r="B147" t="s">
+        <v>835</v>
+      </c>
+      <c r="C147" t="s">
+        <v>15</v>
+      </c>
+      <c r="D147" t="s">
+        <v>836</v>
+      </c>
+      <c r="E147" t="s">
+        <v>815</v>
+      </c>
+      <c r="F147" t="s">
+        <v>18</v>
+      </c>
+      <c r="G147" t="s">
+        <v>19</v>
+      </c>
+      <c r="H147" t="s">
+        <v>20</v>
+      </c>
+      <c r="I147" t="s">
+        <v>21</v>
+      </c>
+      <c r="J147" t="s">
+        <v>30</v>
+      </c>
+      <c r="K147" t="s">
+        <v>23</v>
+      </c>
+      <c r="L147" t="s">
+        <v>837</v>
+      </c>
+      <c r="M147" t="s">
+        <v>838</v>
+      </c>
+    </row>
+    <row r="148" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A148" t="s">
+        <v>839</v>
+      </c>
+      <c r="B148" t="s">
+        <v>840</v>
+      </c>
+      <c r="C148" t="s">
+        <v>15</v>
+      </c>
+      <c r="D148" t="s">
+        <v>841</v>
+      </c>
+      <c r="E148" t="s">
+        <v>815</v>
+      </c>
+      <c r="F148" t="s">
+        <v>18</v>
+      </c>
+      <c r="G148" t="s">
+        <v>19</v>
+      </c>
+      <c r="H148" t="s">
+        <v>20</v>
+      </c>
+      <c r="I148" t="s">
+        <v>21</v>
+      </c>
+      <c r="J148" t="s">
+        <v>30</v>
+      </c>
+      <c r="K148" t="s">
+        <v>23</v>
+      </c>
+      <c r="L148" t="s">
+        <v>842</v>
+      </c>
+      <c r="M148" t="s">
+        <v>843</v>
+      </c>
+    </row>
+    <row r="149" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A149" t="s">
+        <v>844</v>
+      </c>
+      <c r="B149" t="s">
+        <v>845</v>
+      </c>
+      <c r="C149" t="s">
+        <v>15</v>
+      </c>
+      <c r="D149" t="s">
+        <v>846</v>
+      </c>
+      <c r="E149" t="s">
+        <v>815</v>
+      </c>
+      <c r="F149" t="s">
+        <v>18</v>
+      </c>
+      <c r="G149" t="s">
+        <v>19</v>
+      </c>
+      <c r="H149" t="s">
+        <v>20</v>
+      </c>
+      <c r="I149" t="s">
+        <v>21</v>
+      </c>
+      <c r="J149" t="s">
+        <v>30</v>
+      </c>
+      <c r="K149" t="s">
+        <v>23</v>
+      </c>
+      <c r="L149" t="s">
+        <v>847</v>
+      </c>
+      <c r="M149" t="s">
+        <v>848</v>
+      </c>
+    </row>
+    <row r="150" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A150" t="s">
+        <v>849</v>
+      </c>
+      <c r="B150" t="s">
+        <v>850</v>
+      </c>
+      <c r="C150" t="s">
+        <v>333</v>
+      </c>
+      <c r="D150" t="s">
+        <v>851</v>
+      </c>
+      <c r="E150" t="s">
+        <v>815</v>
+      </c>
+      <c r="F150" t="s">
+        <v>18</v>
+      </c>
+      <c r="G150" t="s">
+        <v>19</v>
+      </c>
+      <c r="H150" t="s">
+        <v>542</v>
+      </c>
+      <c r="I150" t="s">
+        <v>21</v>
+      </c>
+      <c r="J150" t="s">
+        <v>30</v>
+      </c>
+      <c r="K150" t="s">
+        <v>23</v>
+      </c>
+      <c r="L150" t="s">
+        <v>852</v>
+      </c>
+      <c r="M150" t="s">
+        <v>853</v>
+      </c>
+    </row>
+    <row r="151" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A151" t="s">
+        <v>854</v>
+      </c>
+      <c r="B151" t="s">
+        <v>855</v>
+      </c>
+      <c r="C151" t="s">
+        <v>333</v>
+      </c>
+      <c r="D151" t="s">
+        <v>856</v>
+      </c>
+      <c r="E151" t="s">
+        <v>815</v>
+      </c>
+      <c r="F151" t="s">
+        <v>18</v>
+      </c>
+      <c r="G151" t="s">
+        <v>19</v>
+      </c>
+      <c r="H151" t="s">
+        <v>345</v>
+      </c>
+      <c r="I151" t="s">
+        <v>21</v>
+      </c>
+      <c r="J151" t="s">
+        <v>30</v>
+      </c>
+      <c r="K151" t="s">
+        <v>23</v>
+      </c>
+      <c r="L151" t="s">
+        <v>857</v>
+      </c>
+      <c r="M151" t="s">
+        <v>858</v>
+      </c>
+    </row>
+    <row r="152" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A152" t="s">
+        <v>859</v>
+      </c>
+      <c r="B152" t="s">
+        <v>860</v>
+      </c>
+      <c r="C152" t="s">
+        <v>15</v>
+      </c>
+      <c r="D152" t="s">
+        <v>861</v>
+      </c>
+      <c r="E152" t="s">
+        <v>815</v>
+      </c>
+      <c r="F152" t="s">
+        <v>18</v>
+      </c>
+      <c r="G152" t="s">
+        <v>19</v>
+      </c>
+      <c r="H152" t="s">
+        <v>29</v>
+      </c>
+      <c r="I152" t="s">
+        <v>21</v>
+      </c>
+      <c r="J152" t="s">
+        <v>30</v>
+      </c>
+      <c r="K152" t="s">
+        <v>23</v>
+      </c>
+      <c r="L152" t="s">
+        <v>862</v>
+      </c>
+      <c r="M152" t="s">
+        <v>863</v>
+      </c>
+    </row>
+    <row r="153" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A153" t="s">
+        <v>864</v>
+      </c>
+      <c r="B153" t="s">
+        <v>865</v>
+      </c>
+      <c r="C153" t="s">
+        <v>15</v>
+      </c>
+      <c r="D153" t="s">
+        <v>866</v>
+      </c>
+      <c r="E153" t="s">
+        <v>815</v>
+      </c>
+      <c r="F153" t="s">
+        <v>18</v>
+      </c>
+      <c r="G153" t="s">
+        <v>19</v>
+      </c>
+      <c r="H153" t="s">
+        <v>128</v>
+      </c>
+      <c r="I153" t="s">
+        <v>21</v>
+      </c>
+      <c r="J153" t="s">
+        <v>65</v>
+      </c>
+      <c r="K153" t="s">
+        <v>23</v>
+      </c>
+      <c r="L153" t="s">
+        <v>867</v>
+      </c>
+      <c r="M153" t="s">
+        <v>868</v>
+      </c>
+    </row>
+    <row r="154" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A154" t="s">
+        <v>869</v>
+      </c>
+      <c r="B154" t="s">
+        <v>870</v>
+      </c>
+      <c r="C154" t="s">
+        <v>15</v>
+      </c>
+      <c r="D154" t="s">
+        <v>871</v>
+      </c>
+      <c r="E154" t="s">
+        <v>815</v>
+      </c>
+      <c r="F154" t="s">
+        <v>18</v>
+      </c>
+      <c r="G154" t="s">
+        <v>19</v>
+      </c>
+      <c r="H154" t="s">
+        <v>20</v>
+      </c>
+      <c r="I154" t="s">
+        <v>21</v>
+      </c>
+      <c r="J154" t="s">
+        <v>30</v>
+      </c>
+      <c r="K154" t="s">
+        <v>23</v>
+      </c>
+      <c r="L154" t="s">
+        <v>872</v>
+      </c>
+      <c r="M154" t="s">
+        <v>873</v>
+      </c>
+    </row>
+    <row r="155" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A155" t="s">
+        <v>874</v>
+      </c>
+      <c r="B155" t="s">
+        <v>875</v>
+      </c>
+      <c r="C155" t="s">
+        <v>138</v>
+      </c>
+      <c r="D155" t="s">
+        <v>876</v>
+      </c>
+      <c r="E155" t="s">
+        <v>815</v>
+      </c>
+      <c r="F155" t="s">
+        <v>18</v>
+      </c>
+      <c r="G155" t="s">
+        <v>19</v>
+      </c>
+      <c r="H155" t="s">
+        <v>72</v>
+      </c>
+      <c r="I155" t="s">
+        <v>21</v>
+      </c>
+      <c r="J155" t="s">
+        <v>65</v>
+      </c>
+      <c r="K155" t="s">
+        <v>23</v>
+      </c>
+      <c r="L155" t="s">
+        <v>877</v>
+      </c>
+      <c r="M155" t="s">
+        <v>878</v>
+      </c>
+    </row>
+    <row r="156" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A156" t="s">
+        <v>879</v>
+      </c>
+      <c r="B156" t="s">
+        <v>880</v>
+      </c>
+      <c r="C156" t="s">
+        <v>15</v>
+      </c>
+      <c r="D156" t="s">
+        <v>881</v>
+      </c>
+      <c r="E156" t="s">
+        <v>815</v>
+      </c>
+      <c r="F156" t="s">
+        <v>18</v>
+      </c>
+      <c r="G156" t="s">
+        <v>19</v>
+      </c>
+      <c r="H156" t="s">
+        <v>72</v>
+      </c>
+      <c r="I156" t="s">
+        <v>21</v>
+      </c>
+      <c r="J156" t="s">
+        <v>51</v>
+      </c>
+      <c r="K156" t="s">
+        <v>23</v>
+      </c>
+      <c r="L156" t="s">
+        <v>882</v>
+      </c>
+      <c r="M156" t="s">
+        <v>883</v>
+      </c>
+    </row>
+    <row r="157" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A157" t="s">
+        <v>884</v>
+      </c>
+      <c r="B157" t="s">
+        <v>885</v>
+      </c>
+      <c r="C157" t="s">
+        <v>15</v>
+      </c>
+      <c r="D157" t="s">
+        <v>886</v>
+      </c>
+      <c r="E157" t="s">
+        <v>815</v>
+      </c>
+      <c r="F157" t="s">
+        <v>18</v>
+      </c>
+      <c r="G157" t="s">
+        <v>19</v>
+      </c>
+      <c r="H157" t="s">
+        <v>72</v>
+      </c>
+      <c r="I157" t="s">
+        <v>21</v>
+      </c>
+      <c r="J157" t="s">
+        <v>51</v>
+      </c>
+      <c r="K157" t="s">
+        <v>23</v>
+      </c>
+      <c r="L157" t="s">
+        <v>887</v>
+      </c>
+      <c r="M157" t="s">
+        <v>888</v>
+      </c>
+    </row>
+    <row r="158" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A158" t="s">
+        <v>889</v>
+      </c>
+      <c r="B158" t="s">
+        <v>890</v>
+      </c>
+      <c r="C158" t="s">
+        <v>88</v>
+      </c>
+      <c r="D158" t="s">
+        <v>891</v>
+      </c>
+      <c r="E158" t="s">
+        <v>815</v>
+      </c>
+      <c r="F158" t="s">
+        <v>18</v>
+      </c>
+      <c r="G158" t="s">
+        <v>19</v>
+      </c>
+      <c r="H158" t="s">
+        <v>72</v>
+      </c>
+      <c r="I158" t="s">
+        <v>21</v>
+      </c>
+      <c r="J158" t="s">
+        <v>65</v>
+      </c>
+      <c r="K158" t="s">
+        <v>23</v>
+      </c>
+      <c r="L158" t="s">
+        <v>892</v>
+      </c>
+      <c r="M158" t="s">
+        <v>893</v>
+      </c>
+    </row>
+    <row r="159" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A159" t="s">
+        <v>894</v>
+      </c>
+      <c r="B159" t="s">
+        <v>895</v>
+      </c>
+      <c r="C159" t="s">
+        <v>88</v>
+      </c>
+      <c r="D159" t="s">
+        <v>896</v>
+      </c>
+      <c r="E159" t="s">
+        <v>815</v>
+      </c>
+      <c r="F159" t="s">
+        <v>18</v>
+      </c>
+      <c r="G159" t="s">
+        <v>19</v>
+      </c>
+      <c r="H159" t="s">
+        <v>65</v>
+      </c>
+      <c r="I159" t="s">
+        <v>66</v>
+      </c>
+      <c r="J159" t="s">
+        <v>65</v>
+      </c>
+      <c r="K159" t="s">
+        <v>23</v>
+      </c>
+      <c r="L159" t="s">
+        <v>897</v>
+      </c>
+      <c r="M159" t="s">
+        <v>898</v>
+      </c>
+    </row>
+    <row r="160" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A160" t="s">
+        <v>899</v>
+      </c>
+      <c r="B160" t="s">
+        <v>900</v>
+      </c>
+      <c r="C160" t="s">
+        <v>577</v>
+      </c>
+      <c r="D160" t="s">
+        <v>901</v>
+      </c>
+      <c r="E160" t="s">
+        <v>815</v>
+      </c>
+      <c r="F160" t="s">
+        <v>18</v>
+      </c>
+      <c r="G160" t="s">
+        <v>19</v>
+      </c>
+      <c r="H160" t="s">
+        <v>36</v>
+      </c>
+      <c r="I160" t="s">
+        <v>902</v>
+      </c>
+      <c r="J160" t="s">
+        <v>903</v>
+      </c>
+      <c r="K160" t="s">
+        <v>23</v>
+      </c>
+      <c r="L160" t="s">
+        <v>904</v>
+      </c>
+      <c r="M160" t="s">
+        <v>905</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>

--- a/Sajjad data/by_country_and_state/USA/TX.xlsx
+++ b/Sajjad data/by_country_and_state/USA/TX.xlsx
@@ -11,7 +11,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2080" uniqueCount="906">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="2275" uniqueCount="990">
   <si>
     <t>Business Name</t>
   </si>
@@ -2729,6 +2729,258 @@
   </si>
   <si>
     <t>2026-10-24T22:38:26.693Z</t>
+  </si>
+  <si>
+    <t>Dentist Hispano Fort Bliss</t>
+  </si>
+  <si>
+    <t>(915) 877-0164</t>
+  </si>
+  <si>
+    <t>1141 Larry Mahan Dr, El Paso, TX 79925</t>
+  </si>
+  <si>
+    <t>El Paso</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dentist+Hispano+Fort+Bliss/data=!4m7!3m6!1s0x86e75b2ef9ada533:0xcc12b49657fcf3b6!8m2!3d31.7682326!4d-106.3669267!16s%2Fg%2F11rfnz2qhx!19sChIJM6Wt-S5b54YRtvP8V5a0Esw?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:47:14.630Z</t>
+  </si>
+  <si>
+    <t>El Paso City Dental Clinic</t>
+  </si>
+  <si>
+    <t>(915) 543-3580</t>
+  </si>
+  <si>
+    <t>City government office</t>
+  </si>
+  <si>
+    <t>3301 Pera Ave, El Paso, TX 79905</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/El+Paso+City+Dental+Clinic/data=!4m7!3m6!1s0x86e7599d0ac242fd:0xdf8061c355b91e12!8m2!3d31.772645!4d-106.455188!16s%2Fg%2F1tl4dgv_!19sChIJ_ULCCp1Z54YREh65VcNhgN8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:47:17.495Z</t>
+  </si>
+  <si>
+    <t>DE LA FUENTE FAMILY DENTISTRY</t>
+  </si>
+  <si>
+    <t>(915) 591-2525</t>
+  </si>
+  <si>
+    <t>1612 Lee Trevino Dr Ste b, El Paso, TX 79936</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/DE+LA+FUENTE+FAMILY+DENTISTRY/data=!4m7!3m6!1s0x86e744973c183551:0xb5a5eb6ce0a8bb1b!8m2!3d31.7577239!4d-106.3181034!16s%2Fg%2F11f3m9sc1h!19sChIJUTUYPJdE54YRG7uo4GzrpbU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:49:45.674Z</t>
+  </si>
+  <si>
+    <t>Dr. Karin L. Calderon, DDS</t>
+  </si>
+  <si>
+    <t>(915) 592-4168</t>
+  </si>
+  <si>
+    <t>1800 McRae Blvd Ste A, El Paso, TX 79925</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Karin+L.+Calderon,+DDS/data=!4m7!3m6!1s0x86e75b37276d3c01:0xdecc2ced821eda8e!8m2!3d31.7668636!4d-106.3552369!16s%2Fg%2F1thzpbq7!19sChIJATxtJzdb54YRjtoegu0szN4?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:51:25.554Z</t>
+  </si>
+  <si>
+    <t>El Paso Braces</t>
+  </si>
+  <si>
+    <t>(915) 249-4317</t>
+  </si>
+  <si>
+    <t>7878 Gtwy Blvd E #101, El Paso, TX 79915</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/El+Paso+Braces/data=!4m7!3m6!1s0x86e75b4c3abdce6b:0x2d96c6945484334f!8m2!3d31.7551707!4d-106.3512883!16s%2Fg%2F11dymg26bs!19sChIJa869Okxb54YRTzOEVJTGli0?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:51:41.082Z</t>
+  </si>
+  <si>
+    <t>Reynolds John W DDS</t>
+  </si>
+  <si>
+    <t>(915) 779-5781</t>
+  </si>
+  <si>
+    <t>5939 Gateway Blvd W, El Paso, TX 79925</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Reynolds+John+W+DDS/data=!4m7!3m6!1s0x86e75a4a1c624e77:0xd65c954d5944ed64!8m2!3d31.7815644!4d-106.4158497!16s%2Fg%2F1tgs1cs1!19sChIJd05iHEpa54YRZO1EWU2VXNY?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:51:44.391Z</t>
+  </si>
+  <si>
+    <t>Marquez Dental Implant Center</t>
+  </si>
+  <si>
+    <t>(915) 594-4048</t>
+  </si>
+  <si>
+    <t>11601 Pellicano Dr, El Paso, TX 79936</t>
+  </si>
+  <si>
+    <t>1</t>
+  </si>
+  <si>
+    <t>SaturdayClosed; SundayClosed; Monday8:30 AM–5 PM; Tuesday8:30 AM–5 PM; Wednesday8:30 AM–5 PM; Thursday8:30 AM–5 PM; FridayClosed</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Marquez+Dental+Implant+Center/data=!4m7!3m6!1s0x86e7437e05df51db:0xd575e6460d5ffef8!8m2!3d31.7458486!4d-106.3048776!16s%2Fg%2F1tdp5h71!19sChIJ21HfBX5D54YR-P5fDUbmddU?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:51:59.584Z</t>
+  </si>
+  <si>
+    <t>Emergency Dentist El Paso</t>
+  </si>
+  <si>
+    <t>(915) 265-4650</t>
+  </si>
+  <si>
+    <t>7815 Helen of Troy Dr, El Paso, TX 79912</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Emergency+Dentist+El+Paso/data=!4m7!3m6!1s0x86ddf917e9110493:0x9b8c5ed443cef2de!8m2!3d31.8764132!4d-106.5765709!16s%2Fg%2F11n8mszxd8!19sChIJkwQR6Rf53YYR3vLOQ9RejJs?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:52:10.642Z</t>
+  </si>
+  <si>
+    <t>Dentista Familiar de Emergencia El Paso</t>
+  </si>
+  <si>
+    <t>(915) 295-0476</t>
+  </si>
+  <si>
+    <t>1611 Marshall Rd, Fort Bliss, TX 79906</t>
+  </si>
+  <si>
+    <t>Fort Bliss</t>
+  </si>
+  <si>
+    <t>Saturday8 AM–5 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dentista+Familiar+de+Emergencia+El+Paso/data=!4m7!3m6!1s0x86e75b46bd18389f:0xb3aeabc1f0a88458!8m2!3d31.8175762!4d-106.4294298!16s%2Fg%2F11q2vxztdy!19sChIJnzgYvUZb54YRWISo8MGrrrM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:52:13.896Z</t>
+  </si>
+  <si>
+    <t>Dental Clinic #3</t>
+  </si>
+  <si>
+    <t>(915) 742-2685</t>
+  </si>
+  <si>
+    <t>2954 Carrington Rd, Fort Bliss, TX 79916</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+Clinic+%233/data=!4m7!3m6!1s0x86e75a73f6c78471:0x3320d21838cf48fd!8m2!3d31.8153408!4d-106.4121526!16s%2Fg%2F11bv1c8x4y!19sChIJcYTH9nNa54YR_UjPOBjSIDM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:52:28.852Z</t>
+  </si>
+  <si>
+    <t>Dr. Woong Lee, DDS.</t>
+  </si>
+  <si>
+    <t>(915) 771-7966</t>
+  </si>
+  <si>
+    <t>6065 Montana Ave, El Paso, TX 79925</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Woong+Lee,+DDS./data=!4m7!3m6!1s0x86e75a485ed84221:0x9fd26b532d4b5edc!8m2!3d31.7861479!4d-106.413685!16s%2Fg%2F1hc23nqpl!19sChIJIULYXkha54YR3F5LLVNr0p8?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:52:33.531Z</t>
+  </si>
+  <si>
+    <t>CHAMBERS DENTAL CLINIC</t>
+  </si>
+  <si>
+    <t>(915) 742-3368</t>
+  </si>
+  <si>
+    <t>11334 Ssg Sims St, Fort Bliss, TX 79908</t>
+  </si>
+  <si>
+    <t>2.0</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/CHAMBERS+DENTAL+CLINIC/data=!4m7!3m6!1s0x86e75074c719099f:0x437100fbdc6254c2!8m2!3d31.8303989!4d-106.369303!16s%2Fg%2F11ck455b1n!19sChIJnwkZx3RQ54YRwlRi3PsAcUM?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:52:48.940Z</t>
+  </si>
+  <si>
+    <t>Dr.Frederick W. Pirk, D.D.S.,M.S.,Inc.</t>
+  </si>
+  <si>
+    <t>(915) 581-7839</t>
+  </si>
+  <si>
+    <t>7211 N Mesa St Ste 1w, El Paso, TX 79912</t>
+  </si>
+  <si>
+    <t>18</t>
+  </si>
+  <si>
+    <t>SaturdayClosed; SundayClosed; Monday8 AM–5 PM; Tuesday8 AM–5 PM; Wednesday8 AM–5 PM; Thursday8 AM–5 PM; Friday7 AM–12 PM</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.Frederick+W.+Pirk,+D.D.S.,M.S.,Inc./data=!4m7!3m6!1s0x86ddf867c6592b39:0xaacc0ab9e236b632!8m2!3d31.8363759!4d-106.5561513!16s%2Fg%2F1tvym6j8!19sChIJOStZxmf43YYRMrY24rkKzKo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:53:13.463Z</t>
+  </si>
+  <si>
+    <t>Dr. Vahid Khoshkam</t>
+  </si>
+  <si>
+    <t>(915) 849-9000</t>
+  </si>
+  <si>
+    <t>1788 N Zaragoza Rd, El Paso, TX 79936</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dr.+Vahid+Khoshkam/data=!4m7!3m6!1s0x86e7440b322a6961:0x6ab03cbda278c7cf!8m2!3d31.7541013!4d-106.2753883!16s%2Fg%2F11qgb7460q!19sChIJYWkqMgtE54YRz8d4or08sGo?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:53:15.591Z</t>
+  </si>
+  <si>
+    <t>Dental Tourism Network</t>
+  </si>
+  <si>
+    <t>(915) 239-9759</t>
+  </si>
+  <si>
+    <t>306 W Paisano Dr #401, El Paso, TX 79901</t>
+  </si>
+  <si>
+    <t>https://www.google.com/maps/place/Dental+Tourism+Network/data=!4m7!3m6!1s0x86e7591d36e16b21:0x273eb38989456bc3!8m2!3d31.7554235!4d-106.4856434!16s%2Fg%2F1tfb2ft0!19sChIJIWvhNh1Z54YRw2tFiYmzPic?authuser=0&amp;hl=en&amp;g_ep=EgoyMDI2MTAyMC4wIJJjKgBIAVAD&amp;rclk=1</t>
+  </si>
+  <si>
+    <t>2026-10-25T03:53:18.980Z</t>
   </si>
 </sst>
 </file>
@@ -3109,7 +3361,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:M160"/>
+  <dimension ref="A1:M175"/>
   <sheetFormatPr defaultRowHeight="15" outlineLevelRow="0" outlineLevelCol="0" x14ac:dyDescent="55"/>
   <cols>
     <col min="1" max="1" width="34" customWidth="1"/>
@@ -9686,6 +9938,621 @@
         <v>905</v>
       </c>
     </row>
+    <row r="161" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A161" t="s">
+        <v>906</v>
+      </c>
+      <c r="B161" t="s">
+        <v>907</v>
+      </c>
+      <c r="C161" t="s">
+        <v>62</v>
+      </c>
+      <c r="D161" t="s">
+        <v>908</v>
+      </c>
+      <c r="E161" t="s">
+        <v>909</v>
+      </c>
+      <c r="F161" t="s">
+        <v>18</v>
+      </c>
+      <c r="G161" t="s">
+        <v>19</v>
+      </c>
+      <c r="H161" t="s">
+        <v>122</v>
+      </c>
+      <c r="I161" t="s">
+        <v>21</v>
+      </c>
+      <c r="J161" t="s">
+        <v>51</v>
+      </c>
+      <c r="K161" t="s">
+        <v>23</v>
+      </c>
+      <c r="L161" t="s">
+        <v>910</v>
+      </c>
+      <c r="M161" t="s">
+        <v>911</v>
+      </c>
+    </row>
+    <row r="162" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A162" t="s">
+        <v>912</v>
+      </c>
+      <c r="B162" t="s">
+        <v>913</v>
+      </c>
+      <c r="C162" t="s">
+        <v>914</v>
+      </c>
+      <c r="D162" t="s">
+        <v>915</v>
+      </c>
+      <c r="E162" t="s">
+        <v>909</v>
+      </c>
+      <c r="F162" t="s">
+        <v>18</v>
+      </c>
+      <c r="G162" t="s">
+        <v>19</v>
+      </c>
+      <c r="H162" t="s">
+        <v>345</v>
+      </c>
+      <c r="I162" t="s">
+        <v>21</v>
+      </c>
+      <c r="J162" t="s">
+        <v>65</v>
+      </c>
+      <c r="K162" t="s">
+        <v>23</v>
+      </c>
+      <c r="L162" t="s">
+        <v>916</v>
+      </c>
+      <c r="M162" t="s">
+        <v>917</v>
+      </c>
+    </row>
+    <row r="163" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A163" t="s">
+        <v>918</v>
+      </c>
+      <c r="B163" t="s">
+        <v>919</v>
+      </c>
+      <c r="C163" t="s">
+        <v>15</v>
+      </c>
+      <c r="D163" t="s">
+        <v>920</v>
+      </c>
+      <c r="E163" t="s">
+        <v>909</v>
+      </c>
+      <c r="F163" t="s">
+        <v>18</v>
+      </c>
+      <c r="G163" t="s">
+        <v>19</v>
+      </c>
+      <c r="H163" t="s">
+        <v>72</v>
+      </c>
+      <c r="I163" t="s">
+        <v>21</v>
+      </c>
+      <c r="J163" t="s">
+        <v>115</v>
+      </c>
+      <c r="K163" t="s">
+        <v>23</v>
+      </c>
+      <c r="L163" t="s">
+        <v>921</v>
+      </c>
+      <c r="M163" t="s">
+        <v>922</v>
+      </c>
+    </row>
+    <row r="164" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A164" t="s">
+        <v>923</v>
+      </c>
+      <c r="B164" t="s">
+        <v>924</v>
+      </c>
+      <c r="C164" t="s">
+        <v>333</v>
+      </c>
+      <c r="D164" t="s">
+        <v>925</v>
+      </c>
+      <c r="E164" t="s">
+        <v>909</v>
+      </c>
+      <c r="F164" t="s">
+        <v>18</v>
+      </c>
+      <c r="G164" t="s">
+        <v>19</v>
+      </c>
+      <c r="H164" t="s">
+        <v>65</v>
+      </c>
+      <c r="I164" t="s">
+        <v>66</v>
+      </c>
+      <c r="J164" t="s">
+        <v>65</v>
+      </c>
+      <c r="K164" t="s">
+        <v>23</v>
+      </c>
+      <c r="L164" t="s">
+        <v>926</v>
+      </c>
+      <c r="M164" t="s">
+        <v>927</v>
+      </c>
+    </row>
+    <row r="165" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A165" t="s">
+        <v>928</v>
+      </c>
+      <c r="B165" t="s">
+        <v>929</v>
+      </c>
+      <c r="C165" t="s">
+        <v>138</v>
+      </c>
+      <c r="D165" t="s">
+        <v>930</v>
+      </c>
+      <c r="E165" t="s">
+        <v>909</v>
+      </c>
+      <c r="F165" t="s">
+        <v>18</v>
+      </c>
+      <c r="G165" t="s">
+        <v>19</v>
+      </c>
+      <c r="H165" t="s">
+        <v>72</v>
+      </c>
+      <c r="I165" t="s">
+        <v>21</v>
+      </c>
+      <c r="J165" t="s">
+        <v>258</v>
+      </c>
+      <c r="K165" t="s">
+        <v>23</v>
+      </c>
+      <c r="L165" t="s">
+        <v>931</v>
+      </c>
+      <c r="M165" t="s">
+        <v>932</v>
+      </c>
+    </row>
+    <row r="166" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A166" t="s">
+        <v>933</v>
+      </c>
+      <c r="B166" t="s">
+        <v>934</v>
+      </c>
+      <c r="C166" t="s">
+        <v>15</v>
+      </c>
+      <c r="D166" t="s">
+        <v>935</v>
+      </c>
+      <c r="E166" t="s">
+        <v>909</v>
+      </c>
+      <c r="F166" t="s">
+        <v>18</v>
+      </c>
+      <c r="G166" t="s">
+        <v>19</v>
+      </c>
+      <c r="H166" t="s">
+        <v>250</v>
+      </c>
+      <c r="I166" t="s">
+        <v>21</v>
+      </c>
+      <c r="J166" t="s">
+        <v>65</v>
+      </c>
+      <c r="K166" t="s">
+        <v>23</v>
+      </c>
+      <c r="L166" t="s">
+        <v>936</v>
+      </c>
+      <c r="M166" t="s">
+        <v>937</v>
+      </c>
+    </row>
+    <row r="167" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A167" t="s">
+        <v>938</v>
+      </c>
+      <c r="B167" t="s">
+        <v>939</v>
+      </c>
+      <c r="C167" t="s">
+        <v>577</v>
+      </c>
+      <c r="D167" t="s">
+        <v>940</v>
+      </c>
+      <c r="E167" t="s">
+        <v>909</v>
+      </c>
+      <c r="F167" t="s">
+        <v>18</v>
+      </c>
+      <c r="G167" t="s">
+        <v>19</v>
+      </c>
+      <c r="H167" t="s">
+        <v>72</v>
+      </c>
+      <c r="I167" t="s">
+        <v>941</v>
+      </c>
+      <c r="J167" t="s">
+        <v>942</v>
+      </c>
+      <c r="K167" t="s">
+        <v>23</v>
+      </c>
+      <c r="L167" t="s">
+        <v>943</v>
+      </c>
+      <c r="M167" t="s">
+        <v>944</v>
+      </c>
+    </row>
+    <row r="168" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A168" t="s">
+        <v>945</v>
+      </c>
+      <c r="B168" t="s">
+        <v>946</v>
+      </c>
+      <c r="C168" t="s">
+        <v>88</v>
+      </c>
+      <c r="D168" t="s">
+        <v>947</v>
+      </c>
+      <c r="E168" t="s">
+        <v>909</v>
+      </c>
+      <c r="F168" t="s">
+        <v>18</v>
+      </c>
+      <c r="G168" t="s">
+        <v>19</v>
+      </c>
+      <c r="H168" t="s">
+        <v>345</v>
+      </c>
+      <c r="I168" t="s">
+        <v>21</v>
+      </c>
+      <c r="J168" t="s">
+        <v>65</v>
+      </c>
+      <c r="K168" t="s">
+        <v>23</v>
+      </c>
+      <c r="L168" t="s">
+        <v>948</v>
+      </c>
+      <c r="M168" t="s">
+        <v>949</v>
+      </c>
+    </row>
+    <row r="169" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A169" t="s">
+        <v>950</v>
+      </c>
+      <c r="B169" t="s">
+        <v>951</v>
+      </c>
+      <c r="C169" t="s">
+        <v>62</v>
+      </c>
+      <c r="D169" t="s">
+        <v>952</v>
+      </c>
+      <c r="E169" t="s">
+        <v>953</v>
+      </c>
+      <c r="F169" t="s">
+        <v>18</v>
+      </c>
+      <c r="G169" t="s">
+        <v>19</v>
+      </c>
+      <c r="H169" t="s">
+        <v>250</v>
+      </c>
+      <c r="I169" t="s">
+        <v>21</v>
+      </c>
+      <c r="J169" t="s">
+        <v>954</v>
+      </c>
+      <c r="K169" t="s">
+        <v>23</v>
+      </c>
+      <c r="L169" t="s">
+        <v>955</v>
+      </c>
+      <c r="M169" t="s">
+        <v>956</v>
+      </c>
+    </row>
+    <row r="170" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A170" t="s">
+        <v>957</v>
+      </c>
+      <c r="B170" t="s">
+        <v>958</v>
+      </c>
+      <c r="C170" t="s">
+        <v>62</v>
+      </c>
+      <c r="D170" t="s">
+        <v>959</v>
+      </c>
+      <c r="E170" t="s">
+        <v>953</v>
+      </c>
+      <c r="F170" t="s">
+        <v>18</v>
+      </c>
+      <c r="G170" t="s">
+        <v>19</v>
+      </c>
+      <c r="H170" t="s">
+        <v>78</v>
+      </c>
+      <c r="I170" t="s">
+        <v>21</v>
+      </c>
+      <c r="J170" t="s">
+        <v>30</v>
+      </c>
+      <c r="K170" t="s">
+        <v>23</v>
+      </c>
+      <c r="L170" t="s">
+        <v>960</v>
+      </c>
+      <c r="M170" t="s">
+        <v>961</v>
+      </c>
+    </row>
+    <row r="171" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A171" t="s">
+        <v>962</v>
+      </c>
+      <c r="B171" t="s">
+        <v>963</v>
+      </c>
+      <c r="C171" t="s">
+        <v>15</v>
+      </c>
+      <c r="D171" t="s">
+        <v>964</v>
+      </c>
+      <c r="E171" t="s">
+        <v>909</v>
+      </c>
+      <c r="F171" t="s">
+        <v>18</v>
+      </c>
+      <c r="G171" t="s">
+        <v>19</v>
+      </c>
+      <c r="H171" t="s">
+        <v>72</v>
+      </c>
+      <c r="I171" t="s">
+        <v>21</v>
+      </c>
+      <c r="J171" t="s">
+        <v>51</v>
+      </c>
+      <c r="K171" t="s">
+        <v>23</v>
+      </c>
+      <c r="L171" t="s">
+        <v>965</v>
+      </c>
+      <c r="M171" t="s">
+        <v>966</v>
+      </c>
+    </row>
+    <row r="172" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A172" t="s">
+        <v>967</v>
+      </c>
+      <c r="B172" t="s">
+        <v>968</v>
+      </c>
+      <c r="C172" t="s">
+        <v>15</v>
+      </c>
+      <c r="D172" t="s">
+        <v>969</v>
+      </c>
+      <c r="E172" t="s">
+        <v>953</v>
+      </c>
+      <c r="F172" t="s">
+        <v>18</v>
+      </c>
+      <c r="G172" t="s">
+        <v>19</v>
+      </c>
+      <c r="H172" t="s">
+        <v>970</v>
+      </c>
+      <c r="I172" t="s">
+        <v>21</v>
+      </c>
+      <c r="J172" t="s">
+        <v>51</v>
+      </c>
+      <c r="K172" t="s">
+        <v>23</v>
+      </c>
+      <c r="L172" t="s">
+        <v>971</v>
+      </c>
+      <c r="M172" t="s">
+        <v>972</v>
+      </c>
+    </row>
+    <row r="173" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A173" t="s">
+        <v>973</v>
+      </c>
+      <c r="B173" t="s">
+        <v>974</v>
+      </c>
+      <c r="C173" t="s">
+        <v>577</v>
+      </c>
+      <c r="D173" t="s">
+        <v>975</v>
+      </c>
+      <c r="E173" t="s">
+        <v>909</v>
+      </c>
+      <c r="F173" t="s">
+        <v>18</v>
+      </c>
+      <c r="G173" t="s">
+        <v>19</v>
+      </c>
+      <c r="H173" t="s">
+        <v>244</v>
+      </c>
+      <c r="I173" t="s">
+        <v>976</v>
+      </c>
+      <c r="J173" t="s">
+        <v>977</v>
+      </c>
+      <c r="K173" t="s">
+        <v>23</v>
+      </c>
+      <c r="L173" t="s">
+        <v>978</v>
+      </c>
+      <c r="M173" t="s">
+        <v>979</v>
+      </c>
+    </row>
+    <row r="174" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A174" t="s">
+        <v>980</v>
+      </c>
+      <c r="B174" t="s">
+        <v>981</v>
+      </c>
+      <c r="C174" t="s">
+        <v>15</v>
+      </c>
+      <c r="D174" t="s">
+        <v>982</v>
+      </c>
+      <c r="E174" t="s">
+        <v>909</v>
+      </c>
+      <c r="F174" t="s">
+        <v>18</v>
+      </c>
+      <c r="G174" t="s">
+        <v>19</v>
+      </c>
+      <c r="H174" t="s">
+        <v>72</v>
+      </c>
+      <c r="I174" t="s">
+        <v>21</v>
+      </c>
+      <c r="J174" t="s">
+        <v>65</v>
+      </c>
+      <c r="K174" t="s">
+        <v>23</v>
+      </c>
+      <c r="L174" t="s">
+        <v>983</v>
+      </c>
+      <c r="M174" t="s">
+        <v>984</v>
+      </c>
+    </row>
+    <row r="175" spans="1:13" x14ac:dyDescent="0.25">
+      <c r="A175" t="s">
+        <v>985</v>
+      </c>
+      <c r="B175" t="s">
+        <v>986</v>
+      </c>
+      <c r="C175" t="s">
+        <v>577</v>
+      </c>
+      <c r="D175" t="s">
+        <v>987</v>
+      </c>
+      <c r="E175" t="s">
+        <v>909</v>
+      </c>
+      <c r="F175" t="s">
+        <v>18</v>
+      </c>
+      <c r="G175" t="s">
+        <v>19</v>
+      </c>
+      <c r="H175" t="s">
+        <v>72</v>
+      </c>
+      <c r="I175" t="s">
+        <v>941</v>
+      </c>
+      <c r="J175" t="s">
+        <v>65</v>
+      </c>
+      <c r="K175" t="s">
+        <v>23</v>
+      </c>
+      <c r="L175" t="s">
+        <v>988</v>
+      </c>
+      <c r="M175" t="s">
+        <v>989</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="4294967295" verticalDpi="4294967295" scale="100" fitToWidth="1" fitToHeight="1"/>
